--- a/data/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/data/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X302"/>
+  <dimension ref="A1:X301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3040,7 +3040,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>ATENDIMENTOS ESCOLAS ESTADUAIS - CAIXAS ESCOLARES E CONVÊNIOS</t>
+          <t>OBRA - PROBLEMAS ESTRUTURAIS, ALÉM DE REFORMA E AMPLIAÇÃO DO PRÉDIO EE DR LAURO CORREA DO AMARAL</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3057,10 +3057,22 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Varginha</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>GUAPÉ</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>387600</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
@@ -3096,7 +3108,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>OBRA - PROBLEMAS ESTRUTURAIS, ALÉM DE REFORMA E AMPLIAÇÃO DO PRÉDIO EE DR LAURO CORREA DO AMARAL</t>
+          <t>CONCLUSÃO DA OBRA DE CONTENÇÃO DE TALUDE E RECUPERAÇÕES NA CONSTRUÇÃO EE ANTÔNIO MARINHO CAMPOS</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3115,16 +3127,16 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>GUAPÉ</t>
+          <t>IBIRITÉ</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>387600</v>
+        <v>361760</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -3164,7 +3176,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>CONCLUSÃO DA OBRA DE CONTENÇÃO DE TALUDE E RECUPERAÇÕES NA CONSTRUÇÃO EE ANTÔNIO MARINHO CAMPOS</t>
+          <t>OBRA DE CONTENÇÃO, REFORMA E REFORÇO ESTRUTURAL DO PRÉDIO EE ANTÔNIO PAPINI</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3183,16 +3195,16 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>IBIRITÉ</t>
+          <t>JOÃO MONLEVADE</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>361760</v>
+        <v>218500</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -3232,7 +3244,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>OBRA DE CONTENÇÃO, REFORMA E REFORÇO ESTRUTURAL DO PRÉDIO EE ANTÔNIO PAPINI</t>
+          <t>OBRA PARA REFORMA/RESTAURAÇÃO E  REPAROS ESTRUTURAIS EE DUQUE DE CAXIAS</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3251,16 +3263,16 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>JOÃO MONLEVADE</t>
+          <t>JUIZ DE FORA</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>218500</v>
+        <v>1976000</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3300,7 +3312,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA/RESTAURAÇÃO E  REPAROS ESTRUTURAIS EE DUQUE DE CAXIAS</t>
+          <t>OBRA DE CONSTRUÇÃO DA SEDESEDE DA SRE DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3319,16 +3331,16 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>JUIZ DE FORA</t>
+          <t>MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>1976000</v>
+        <v>805600</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -3368,7 +3380,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>OBRA DE CONSTRUÇÃO DA SEDESEDE DA SRE DE MONTES CLAROS</t>
+          <t>OBRAS DE CONTENÇÃO EE AUGUSTO DE LIMA</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3387,16 +3399,16 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>MONTES CLAROS</t>
+          <t>NOVA LIMA</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>805600</v>
+        <v>760000</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -3436,7 +3448,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>OBRAS DE CONTENÇÃO EE AUGUSTO DE LIMA</t>
+          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS  ESTRUTURAIS NO EDIFÍCIO, INCLUINDO INFILTRAÇÃO NAS PAREDES, DETERIORAÇÃO DO GUARDA-CORPO NA FACHADA, ABATIMENTO NO PISO, ASSOALHO DANIFICADO E INCLINAÇÃO DA FACHADA.EE PROFESSOR PINHEIRO CAMPOS</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3455,16 +3467,16 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>NOVA LIMA</t>
+          <t>OLIVEIRA</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>760000</v>
+        <v>653600</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -3504,12 +3516,12 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS  ESTRUTURAIS NO EDIFÍCIO, INCLUINDO INFILTRAÇÃO NAS PAREDES, DETERIORAÇÃO DO GUARDA-CORPO NA FACHADA, ABATIMENTO NO PISO, ASSOALHO DANIFICADO E INCLINAÇÃO DA FACHADA.EE PROFESSOR PINHEIRO CAMPOS</t>
+          <t>REFORMA GERAL E RESTAURAÇÃO EE DOM PEDRO II</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -3523,16 +3535,16 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>OLIVEIRA</t>
+          <t>OURO PRETO</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>653600</v>
+        <v>1204600</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -3572,12 +3584,12 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>REFORMA GERAL E RESTAURAÇÃO EE DOM PEDRO II</t>
+          <t>OBRA PARA RESTAURAÇÃO EE PROFESSOR ANTÔNIO DIAS MACIEL</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -3591,16 +3603,16 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
+          <t>PATOS DE MINAS</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>1204600</v>
+        <v>1927740</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -3640,7 +3652,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>OBRA PARA RESTAURAÇÃO EE PROFESSOR ANTÔNIO DIAS MACIEL</t>
+          <t>OBRA RESTAURAÇÃO INSTITUTO DE EDUCAÇÃO DE JUIZ DE FORA</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3659,16 +3671,16 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>PATOS DE MINAS</t>
+          <t>JUIZ DE FORA</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>1927740</v>
+        <v>653600</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -3708,7 +3720,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>OBRA RESTAURAÇÃO INSTITUTO DE EDUCAÇÃO DE JUIZ DE FORA</t>
+          <t>OBRA - PROBLEMAS REFERENTES À CONTENÇÃO DE TALUDE E DRENAGEM PLUVIALEE HENRIQUE BURNIER</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3736,7 +3748,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>653600</v>
+        <v>19000</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -3776,7 +3788,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>OBRA - PROBLEMAS REFERENTES À CONTENÇÃO DE TALUDE E DRENAGEM PLUVIALEE HENRIQUE BURNIER</t>
+          <t>OBRA - PROBLEMAS REFERENTES À CONTENÇÃO DE TALUDE E DRENAGEM PLUVIALEE BATISTA DE OLIVEIRA</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3844,7 +3856,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>OBRA - PROBLEMAS REFERENTES À CONTENÇÃO DE TALUDE E DRENAGEM PLUVIALEE BATISTA DE OLIVEIRA</t>
+          <t>OBRA REFORMA, RESTAURAÇÃO E AMPLIAÇÃOEE ANA ROCHA (PREDIO EE FREI LEOPOLDO)</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3863,16 +3875,16 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>JUIZ DE FORA</t>
+          <t>MATUTINA</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>19000</v>
+        <v>1318600</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -3912,12 +3924,12 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>OBRA REFORMA, RESTAURAÇÃO E AMPLIAÇÃOEE ANA ROCHA (PREDIO EE FREI LEOPOLDO)</t>
+          <t>OBRA PARA REFORMA DA EDIFICAÇÃO E EXECUÇÃO DAS OBRAS DE ESTABILIZAÇÃO DE TALUDE, REFORÇO DA CONTENÇÃO E CONSTRUÇÃO DE NOVO MURO DE DIVISA EE JULIETA DE OLIVEIRA MACEDO</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -3931,16 +3943,16 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>MATUTINA</t>
+          <t>MURIAÉ</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>1318600</v>
+        <v>653600</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -3980,12 +3992,12 @@
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA DA EDIFICAÇÃO E EXECUÇÃO DAS OBRAS DE ESTABILIZAÇÃO DE TALUDE, REFORÇO DA CONTENÇÃO E CONSTRUÇÃO DE NOVO MURO DE DIVISA EE JULIETA DE OLIVEIRA MACEDO</t>
+          <t>CONSTRUÇÃO DE PRÉDIO DA SEDE DA SRE DE MURIAÉ</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -4008,7 +4020,7 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>653600</v>
+        <v>19000</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -4048,7 +4060,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO DE PRÉDIO DA SEDE DA SRE DE MURIAÉ</t>
+          <t>OBRA DE REFORMA SEDE DA SRE DE NOVA ERA</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4067,12 +4079,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>MURIAÉ</t>
+          <t>NOVA ERA</t>
         </is>
       </c>
       <c r="Q53" t="n">
@@ -4116,7 +4128,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>OBRA DE REFORMA SEDE DA SRE DE NOVA ERA</t>
+          <t>OBRAS PARA PROBLEMAS ESTRUTURAIS NO AUDITÓRIO (ESTRUTURA PISO E TELHADO) - REFORMA GERAL E RESTAURAÇÃO - PRÉDIO TOMBADOEE FRANCISCO FERNANDES</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4135,16 +4147,16 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>NOVA ERA</t>
+          <t>OLIVEIRA</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>19000</v>
+        <v>760000</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -4184,7 +4196,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>OBRAS PARA PROBLEMAS ESTRUTURAIS NO AUDITÓRIO (ESTRUTURA PISO E TELHADO) - REFORMA GERAL E RESTAURAÇÃO - PRÉDIO TOMBADOEE FRANCISCO FERNANDES</t>
+          <t xml:space="preserve">OBRA PARA REFORMA GERAL / RESTAURAÇÃO EE CONSELHEIRO AFONSO PENA </t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4203,16 +4215,16 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>OLIVEIRA</t>
+          <t>PARAOPEBA</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>760000</v>
+        <v>19000</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -4252,7 +4264,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBRA PARA REFORMA GERAL / RESTAURAÇÃO EE CONSELHEIRO AFONSO PENA </t>
+          <t>OBRA PARA RESTAURAÇÃOEE DOM LUSTOSA</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4271,12 +4283,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>PARAOPEBA</t>
+          <t>PATROCÍNIO</t>
         </is>
       </c>
       <c r="Q56" t="n">
@@ -4320,7 +4332,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>OBRA PARA RESTAURAÇÃOEE DOM LUSTOSA</t>
+          <t>OBRA DE RESTAURAÇÃOSEDE DA SRE DE PATROCÍNIO</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4388,7 +4400,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>OBRA DE RESTAURAÇÃOSEDE DA SRE DE PATROCÍNIO</t>
+          <t>OBRA PARA REFORMA E RESTAURAÇÃO DO PRÉDIOEE FRANCISCA BOTELHO</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4407,16 +4419,16 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>PATROCÍNIO</t>
+          <t>PITANGUI</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>19000</v>
+        <v>434720</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -4456,7 +4468,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E RESTAURAÇÃO DO PRÉDIOEE FRANCISCA BOTELHO</t>
+          <t>OBRA  DE REFORMA E RESTAURAÇÃOCESEC TANCREDO NEVES (PRÉDIO OCUPADO ANTERIORMENTE PELA EE FARNESE MACIEL )</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4475,16 +4487,16 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>PITANGUI</t>
+          <t>PRESIDENTE OLEGÁRIO</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>434720</v>
+        <v>221160</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -4524,7 +4536,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>OBRA  DE REFORMA E RESTAURAÇÃOCESEC TANCREDO NEVES (PRÉDIO OCUPADO ANTERIORMENTE PELA EE FARNESE MACIEL )</t>
+          <t>CONCLUSÃO DA OBRA DE REFORMA E RESTAURAÇÃO EE JOAO DOS SANTOS</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4543,16 +4555,16 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Barbacena</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>PRESIDENTE OLEGÁRIO</t>
+          <t>SÃO JOÃO DEL REI</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>221160</v>
+        <v>1748000</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -4592,7 +4604,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>CONCLUSÃO DA OBRA DE REFORMA E RESTAURAÇÃO EE JOAO DOS SANTOS</t>
+          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS ESTRUTURAISSEDE DA SRE DE SETE LAGOAS</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4611,16 +4623,16 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>SÃO JOÃO DEL REI</t>
+          <t>SETE LAGOAS</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>1748000</v>
+        <v>479560</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -4660,7 +4672,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS ESTRUTURAISSEDE DA SRE DE SETE LAGOAS</t>
+          <t>OBRA PARA REPAROS ESTRUTURAIS (EXECUÇÃO DO REFORÇO DE FUNDAÇÃO E SERVIÇOS CORRELATOS) - 1A ETAPAEE DEPUTADO CARLOS PEIXOTO FILHO</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4679,16 +4691,16 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>SETE LAGOAS</t>
+          <t>UBÁ</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>479560</v>
+        <v>228000</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -4728,12 +4740,12 @@
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>OBRA PARA REPAROS ESTRUTURAIS (EXECUÇÃO DO REFORÇO DE FUNDAÇÃO E SERVIÇOS CORRELATOS) - 1A ETAPAEE DEPUTADO CARLOS PEIXOTO FILHO</t>
+          <t>CONSTRUÇÃO DE ESCOLA - 16 SALAS DE AULA (NO BAIRRO JARDIM CÉLIA)EE 13 DE MAIO</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -4747,16 +4759,16 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>UBÁ</t>
+          <t>UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>228000</v>
+        <v>2552080</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -4796,12 +4808,12 @@
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO DE ESCOLA - 16 SALAS DE AULA (NO BAIRRO JARDIM CÉLIA)EE 13 DE MAIO</t>
+          <t>REFORMA / REFORÇO ESTRUTURALEE CORAÇÃO DE JESUS</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -4815,16 +4827,16 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>UBERLÂNDIA</t>
+          <t>VARGINHA</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>2552080</v>
+        <v>1386240</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
@@ -4864,7 +4876,7 @@
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>REFORMA / REFORÇO ESTRUTURALEE CORAÇÃO DE JESUS</t>
+          <t>OBRA PARA REFORMA/RESTAURAÇÃO EE BRASIL</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4892,7 +4904,7 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>1386240</v>
+        <v>1900000</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
@@ -4932,7 +4944,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA/RESTAURAÇÃO EE BRASIL</t>
+          <t>OBRA DE REFORMA E RESTAURAÇÃOEE DR. JOÃO PINHEIRO</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4956,11 +4968,11 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>VARGINHA</t>
+          <t>SÃO GONÇALO DO SAPUCAÍ</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>1900000</v>
+        <v>1008140</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
@@ -5000,7 +5012,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>OBRA DE REFORMA E RESTAURAÇÃOEE DR. JOÃO PINHEIRO</t>
+          <t>OBRAS PARA MURO DE ARRIMO E DRENAGEM, ALÉM DE REFORMA/RESTAURAÇÃO EE MINISTRO EDMUNDO LINS</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -5019,16 +5031,16 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Teófilo Otoni</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>SÃO GONÇALO DO SAPUCAÍ</t>
+          <t>SERRO</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>1008140</v>
+        <v>380000</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
@@ -5068,7 +5080,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>OBRAS PARA MURO DE ARRIMO E DRENAGEM, ALÉM DE REFORMA/RESTAURAÇÃO EE MINISTRO EDMUNDO LINS</t>
+          <t>OBRA PARA REFORMA E RESTAURAÇÃOEE DR. ARTHUR BERNARDES</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5087,16 +5099,16 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Região Intermediária de Teófilo Otoni</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>SERRO</t>
+          <t>SETE LAGOAS</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>380000</v>
+        <v>228000</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
@@ -5136,7 +5148,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E RESTAURAÇÃOEE DR. ARTHUR BERNARDES</t>
+          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS ESTRUTURAISEE HAYDÉE DE SOUZA ABREU</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5155,16 +5167,16 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>SETE LAGOAS</t>
+          <t>TIMÓTEO</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>228000</v>
+        <v>539600</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
@@ -5204,7 +5216,7 @@
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS ESTRUTURAISEE HAYDÉE DE SOUZA ABREU</t>
+          <t>OBRA - MANUTENÇÃO E REVISÃO COMPLETA DAS COBERTURAS; PINTURA EXTERNA E INTERNA; RESTAURO DE ESQUADRIAS;  REVISÃO DE TODA A REDE ELÉTRICA; RESTAURO DA PINTURA ARTÍSTICA DO RODATETO E PROSPECÇÃO EXPLORATÓRIA NO HALL DE ENTRADA, VISANDO AVALIAR A EXISTÊ</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5223,16 +5235,16 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>TIMÓTEO</t>
+          <t>UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>539600</v>
+        <v>19000</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
@@ -5272,12 +5284,12 @@
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>OBRA - MANUTENÇÃO E REVISÃO COMPLETA DAS COBERTURAS; PINTURA EXTERNA E INTERNA; RESTAURO DE ESQUADRIAS;  REVISÃO DE TODA A REDE ELÉTRICA; RESTAURO DA PINTURA ARTÍSTICA DO RODATETO E PROSPECÇÃO EXPLORATÓRIA NO HALL DE ENTRADA, VISANDO AVALIAR A EXISTÊ</t>
+          <t>OBRA PARA RESTAURAÇÃO EE AFONSO PENA</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -5291,16 +5303,16 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>UBERLÂNDIA</t>
+          <t>VARGINHA</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>19000</v>
+        <v>2074800</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
@@ -5314,33 +5326,35 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1261</v>
+        <v>1301</v>
       </c>
       <c r="B72" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C72" t="n">
-        <v>368</v>
+        <v>451</v>
       </c>
       <c r="D72" t="n">
-        <v>168</v>
+        <v>81</v>
       </c>
       <c r="E72" t="n">
-        <v>4519</v>
+        <v>1037</v>
       </c>
       <c r="F72" t="n">
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
         <v>71</v>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="n">
+        <v>12404</v>
+      </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>OBRA PARA RESTAURAÇÃO EE AFONSO PENA</t>
+          <t>DC-018/2023-Execução das serviço de Aumento de capacidade e Recuperação de Rodovia (aumento de capacidade) no trecho Três Pontas - Varginhas (Estaca 80 a 610), com 10,60 km de extensão, na Rodovia MG-167</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5349,12 +5363,10 @@
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="n">
-        <v>1</v>
-      </c>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -5364,14 +5376,14 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>VARGINHA</t>
+          <t>TRÊS PONTAS</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>2074800</v>
+        <v>280106</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>519640</v>
       </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
@@ -5406,11 +5418,11 @@
         <v>72</v>
       </c>
       <c r="I73" t="n">
-        <v>12404</v>
+        <v>12780</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>DC-018/2023-Execução das serviço de Aumento de capacidade e Recuperação de Rodovia (aumento de capacidade) no trecho Três Pontas - Varginhas (Estaca 80 a 610), com 10,60 km de extensão, na Rodovia MG-167</t>
+          <t>Execução das obras de Implantação de Passarela na Rodovia MG-010, Km 15+850, trecho Belo Horizonte - Lagoa Santa (Cidade Administrativa), extensão de 312,00 m</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5427,19 +5439,19 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>TRÊS PONTAS</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>280106</v>
+        <v>894720</v>
       </c>
       <c r="R73" t="n">
-        <v>519640</v>
+        <v>4087644</v>
       </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
@@ -5474,11 +5486,11 @@
         <v>73</v>
       </c>
       <c r="I74" t="n">
-        <v>12780</v>
+        <v>10397</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Execução das obras de Implantação de Passarela na Rodovia MG-010, Km 15+850, trecho Belo Horizonte - Lagoa Santa (Cidade Administrativa), extensão de 312,00 m</t>
+          <t>PRC-22.021/18 -Melhoramento e pavimentação no trecho Ibertioga  Piedade do Rio Grande, na Rodovia MG/338, extensão de 13,25km</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5495,19 +5507,19 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Barbacena</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>IBERTIOGA</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>894720</v>
+        <v>8264640</v>
       </c>
       <c r="R74" t="n">
-        <v>4087644</v>
+        <v>19153735</v>
       </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
@@ -5542,11 +5554,11 @@
         <v>74</v>
       </c>
       <c r="I75" t="n">
-        <v>10397</v>
+        <v>12850</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>PRC-22.021/18 -Melhoramento e pavimentação no trecho Ibertioga  Piedade do Rio Grande, na Rodovia MG/338, extensão de 13,25km</t>
+          <t>Melhoramento e pavimentação do trecho de Jaboticatubas - Lagoa Santa, em rodovia Municipal.</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5563,19 +5575,19 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>IBERTIOGA</t>
+          <t>JABOTICATUBAS</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>8264640</v>
+        <v>3155040</v>
       </c>
       <c r="R75" t="n">
-        <v>19153735</v>
+        <v>23943007</v>
       </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
@@ -5610,11 +5622,11 @@
         <v>75</v>
       </c>
       <c r="I76" t="n">
-        <v>12850</v>
+        <v>12634</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Melhoramento e pavimentação do trecho de Jaboticatubas - Lagoa Santa, em rodovia Municipal.</t>
+          <t>Melhoramento e pavimentação do Trecho Itapagipe - Entrº 364 (Campina Verde) MGC 154 - LOTE 01</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5631,19 +5643,19 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>JABOTICATUBAS</t>
+          <t>ITAPAGIPE</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>3155040</v>
+        <v>4840800</v>
       </c>
       <c r="R76" t="n">
-        <v>23943007</v>
+        <v>26593690</v>
       </c>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
@@ -5678,11 +5690,11 @@
         <v>76</v>
       </c>
       <c r="I77" t="n">
-        <v>12634</v>
+        <v>12785</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Melhoramento e pavimentação do Trecho Itapagipe - Entrº 364 (Campina Verde) MGC 154 - LOTE 01</t>
+          <t>Execução da Obra de Engenharia de Melhoramento e pavimentação da Interseção de acesso ao Presídio de Iturama, na via Municipal, com extensão de 2,000 km.</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5704,14 +5716,14 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>ITAPAGIPE</t>
+          <t>ITURAMA</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>4840800</v>
+        <v>613500</v>
       </c>
       <c r="R77" t="n">
-        <v>26593690</v>
+        <v>2870210</v>
       </c>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
@@ -5746,11 +5758,11 @@
         <v>77</v>
       </c>
       <c r="I78" t="n">
-        <v>12785</v>
+        <v>12824</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Execução da Obra de Engenharia de Melhoramento e pavimentação da Interseção de acesso ao Presídio de Iturama, na via Municipal, com extensão de 2,000 km.</t>
+          <t>Melhoramento e Pavimentação em Rodovia de Ligação no trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700 km e Segmento 2 (835 a 1250), extensão 8,300 km.</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5767,19 +5779,19 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>ITURAMA</t>
+          <t>PARACATU</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>613500</v>
+        <v>5963400</v>
       </c>
       <c r="R78" t="n">
-        <v>2870210</v>
+        <v>23280000</v>
       </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
@@ -5814,11 +5826,11 @@
         <v>78</v>
       </c>
       <c r="I79" t="n">
-        <v>12824</v>
+        <v>4716</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação em Rodovia de Ligação no trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700 km e Segmento 2 (835 a 1250), extensão 8,300 km.</t>
+          <t>Entr. BR/365-Entr. LMG/782 (p/ Iraí de Minas), Monte Carmelo-Chapada de Minas e Pindaibas-Ent.BR/365</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5835,19 +5847,19 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>PARACATU</t>
+          <t>MONTE CARMELO</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>5963400</v>
+        <v>3620820</v>
       </c>
       <c r="R79" t="n">
-        <v>23280000</v>
+        <v>19100000</v>
       </c>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
@@ -5881,17 +5893,15 @@
       <c r="H80" t="n">
         <v>79</v>
       </c>
-      <c r="I80" t="n">
-        <v>4716</v>
-      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Entr. BR/365-Entr. LMG/782 (p/ Iraí de Minas), Monte Carmelo-Chapada de Minas e Pindaibas-Ent.BR/365</t>
+          <t>Recapeamento de vias / pavimentação de trecho rodoviário / pavimentação e obra de arte especial no trecho viário; para melhoria da infraestrutura viária do Estado de Minas Gerais (8 propostas de novos convênios)</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -5903,19 +5913,19 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>MONTE CARMELO</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>3620820</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>19100000</v>
+        <v>11755000</v>
       </c>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr"/>
@@ -5935,10 +5945,10 @@
         <v>451</v>
       </c>
       <c r="D81" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="E81" t="n">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
@@ -5949,15 +5959,17 @@
       <c r="H81" t="n">
         <v>80</v>
       </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="n">
+        <v>11140</v>
+      </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Recapeamento de vias / pavimentação de trecho rodoviário / pavimentação e obra de arte especial no trecho viário; para melhoria da infraestrutura viária do Estado de Minas Gerais (8 propostas de novos convênios)</t>
+          <t xml:space="preserve">CONSTRUÇÃO DE 64 UNIDADES HABITACIONAIS PAC FNHIS </t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -5969,19 +5981,19 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>1839798</v>
       </c>
       <c r="R81" t="n">
-        <v>11755000</v>
+        <v>3269655</v>
       </c>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr"/>
@@ -6016,11 +6028,11 @@
         <v>81</v>
       </c>
       <c r="I82" t="n">
-        <v>11140</v>
+        <v>11531</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONSTRUÇÃO DE 64 UNIDADES HABITACIONAIS PAC FNHIS </t>
+          <t>REQUALIFICAÇÃO URBANA E AMBIENTAL DO RIBEIRÃO ARRUDAS - FNHIS/2009 - Continuidade da execução do PTTS (Programa de Trabalho Técnico-Social)</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -6046,10 +6058,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>1839798</v>
+        <v>222899</v>
       </c>
       <c r="R82" t="n">
-        <v>3269655</v>
+        <v>0</v>
       </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
@@ -6072,7 +6084,7 @@
         <v>99</v>
       </c>
       <c r="E83" t="n">
-        <v>1038</v>
+        <v>4262</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
@@ -6083,12 +6095,10 @@
       <c r="H83" t="n">
         <v>82</v>
       </c>
-      <c r="I83" t="n">
-        <v>11531</v>
-      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
-          <t>REQUALIFICAÇÃO URBANA E AMBIENTAL DO RIBEIRÃO ARRUDAS - FNHIS/2009 - Continuidade da execução do PTTS (Programa de Trabalho Técnico-Social)</t>
+          <t>Aquisição de materiais para obras - mata-burros, vigas metálicas e bueiros metálicos</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -6105,16 +6115,16 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>222899</v>
+        <v>10932874</v>
       </c>
       <c r="R83" t="n">
         <v>0</v>
@@ -6131,16 +6141,16 @@
         <v>1301</v>
       </c>
       <c r="B84" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C84" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D84" t="n">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="E84" t="n">
-        <v>4262</v>
+        <v>4290</v>
       </c>
       <c r="F84" t="n">
         <v>1</v>
@@ -6151,10 +6161,12 @@
       <c r="H84" t="n">
         <v>83</v>
       </c>
-      <c r="I84" t="inlineStr"/>
+      <c r="I84" t="n">
+        <v>12510</v>
+      </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Aquisição de materiais para obras - mata-burros, vigas metálicas e bueiros metálicos</t>
+          <t xml:space="preserve"> tratamento viário para implantação de sistema BRS em dois corredores de importância metropolitana na Região Metropolitana de Belo Horizonte (RMBH)</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -6171,19 +6183,19 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>10932874</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>40000000</v>
       </c>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr"/>
@@ -6217,17 +6229,15 @@
       <c r="H85" t="n">
         <v>84</v>
       </c>
-      <c r="I85" t="n">
-        <v>12510</v>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve"> tratamento viário para implantação de sistema BRS em dois corredores de importância metropolitana na Região Metropolitana de Belo Horizonte (RMBH)</t>
+          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE - Obra Av Brasília)</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -6248,10 +6258,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>478579</v>
       </c>
       <c r="R85" t="n">
-        <v>40000000</v>
+        <v>0</v>
       </c>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr"/>
@@ -6288,7 +6298,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE - Obra Av Brasília)</t>
+          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE - Obra Av Civilização/Vilarinho)</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -6314,7 +6324,7 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>478579</v>
+        <v>2246479</v>
       </c>
       <c r="R86" t="n">
         <v>0</v>
@@ -6354,7 +6364,7 @@
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE - Obra Av Civilização/Vilarinho)</t>
+          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE -  Obras Estações  BRT MG10)</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6380,7 +6390,7 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>2246479</v>
+        <v>156926</v>
       </c>
       <c r="R87" t="n">
         <v>0</v>
@@ -6397,16 +6407,16 @@
         <v>1301</v>
       </c>
       <c r="B88" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C88" t="n">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D88" t="n">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="E88" t="n">
-        <v>4290</v>
+        <v>1036</v>
       </c>
       <c r="F88" t="n">
         <v>1</v>
@@ -6417,15 +6427,17 @@
       <c r="H88" t="n">
         <v>87</v>
       </c>
-      <c r="I88" t="inlineStr"/>
+      <c r="I88" t="n">
+        <v>12453</v>
+      </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE -  Obras Estações  BRT MG10)</t>
+          <t>LOTE 1 EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM ALEM PARAIBA</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
@@ -6437,19 +6449,19 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>ALÉM PARAÍBA</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>156926</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>539924</v>
       </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="inlineStr"/>
@@ -6484,11 +6496,11 @@
         <v>88</v>
       </c>
       <c r="I89" t="n">
-        <v>12453</v>
+        <v>12454</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>LOTE 1 EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM ALEM PARAIBA</t>
+          <t>LOTE  2 -  EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM MURIAE</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6510,14 +6522,14 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>ALÉM PARAÍBA</t>
+          <t>MURIAÉ</t>
         </is>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>539924</v>
+        <v>15337533</v>
       </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr"/>
@@ -6552,11 +6564,11 @@
         <v>89</v>
       </c>
       <c r="I90" t="n">
-        <v>12454</v>
+        <v>11521</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>LOTE  2 -  EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM MURIAE</t>
+          <t>Obras de contenção de encostas em Sabará - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6573,19 +6585,19 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>MURIAÉ</t>
+          <t>SABARÁ</t>
         </is>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>15337533</v>
+        <v>1440021</v>
       </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="inlineStr"/>
@@ -6620,11 +6632,11 @@
         <v>90</v>
       </c>
       <c r="I91" t="n">
-        <v>11521</v>
+        <v>11519</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Obras de contenção de encostas em Sabará - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>Obras de contenção de encostas em João Monlevade - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6641,19 +6653,19 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>SABARÁ</t>
+          <t>JOÃO MONLEVADE</t>
         </is>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>1440021</v>
+        <v>6942767</v>
       </c>
       <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr"/>
@@ -6688,16 +6700,16 @@
         <v>91</v>
       </c>
       <c r="I92" t="n">
-        <v>11519</v>
+        <v>11512</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Obras de contenção de encostas em João Monlevade - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>bras de contenção de encostas em Timóteo - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Respostas a Desastres.</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -6714,14 +6726,14 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>JOÃO MONLEVADE</t>
+          <t>TIMÓTEO</t>
         </is>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>6942767</v>
+        <v>14686005</v>
       </c>
       <c r="S92" t="inlineStr"/>
       <c r="T92" t="inlineStr"/>
@@ -6756,16 +6768,16 @@
         <v>92</v>
       </c>
       <c r="I93" t="n">
-        <v>11512</v>
+        <v>11514</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>bras de contenção de encostas em Timóteo - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Respostas a Desastres.</t>
+          <t>Obras de Contenção de encostas em Ouro Preto - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e resposta a desastres.</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -6777,19 +6789,19 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>TIMÓTEO</t>
+          <t>OURO PRETO</t>
         </is>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>14686005</v>
+        <v>52160376</v>
       </c>
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr"/>
@@ -6824,11 +6836,11 @@
         <v>93</v>
       </c>
       <c r="I94" t="n">
-        <v>11514</v>
+        <v>11511</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Obras de Contenção de encostas em Ouro Preto - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e resposta a desastres.</t>
+          <t>Obras de Contenção de encostas em Manhumirim, Lajinha, Ervália,Sabinópolis e Diogo de Vasconcelos - Intervenção em setores de risco alto e muito alto. No ambito do Programa PAC gestão de riscos e proposta a desastres.</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6845,19 +6857,19 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>52160376</v>
+        <v>20521500</v>
       </c>
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr"/>
@@ -6892,11 +6904,11 @@
         <v>94</v>
       </c>
       <c r="I95" t="n">
-        <v>11511</v>
+        <v>11520</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Obras de Contenção de encostas em Manhumirim, Lajinha, Ervália,Sabinópolis e Diogo de Vasconcelos - Intervenção em setores de risco alto e muito alto. No ambito do Programa PAC gestão de riscos e proposta a desastres.</t>
+          <t>Obras de contenção de encostas em Santa Luzia - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6913,19 +6925,19 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>SANTA LUZIA</t>
         </is>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>20521500</v>
+        <v>6952445</v>
       </c>
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr"/>
@@ -6960,11 +6972,11 @@
         <v>95</v>
       </c>
       <c r="I96" t="n">
-        <v>11520</v>
+        <v>11513</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Obras de contenção de encostas em Santa Luzia - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>Obras de Contenção de encostas em Ewbank da Câmara, Matias Barbosa e Visconde do Rio Branco - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e proposta a desastre.</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6981,19 +6993,19 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>SANTA LUZIA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>6952445</v>
+        <v>12959175</v>
       </c>
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
@@ -7028,11 +7040,11 @@
         <v>96</v>
       </c>
       <c r="I97" t="n">
-        <v>11513</v>
+        <v>11977</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Obras de Contenção de encostas em Ewbank da Câmara, Matias Barbosa e Visconde do Rio Branco - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e proposta a desastre.</t>
+          <t>Execução de Obras de Contenção de Encostas em Cataguases/MG - Intervenção em setores de risco alto e muito alto, no âmbito do programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -7049,19 +7061,19 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>CATAGUASES</t>
         </is>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>12959175</v>
+        <v>38244490</v>
       </c>
       <c r="S97" t="inlineStr"/>
       <c r="T97" t="inlineStr"/>
@@ -7096,11 +7108,11 @@
         <v>97</v>
       </c>
       <c r="I98" t="n">
-        <v>11977</v>
+        <v>11162</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Execução de Obras de Contenção de Encostas em Cataguases/MG - Intervenção em setores de risco alto e muito alto, no âmbito do programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>OBRAS DE ESTABILIZAÇÃO E CONTENÇÃO DE ENCOSTAS E DESLIZAMENTOS EM ÁREAS URBANAS</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -7117,19 +7129,19 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>CATAGUASES</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>9858067</v>
       </c>
       <c r="R98" t="n">
-        <v>38244490</v>
+        <v>0</v>
       </c>
       <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr"/>
@@ -7152,7 +7164,7 @@
         <v>139</v>
       </c>
       <c r="E99" t="n">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="F99" t="n">
         <v>1</v>
@@ -7164,11 +7176,11 @@
         <v>98</v>
       </c>
       <c r="I99" t="n">
-        <v>11162</v>
+        <v>12699</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>OBRAS DE ESTABILIZAÇÃO E CONTENÇÃO DE ENCOSTAS E DESLIZAMENTOS EM ÁREAS URBANAS</t>
+          <t>SERVIÇOS TÉCNICOS ESPECIALIZADOS PARA A CONCLUSÃO DA IMPLEMENTAÇÃO DO PTTS  PROJETO DE TRABALHO TÉCNICO SOCIAL- PROGRAMA DE REQUALIFICAÇÃO URBANA E AMBIENTAL E CONTROLE DE CHEIAS DO CÓRREGO FERRUGEM</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -7185,16 +7197,16 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>9858067</v>
+        <v>299895</v>
       </c>
       <c r="R99" t="n">
         <v>0</v>
@@ -7232,11 +7244,11 @@
         <v>99</v>
       </c>
       <c r="I100" t="n">
-        <v>12699</v>
+        <v>11536</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>SERVIÇOS TÉCNICOS ESPECIALIZADOS PARA A CONCLUSÃO DA IMPLEMENTAÇÃO DO PTTS  PROJETO DE TRABALHO TÉCNICO SOCIAL- PROGRAMA DE REQUALIFICAÇÃO URBANA E AMBIENTAL E CONTROLE DE CHEIAS DO CÓRREGO FERRUGEM</t>
+          <t>Construção de 192 unidades habitacionais referente a 2ª etapa da Requalificação urbana e ambiental do Córrego Ferrugem</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -7262,7 +7274,7 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>299895</v>
+        <v>4565604</v>
       </c>
       <c r="R100" t="n">
         <v>0</v>
@@ -7288,7 +7300,7 @@
         <v>139</v>
       </c>
       <c r="E101" t="n">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="F101" t="n">
         <v>1</v>
@@ -7300,11 +7312,11 @@
         <v>100</v>
       </c>
       <c r="I101" t="n">
-        <v>11536</v>
+        <v>11855</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Construção de 192 unidades habitacionais referente a 2ª etapa da Requalificação urbana e ambiental do Córrego Ferrugem</t>
+          <t>REMANESCENTE DAS OBRAS DE INFRAESTRUTURA PARA A CONCLUSAO DAS BACIAS DO CONTROLE DE CHEIAS DO CORREGO RIACHO DAS PEDRAS.</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -7330,10 +7342,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>4565604</v>
+        <v>6286532</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>2728583</v>
       </c>
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="inlineStr"/>
@@ -7368,11 +7380,11 @@
         <v>101</v>
       </c>
       <c r="I102" t="n">
-        <v>11855</v>
+        <v>11973</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>REMANESCENTE DAS OBRAS DE INFRAESTRUTURA PARA A CONCLUSAO DAS BACIAS DO CONTROLE DE CHEIAS DO CORREGO RIACHO DAS PEDRAS.</t>
+          <t>execução do Plano de Trabalho Técnico-Social - PTTS, que é uma exigência do contrato de financiamento PAC RIACHO</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -7398,10 +7410,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>6286532</v>
+        <v>193263</v>
       </c>
       <c r="R102" t="n">
-        <v>2728583</v>
+        <v>0</v>
       </c>
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="inlineStr"/>
@@ -7412,19 +7424,19 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1301</v>
+        <v>1371</v>
       </c>
       <c r="B103" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C103" t="n">
-        <v>451</v>
+        <v>511</v>
       </c>
       <c r="D103" t="n">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="E103" t="n">
-        <v>1041</v>
+        <v>4118</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
@@ -7435,17 +7447,15 @@
       <c r="H103" t="n">
         <v>102</v>
       </c>
-      <c r="I103" t="n">
-        <v>11973</v>
-      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
-          <t>execução do Plano de Trabalho Técnico-Social - PTTS, que é uma exigência do contrato de financiamento PAC RIACHO</t>
+          <t>Programa Água Doce - RIMC</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -7457,19 +7467,19 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>193263</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>4547000</v>
       </c>
       <c r="S103" t="inlineStr"/>
       <c r="T103" t="inlineStr"/>
@@ -7506,7 +7516,7 @@
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Programa Água Doce - RIMC</t>
+          <t>Programa Água Doce - RITO</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -7523,12 +7533,12 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Teófilo Otoni</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE TEÓFILO OTONI</t>
         </is>
       </c>
       <c r="Q104" t="n">
@@ -7546,25 +7556,25 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1371</v>
+        <v>1451</v>
       </c>
       <c r="B105" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C105" t="n">
-        <v>511</v>
+        <v>421</v>
       </c>
       <c r="D105" t="n">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="E105" t="n">
-        <v>4118</v>
+        <v>1048</v>
       </c>
       <c r="F105" t="n">
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" t="n">
         <v>104</v>
@@ -7572,12 +7582,12 @@
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Programa Água Doce - RITO</t>
+          <t>Construção de uma unidade prisional de segurança média com aproximadamente 800 (oitocentas) vagas.</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>PARALISADO</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -7589,19 +7599,19 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Região Intermediária de Teófilo Otoni</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE TEÓFILO OTONI</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>904245</v>
       </c>
       <c r="R105" t="n">
-        <v>4547000</v>
+        <v>44308050</v>
       </c>
       <c r="S105" t="inlineStr"/>
       <c r="T105" t="inlineStr"/>
@@ -7618,13 +7628,13 @@
         <v>6</v>
       </c>
       <c r="C106" t="n">
-        <v>421</v>
+        <v>243</v>
       </c>
       <c r="D106" t="n">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="E106" t="n">
-        <v>1048</v>
+        <v>4441</v>
       </c>
       <c r="F106" t="n">
         <v>1</v>
@@ -7638,7 +7648,7 @@
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Construção de uma unidade prisional de segurança média com aproximadamente 800 (oitocentas) vagas.</t>
+          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -7655,19 +7665,19 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>904245</v>
+        <v>6999284</v>
       </c>
       <c r="R106" t="n">
-        <v>44308050</v>
+        <v>0</v>
       </c>
       <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr"/>
@@ -7726,11 +7736,11 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>6999284</v>
+        <v>651694</v>
       </c>
       <c r="R107" t="n">
         <v>0</v>
@@ -7787,12 +7797,12 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>ALFENAS</t>
         </is>
       </c>
       <c r="Q108" t="n">
@@ -7853,16 +7863,16 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>ALFENAS</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>651694</v>
+        <v>1472757</v>
       </c>
       <c r="R109" t="n">
         <v>0</v>
@@ -7919,16 +7929,16 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>ARAXÁ</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>1472757</v>
+        <v>651694</v>
       </c>
       <c r="R110" t="n">
         <v>0</v>
@@ -7985,16 +7995,16 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>ARAXÁ</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>651694</v>
+        <v>18572878</v>
       </c>
       <c r="R111" t="n">
         <v>0</v>
@@ -8008,25 +8018,25 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1451</v>
+        <v>1501</v>
       </c>
       <c r="B112" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C112" t="n">
-        <v>243</v>
+        <v>122</v>
       </c>
       <c r="D112" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E112" t="n">
-        <v>4441</v>
+        <v>4476</v>
       </c>
       <c r="F112" t="n">
         <v>1</v>
       </c>
       <c r="G112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H112" t="n">
         <v>111</v>
@@ -8034,12 +8044,12 @@
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
+          <t>REDIMENSIONAMENTO DE REDE ELÉTRICA (NRPMSO`S) - Garantir a segurança elétrica para implementação de novos equipamentos</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
@@ -8051,16 +8061,16 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>18572878</v>
+        <v>270000</v>
       </c>
       <c r="R112" t="n">
         <v>0</v>
@@ -8083,10 +8093,10 @@
         <v>122</v>
       </c>
       <c r="D113" t="n">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="E113" t="n">
-        <v>4476</v>
+        <v>4465</v>
       </c>
       <c r="F113" t="n">
         <v>1</v>
@@ -8100,7 +8110,7 @@
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
-          <t>REDIMENSIONAMENTO DE REDE ELÉTRICA (NRPMSO`S) - Garantir a segurança elétrica para implementação de novos equipamentos</t>
+          <t>Construção de um abrigo de Resíduos Sólidos e guaritas de segurança externa na CAMG</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -8126,7 +8136,7 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>270000</v>
+        <v>1100000</v>
       </c>
       <c r="R113" t="n">
         <v>0</v>
@@ -8166,7 +8176,7 @@
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Construção de um abrigo de Resíduos Sólidos e guaritas de segurança externa na CAMG</t>
+          <t xml:space="preserve">Execução do projeto de reutilização da água da purga </t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -8192,7 +8202,7 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>1100000</v>
+        <v>624000</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
@@ -8232,7 +8242,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Execução do projeto de reutilização da água da purga </t>
+          <t>Projeto de modernização da alimentação elétrica emergencial dos elevadores</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -8258,7 +8268,7 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>624000</v>
+        <v>210000</v>
       </c>
       <c r="R115" t="n">
         <v>0</v>
@@ -8298,7 +8308,7 @@
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Projeto de modernização da alimentação elétrica emergencial dos elevadores</t>
+          <t>Programa de monitoramento e responsabilidade técnica das barragens da Cidade Administrativa</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -8324,7 +8334,7 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>210000</v>
+        <v>150000</v>
       </c>
       <c r="R116" t="n">
         <v>0</v>
@@ -8364,7 +8374,7 @@
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Programa de monitoramento e responsabilidade técnica das barragens da Cidade Administrativa</t>
+          <t>Impermeabilização das coberturas do prédio Alterosa e reforço estrutural do estacionamento do Alterosas</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -8390,7 +8400,7 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>150000</v>
+        <v>3918408</v>
       </c>
       <c r="R117" t="n">
         <v>0</v>
@@ -8413,10 +8423,10 @@
         <v>122</v>
       </c>
       <c r="D118" t="n">
-        <v>156</v>
+        <v>705</v>
       </c>
       <c r="E118" t="n">
-        <v>4465</v>
+        <v>2500</v>
       </c>
       <c r="F118" t="n">
         <v>1</v>
@@ -8430,7 +8440,7 @@
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Impermeabilização das coberturas do prédio Alterosa e reforço estrutural do estacionamento do Alterosas</t>
+          <t>Projeto AVCB para o antigo prédio do IOF na av. Augusto de Lima</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -8438,11 +8448,17 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M118" t="n">
+        <v>1</v>
+      </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -8456,7 +8472,7 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>3918408</v>
+        <v>282000</v>
       </c>
       <c r="R118" t="n">
         <v>0</v>
@@ -8470,19 +8486,19 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1501</v>
+        <v>1511</v>
       </c>
       <c r="B119" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C119" t="n">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="D119" t="n">
-        <v>705</v>
+        <v>32</v>
       </c>
       <c r="E119" t="n">
-        <v>2500</v>
+        <v>1006</v>
       </c>
       <c r="F119" t="n">
         <v>1</v>
@@ -8496,7 +8512,7 @@
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Projeto AVCB para o antigo prédio do IOF na av. Augusto de Lima</t>
+          <t xml:space="preserve">1ª Fase da Execução da Obra de Reformas e Adaptações da Antiga Cadeia Pública de Teofilo Otoni onde será instalada a Nova Delegacia Especializada no Atendimento a Mulher da DRPC de Teofilo Otoni. </t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -8504,34 +8520,28 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M119" t="n">
-        <v>1</v>
-      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>282000</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="S119" t="inlineStr"/>
       <c r="T119" t="inlineStr"/>
@@ -8554,7 +8564,7 @@
         <v>32</v>
       </c>
       <c r="E120" t="n">
-        <v>1006</v>
+        <v>4063</v>
       </c>
       <c r="F120" t="n">
         <v>1</v>
@@ -8568,7 +8578,7 @@
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1ª Fase da Execução da Obra de Reformas e Adaptações da Antiga Cadeia Pública de Teofilo Otoni onde será instalada a Nova Delegacia Especializada no Atendimento a Mulher da DRPC de Teofilo Otoni. </t>
+          <t>Construção do Complexo que irá abrigar o Núcleo Integrado de Perícias</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -8585,19 +8595,19 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="R120" t="n">
-        <v>1000000</v>
+        <v>19850000</v>
       </c>
       <c r="S120" t="inlineStr"/>
       <c r="T120" t="inlineStr"/>
@@ -8608,19 +8618,19 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1511</v>
+        <v>1541</v>
       </c>
       <c r="B121" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C121" t="n">
-        <v>181</v>
+        <v>122</v>
       </c>
       <c r="D121" t="n">
-        <v>32</v>
+        <v>705</v>
       </c>
       <c r="E121" t="n">
-        <v>4063</v>
+        <v>2500</v>
       </c>
       <c r="F121" t="n">
         <v>1</v>
@@ -8634,12 +8644,12 @@
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Construção do Complexo que irá abrigar o Núcleo Integrado de Perícias</t>
+          <t>REFORMA DA ESCOLA DE SAÚDE PÚBLICA DO MUNICÍPIO DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
@@ -8656,14 +8666,14 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>150000</v>
+        <v>2896100</v>
       </c>
       <c r="R121" t="n">
-        <v>19850000</v>
+        <v>0</v>
       </c>
       <c r="S121" t="inlineStr"/>
       <c r="T121" t="inlineStr"/>
@@ -8674,19 +8684,19 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1541</v>
+        <v>2011</v>
       </c>
       <c r="B122" t="n">
         <v>10</v>
       </c>
       <c r="C122" t="n">
-        <v>122</v>
+        <v>302</v>
       </c>
       <c r="D122" t="n">
-        <v>705</v>
+        <v>88</v>
       </c>
       <c r="E122" t="n">
-        <v>2500</v>
+        <v>4231</v>
       </c>
       <c r="F122" t="n">
         <v>1</v>
@@ -8697,15 +8707,17 @@
       <c r="H122" t="n">
         <v>121</v>
       </c>
-      <c r="I122" t="inlineStr"/>
+      <c r="I122" t="n">
+        <v>12871</v>
+      </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>REFORMA DA ESCOLA DE SAÚDE PÚBLICA DO MUNICÍPIO DE BELO HORIZONTE</t>
+          <t xml:space="preserve">EXECUCAO DE OBRAS POR CONTRATO DE BENS PATRIMONIAVEIS adequação do HGIP para obtenção do AVCB                       </t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L122" t="inlineStr"/>
@@ -8726,10 +8738,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>2896100</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr"/>
@@ -8764,11 +8776,11 @@
         <v>122</v>
       </c>
       <c r="I123" t="n">
-        <v>12871</v>
+        <v>9999</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">EXECUCAO DE OBRAS POR CONTRATO DE BENS PATRIMONIAVEIS adequação do HGIP para obtenção do AVCB                       </t>
+          <t xml:space="preserve">Reforma da Endoscopia - HGIP </t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8797,7 +8809,7 @@
         <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>2000000</v>
+        <v>1600000</v>
       </c>
       <c r="S123" t="inlineStr"/>
       <c r="T123" t="inlineStr"/>
@@ -8814,13 +8826,13 @@
         <v>10</v>
       </c>
       <c r="C124" t="n">
-        <v>302</v>
+        <v>122</v>
       </c>
       <c r="D124" t="n">
-        <v>88</v>
+        <v>705</v>
       </c>
       <c r="E124" t="n">
-        <v>4231</v>
+        <v>2500</v>
       </c>
       <c r="F124" t="n">
         <v>1</v>
@@ -8832,11 +8844,11 @@
         <v>123</v>
       </c>
       <c r="I124" t="n">
-        <v>9999</v>
+        <v>12690</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reforma da Endoscopia - HGIP </t>
+          <t>Apoio à GELENG, no atendimento às demandas de serviços de reforma e manutenção nas unidades.</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8865,7 +8877,7 @@
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>1600000</v>
+        <v>2200000</v>
       </c>
       <c r="S124" t="inlineStr"/>
       <c r="T124" t="inlineStr"/>
@@ -8876,19 +8888,19 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>2011</v>
+        <v>2101</v>
       </c>
       <c r="B125" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C125" t="n">
-        <v>122</v>
+        <v>541</v>
       </c>
       <c r="D125" t="n">
-        <v>705</v>
+        <v>31</v>
       </c>
       <c r="E125" t="n">
-        <v>2500</v>
+        <v>4058</v>
       </c>
       <c r="F125" t="n">
         <v>1</v>
@@ -8899,12 +8911,10 @@
       <c r="H125" t="n">
         <v>124</v>
       </c>
-      <c r="I125" t="n">
-        <v>12690</v>
-      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Apoio à GELENG, no atendimento às demandas de serviços de reforma e manutenção nas unidades.</t>
+          <t>Construção do Cetras de Governador Valadares</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -8912,28 +8922,34 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M125" t="n">
+        <v>1</v>
+      </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="R125" t="n">
-        <v>2200000</v>
+        <v>0</v>
       </c>
       <c r="S125" t="inlineStr"/>
       <c r="T125" t="inlineStr"/>
@@ -8956,7 +8972,7 @@
         <v>31</v>
       </c>
       <c r="E126" t="n">
-        <v>4058</v>
+        <v>4059</v>
       </c>
       <c r="F126" t="n">
         <v>1</v>
@@ -8970,7 +8986,7 @@
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Construção do Cetras de Governador Valadares</t>
+          <t>APA Parque Cataguás</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -9002,7 +9018,7 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>350000</v>
+        <v>1000000</v>
       </c>
       <c r="R126" t="n">
         <v>0</v>
@@ -9016,19 +9032,19 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2101</v>
+        <v>2151</v>
       </c>
       <c r="B127" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C127" t="n">
-        <v>541</v>
+        <v>572</v>
       </c>
       <c r="D127" t="n">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="E127" t="n">
-        <v>4059</v>
+        <v>1023</v>
       </c>
       <c r="F127" t="n">
         <v>1</v>
@@ -9042,7 +9058,7 @@
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
-          <t>APA Parque Cataguás</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA ELABORAÇÃO DE ESTUDOS TÉCNICOS, LEVANTAMENTOS TOPOGRÁFICOS, SONDAGENS, ESTUDOS AMBIENTAIS, PROJETOS DE ARQUITETURA E ENGENHARIA, ORÇAMENTOS, MEMORIAIS DESCRITIVOS E AFINS</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -9050,31 +9066,25 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M127" t="n">
-        <v>1</v>
-      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>IBIRITÉ</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>1000000</v>
+        <v>200000</v>
       </c>
       <c r="R127" t="n">
         <v>0</v>
@@ -9094,13 +9104,13 @@
         <v>12</v>
       </c>
       <c r="C128" t="n">
-        <v>572</v>
+        <v>122</v>
       </c>
       <c r="D128" t="n">
-        <v>75</v>
+        <v>705</v>
       </c>
       <c r="E128" t="n">
-        <v>1023</v>
+        <v>2500</v>
       </c>
       <c r="F128" t="n">
         <v>1</v>
@@ -9114,7 +9124,7 @@
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA ELABORAÇÃO DE ESTUDOS TÉCNICOS, LEVANTAMENTOS TOPOGRÁFICOS, SONDAGENS, ESTUDOS AMBIENTAIS, PROJETOS DE ARQUITETURA E ENGENHARIA, ORÇAMENTOS, MEMORIAIS DESCRITIVOS E AFINS</t>
+          <t>CONTRATAÇÃO DO CONSÓRCIO PGM / SINAURB CIDERSU (PGM CONSTRUÇÕES E EMPREENDIMENTOS LTDA E SINAURB SERVIÇOS E EMPREENDIMENTOS LTDA) PRESTAÇÃO DE SERVIÇOS COMUNS E CONTÍNUOS DE ENGENHARIA, SOB DEMANDA, DESTINADOS À MANUTENÇÃO PREDIAL, CONSERVAÇÃO E EXEC</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -9140,7 +9150,7 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>200000</v>
+        <v>1500000</v>
       </c>
       <c r="R128" t="n">
         <v>0</v>
@@ -9154,19 +9164,19 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2151</v>
+        <v>2161</v>
       </c>
       <c r="B129" t="n">
         <v>12</v>
       </c>
       <c r="C129" t="n">
-        <v>122</v>
+        <v>242</v>
       </c>
       <c r="D129" t="n">
-        <v>705</v>
+        <v>5</v>
       </c>
       <c r="E129" t="n">
-        <v>2500</v>
+        <v>1030</v>
       </c>
       <c r="F129" t="n">
         <v>1</v>
@@ -9180,12 +9190,12 @@
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DO CONSÓRCIO PGM / SINAURB CIDERSU (PGM CONSTRUÇÕES E EMPREENDIMENTOS LTDA E SINAURB SERVIÇOS E EMPREENDIMENTOS LTDA) PRESTAÇÃO DE SERVIÇOS COMUNS E CONTÍNUOS DE ENGENHARIA, SOB DEMANDA, DESTINADOS À MANUTENÇÃO PREDIAL, CONSERVAÇÃO E EXEC</t>
+          <t>Projeto para melhoria de acessibilidade nas unidades da FUCAM</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>PARALISADO</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -9197,16 +9207,16 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>IBIRITÉ</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>1500000</v>
+        <v>14000</v>
       </c>
       <c r="R129" t="n">
         <v>0</v>
@@ -9263,16 +9273,16 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE PATOS DE MINAS</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>14000</v>
+        <v>3000</v>
       </c>
       <c r="R130" t="n">
         <v>0</v>
@@ -9329,12 +9339,12 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE PATOS DE MINAS</t>
+          <t>ESMERALDAS</t>
         </is>
       </c>
       <c r="Q131" t="n">
@@ -9352,19 +9362,19 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2161</v>
+        <v>2261</v>
       </c>
       <c r="B132" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C132" t="n">
-        <v>242</v>
+        <v>303</v>
       </c>
       <c r="D132" t="n">
-        <v>5</v>
+        <v>154</v>
       </c>
       <c r="E132" t="n">
-        <v>1030</v>
+        <v>4460</v>
       </c>
       <c r="F132" t="n">
         <v>1</v>
@@ -9375,15 +9385,17 @@
       <c r="H132" t="n">
         <v>131</v>
       </c>
-      <c r="I132" t="inlineStr"/>
+      <c r="I132" t="n">
+        <v>12502</v>
+      </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Projeto para melhoria de acessibilidade nas unidades da FUCAM</t>
+          <t>Execução de Obras da nova sede da Divisão de Controle de Qualidade.</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L132" t="inlineStr"/>
@@ -9400,11 +9412,11 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>ESMERALDAS</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>3000</v>
+        <v>500000</v>
       </c>
       <c r="R132" t="n">
         <v>0</v>
@@ -9424,13 +9436,13 @@
         <v>10</v>
       </c>
       <c r="C133" t="n">
-        <v>303</v>
+        <v>122</v>
       </c>
       <c r="D133" t="n">
-        <v>154</v>
+        <v>705</v>
       </c>
       <c r="E133" t="n">
-        <v>4460</v>
+        <v>2500</v>
       </c>
       <c r="F133" t="n">
         <v>1</v>
@@ -9442,11 +9454,11 @@
         <v>132</v>
       </c>
       <c r="I133" t="n">
-        <v>12502</v>
+        <v>12500</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Execução de Obras da nova sede da Divisão de Controle de Qualidade.</t>
+          <t>Novo Prédio Administrativo da FUNED em Steel Frame (Unidade IV)</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -9472,7 +9484,7 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>500000</v>
+        <v>10535000</v>
       </c>
       <c r="R133" t="n">
         <v>0</v>
@@ -9509,12 +9521,10 @@
       <c r="H134" t="n">
         <v>133</v>
       </c>
-      <c r="I134" t="n">
-        <v>12500</v>
-      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Novo Prédio Administrativo da FUNED em Steel Frame (Unidade IV)</t>
+          <t>Obras de adequação estrutural do refeitório para atendimento às exigências da Vigilância Sanitária Municipal.</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -9540,7 +9550,7 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>10535000</v>
+        <v>500000</v>
       </c>
       <c r="R134" t="n">
         <v>0</v>
@@ -9554,19 +9564,19 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2261</v>
+        <v>2301</v>
       </c>
       <c r="B135" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C135" t="n">
-        <v>122</v>
+        <v>782</v>
       </c>
       <c r="D135" t="n">
-        <v>705</v>
+        <v>81</v>
       </c>
       <c r="E135" t="n">
-        <v>2500</v>
+        <v>4268</v>
       </c>
       <c r="F135" t="n">
         <v>1</v>
@@ -9580,7 +9590,7 @@
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Obras de adequação estrutural do refeitório para atendimento às exigências da Vigilância Sanitária Municipal.</t>
+          <t>REABILITAÇÃO DA MG-010 (CONCEIÇÃO DO MATO DENTRO A SERRO)</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -9597,19 +9607,19 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="S135" t="inlineStr"/>
       <c r="T135" t="inlineStr"/>
@@ -9646,7 +9656,7 @@
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
-          <t>REABILITAÇÃO DA MG-010 (CONCEIÇÃO DO MATO DENTRO A SERRO)</t>
+          <t>REABILITAÇÃO DA MG-129 (OURO PRETO A OURO BRANCO)</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -9712,7 +9722,7 @@
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
-          <t>REABILITAÇÃO DA MG-129 (OURO PRETO A OURO BRANCO)</t>
+          <t>RESTAURAÇÃO RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO) E RECOMPOSIÇÃO DE TALUDE ERODIDO</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -9741,7 +9751,7 @@
         <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>5000000</v>
+        <v>10000000</v>
       </c>
       <c r="S137" t="inlineStr"/>
       <c r="T137" t="inlineStr"/>
@@ -9778,7 +9788,7 @@
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO) E RECOMPOSIÇÃO DE TALUDE ERODIDO</t>
+          <t>ARCOS - CORUMBÁ - RODOVIA: MG-170 (ENTR BR-354 - AGRIMIG)</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -9804,10 +9814,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>9792000</v>
       </c>
       <c r="R138" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="S138" t="inlineStr"/>
       <c r="T138" t="inlineStr"/>
@@ -9844,7 +9854,7 @@
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
-          <t>ARCOS - CORUMBÁ - RODOVIA: MG-170 (ENTR BR-354 - AGRIMIG)</t>
+          <t>MG-129 - OURO PRETO A OURO BRANCO</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -9870,7 +9880,7 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>9792000</v>
+        <v>1000000</v>
       </c>
       <c r="R139" t="n">
         <v>0</v>
@@ -9910,7 +9920,7 @@
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
-          <t>MG-129 - OURO PRETO A OURO BRANCO</t>
+          <t>RECUPERAÇÃO DE EROSÃO EM TALUDE DE CORTE NA RODOVIA MGC-354, KM 167,8, TRECHO: RIBEIRÃO DA MATA - AV MARABÁ (PATOS DE MINAS)</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9936,7 +9946,7 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>1000000</v>
+        <v>143000</v>
       </c>
       <c r="R140" t="n">
         <v>0</v>
@@ -9976,7 +9986,7 @@
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO DE EROSÃO EM TALUDE DE CORTE NA RODOVIA MGC-354, KM 167,8, TRECHO: RIBEIRÃO DA MATA - AV MARABÁ (PATOS DE MINAS)</t>
+          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 150,9, TRECHO: TRAVESSIA URBANA DE PRESIDENTE OLEGÁRIO</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -10002,7 +10012,7 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>143000</v>
+        <v>5876140</v>
       </c>
       <c r="R141" t="n">
         <v>0</v>
@@ -10042,7 +10052,7 @@
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 150,9, TRECHO: TRAVESSIA URBANA DE PRESIDENTE OLEGÁRIO</t>
+          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 176,2, TRECHO: AV MARABÁ (PATOS DE MINAS) - ENTR BR 365</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -10068,7 +10078,7 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>5876140</v>
+        <v>1132500</v>
       </c>
       <c r="R142" t="n">
         <v>0</v>
@@ -10108,7 +10118,7 @@
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 176,2, TRECHO: AV MARABÁ (PATOS DE MINAS) - ENTR BR 365</t>
+          <t>RESTAURAÇÃO E 3ª FAIXA, TRECHO ENTR. BR-354 (CAXAMBÚ) - ENTR. BR-381 (PALMELA DISTRITO DE CAMPANHA), NA MGC-267</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -10134,7 +10144,7 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>1132500</v>
+        <v>1000000</v>
       </c>
       <c r="R143" t="n">
         <v>0</v>
@@ -10174,7 +10184,7 @@
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E 3ª FAIXA, TRECHO ENTR. BR-354 (CAXAMBÚ) - ENTR. BR-381 (PALMELA DISTRITO DE CAMPANHA), NA MGC-267</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE (3ª FAIXA) DO TRECHO SERRA DO SALITRE - SALITRE DE MINAS, NA MG-230</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -10200,7 +10210,7 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>1000000</v>
+        <v>34710000</v>
       </c>
       <c r="R144" t="n">
         <v>0</v>
@@ -10240,7 +10250,7 @@
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE (3ª FAIXA) DO TRECHO SERRA DO SALITRE - SALITRE DE MINAS, NA MG-230</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO MG-344 (ENTR. P/ CÁSSIA) - DIVISA MG/SP, NA MG-444, EXT. 23,9 KM</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -10266,7 +10276,7 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>34710000</v>
+        <v>59000000</v>
       </c>
       <c r="R145" t="n">
         <v>0</v>
@@ -10306,7 +10316,7 @@
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO MG-344 (ENTR. P/ CÁSSIA) - DIVISA MG/SP, NA MG-444, EXT. 23,9 KM</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO PARÁ DE MINAS - PAPAGAIOS (3ª FAIXA) - LOTE 1</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -10332,7 +10342,7 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>59000000</v>
+        <v>1000000</v>
       </c>
       <c r="R146" t="n">
         <v>0</v>
@@ -10372,7 +10382,7 @@
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO PARÁ DE MINAS - PAPAGAIOS (3ª FAIXA) - LOTE 1</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO: UNAÍ A GARAPUAVA</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -10438,7 +10448,7 @@
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO: UNAÍ A GARAPUAVA</t>
+          <t>RESTAURAÇÃO TIMÓTEO - ENTR. LMG-760 (CAVA GRANDE), NA MG-425</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -10464,7 +10474,7 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>1000000</v>
+        <v>200000</v>
       </c>
       <c r="R148" t="n">
         <v>0</v>
@@ -10504,7 +10514,7 @@
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TIMÓTEO - ENTR. LMG-760 (CAVA GRANDE), NA MG-425</t>
+          <t>RESTAURAÇÃO TRECHO ENTR. LMG764 (P/ MATUTINA) - SÃO GOTARDO, NA MG- 235 - 3ª FAIXA</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -10530,7 +10540,7 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="R149" t="n">
         <v>0</v>
@@ -10570,7 +10580,7 @@
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO ENTR. LMG764 (P/ MATUTINA) - SÃO GOTARDO, NA MG- 235 - 3ª FAIXA</t>
+          <t>RESTAURAÇÃO TRECHO ENTR. MGC-120 (B) (DONA EUZÉBIA) - ENTR. MGC-265, NA MG-285</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -10596,7 +10606,7 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>1000000</v>
+        <v>30980000</v>
       </c>
       <c r="R150" t="n">
         <v>0</v>
@@ -10636,7 +10646,7 @@
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO ENTR. MGC-120 (B) (DONA EUZÉBIA) - ENTR. MGC-265, NA MG-285</t>
+          <t>RESTAURAÇÃO TRECHO ENTR. MGC-265/MG-452 (P/ PAIVA) - ENTR. BR-040, NA MG-448</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -10662,7 +10672,7 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>30980000</v>
+        <v>25655000</v>
       </c>
       <c r="R151" t="n">
         <v>0</v>
@@ -10702,7 +10712,7 @@
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO ENTR. MGC-265/MG-452 (P/ PAIVA) - ENTR. BR-040, NA MG-448</t>
+          <t>RESTAURAÇÃO TRECHO PIRAÚBA (ENTR. MG-285) - PAIVA (ENTR. MG-488/MG-455), NA MG-265 E 3ª FAIXA</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -10728,7 +10738,7 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>25655000</v>
+        <v>66560000</v>
       </c>
       <c r="R152" t="n">
         <v>0</v>
@@ -10768,7 +10778,7 @@
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO PIRAÚBA (ENTR. MG-285) - PAIVA (ENTR. MG-488/MG-455), NA MG-265 E 3ª FAIXA</t>
+          <t>RESTAURAÇÃO TRECHO SÃO GOTARDO - ENTR. BR-354 (P/ PATOS DE MINAS), NA MG-235</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -10794,7 +10804,7 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>66560000</v>
+        <v>1000000</v>
       </c>
       <c r="R153" t="n">
         <v>0</v>
@@ -10834,7 +10844,7 @@
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO SÃO GOTARDO - ENTR. BR-354 (P/ PATOS DE MINAS), NA MG-235</t>
+          <t>RESTAURAÇÃO TRÊS PONTAS - VARGINHA, NA MG-167</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -10860,7 +10870,7 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>1000000</v>
+        <v>25464500</v>
       </c>
       <c r="R154" t="n">
         <v>0</v>
@@ -10886,7 +10896,7 @@
         <v>81</v>
       </c>
       <c r="E155" t="n">
-        <v>4268</v>
+        <v>4272</v>
       </c>
       <c r="F155" t="n">
         <v>1</v>
@@ -10900,7 +10910,7 @@
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRÊS PONTAS - VARGINHA, NA MG-167</t>
+          <t>BDCC 3X3 CÓRREGO CAVALO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -10926,7 +10936,7 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>25464500</v>
+        <v>100000</v>
       </c>
       <c r="R155" t="n">
         <v>0</v>
@@ -10966,7 +10976,7 @@
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
-          <t>BDCC 3X3 CÓRREGO CAVALO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
+          <t>COMPLEMENTAÇÃO DA CONSTRUÇÃO DA PONTE SOBRE O RIO SÃO FRANCISCO, PINTÓPOLIS</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -10992,7 +11002,7 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>100000</v>
+        <v>24000000</v>
       </c>
       <c r="R156" t="n">
         <v>0</v>
@@ -11032,7 +11042,7 @@
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO DA CONSTRUÇÃO DA PONTE SOBRE O RIO SÃO FRANCISCO, PINTÓPOLIS</t>
+          <t>ENCABEÇAMENTO E PONTE CÓRREGO SÃO BARTOLOMEU E ENCABEÇAMENTO CÓRREGO BARBADINHO, TRECHO CANABRAVA (JOÃO PINHEIRO) - ENTR. MG-181, NA LMG-698</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -11058,7 +11068,7 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>24000000</v>
+        <v>252000</v>
       </c>
       <c r="R157" t="n">
         <v>0</v>
@@ -11098,7 +11108,7 @@
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE CÓRREGO SÃO BARTOLOMEU E ENCABEÇAMENTO CÓRREGO BARBADINHO, TRECHO CANABRAVA (JOÃO PINHEIRO) - ENTR. MG-181, NA LMG-698</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO AMENDOIM, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -11124,7 +11134,7 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>252000</v>
+        <v>319200</v>
       </c>
       <c r="R158" t="n">
         <v>0</v>
@@ -11164,7 +11174,7 @@
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO AMENDOIM, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO BOI PRETO, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -11190,7 +11200,7 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>319200</v>
+        <v>495600</v>
       </c>
       <c r="R159" t="n">
         <v>0</v>
@@ -11230,7 +11240,7 @@
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO BOI PRETO, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O CÓRREGO DAS LAJES, TRECHO ENTR. MGC-479 (SERRA DAS ARARAS) - ENTR. MG-402, NA LMG-622</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -11256,7 +11266,7 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>495600</v>
+        <v>679000</v>
       </c>
       <c r="R160" t="n">
         <v>0</v>
@@ -11296,7 +11306,7 @@
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O CÓRREGO DAS LAJES, TRECHO ENTR. MGC-479 (SERRA DAS ARARAS) - ENTR. MG-402, NA LMG-622</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SANTO INÁCIO, TRECHO ENTR. MG-188 (COROMANDEL) - DISTRITO DE VEREDA, NA LMG-747</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -11322,7 +11332,7 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>679000</v>
+        <v>440000</v>
       </c>
       <c r="R161" t="n">
         <v>0</v>
@@ -11362,7 +11372,7 @@
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SANTO INÁCIO, TRECHO ENTR. MG-188 (COROMANDEL) - DISTRITO DE VEREDA, NA LMG-747</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SÃO JOÃO, TRECHO IGARATINGA - ENTR. MG-252, NA MG-430 (SEMI-INTEGRADA)</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -11388,7 +11398,7 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>440000</v>
+        <v>14920000</v>
       </c>
       <c r="R162" t="n">
         <v>0</v>
@@ -11428,7 +11438,7 @@
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SÃO JOÃO, TRECHO IGARATINGA - ENTR. MG-252, NA MG-430 (SEMI-INTEGRADA)</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SERRA BRANCA, TRECHO PAI PEDRO - CATUTI, NA MGC-122</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -11454,7 +11464,7 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>14920000</v>
+        <v>8798400</v>
       </c>
       <c r="R163" t="n">
         <v>0</v>
@@ -11494,7 +11504,7 @@
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SERRA BRANCA, TRECHO PAI PEDRO - CATUTI, NA MGC-122</t>
+          <t>ENCABEÇAMENTOS E PONTES SOBRE CÓRREGO VEREDINHA E RIBEIRÃO MARQUES, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -11520,7 +11530,7 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>8798400</v>
+        <v>369600</v>
       </c>
       <c r="R164" t="n">
         <v>0</v>
@@ -11560,7 +11570,7 @@
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTOS E PONTES SOBRE CÓRREGO VEREDINHA E RIBEIRÃO MARQUES, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
+          <t>LMG-722 (ROCHINHA A LAGAMAR, PONTE SOBRE O RIO PARANAÍBA)</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -11586,7 +11596,7 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>369600</v>
+        <v>1000000</v>
       </c>
       <c r="R165" t="n">
         <v>0</v>
@@ -11626,7 +11636,7 @@
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
-          <t>LMG-722 (ROCHINHA A LAGAMAR, PONTE SOBRE O RIO PARANAÍBA)</t>
+          <t>MGC-267 (CORDISLÂNDIA A CARVALHÓPOLIS, PONTE SOBRE O RIO SAPUCAÍ -  LOTE 01)</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -11652,7 +11662,7 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>1000000</v>
+        <v>1203643</v>
       </c>
       <c r="R166" t="n">
         <v>0</v>
@@ -11692,7 +11702,7 @@
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
-          <t>MGC-267 (CORDISLÂNDIA A CARVALHÓPOLIS, PONTE SOBRE O RIO SAPUCAÍ -  LOTE 01)</t>
+          <t>OLHOS D´AGUA DO OESTE A SANTA LUZIA DA SERRA - CÓRREGO SÃO BARTOLOMEU</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -11718,7 +11728,7 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>1203643</v>
+        <v>730000</v>
       </c>
       <c r="R167" t="n">
         <v>0</v>
@@ -11758,7 +11768,7 @@
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
-          <t>OLHOS D´AGUA DO OESTE A SANTA LUZIA DA SERRA - CÓRREGO SÃO BARTOLOMEU</t>
+          <t>PASSARELA MG-010 (CIDADE ADMINISTRATIVA)</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -11784,7 +11794,7 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>730000</v>
+        <v>66619</v>
       </c>
       <c r="R168" t="n">
         <v>0</v>
@@ -11824,7 +11834,7 @@
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
-          <t>PASSARELA MG-010 (CIDADE ADMINISTRATIVA)</t>
+          <t>PONTE CÓRREGO PERUAÇU, TRECHO CÔNEGO MARINHO - MIRAVÂNIA (RESERVA XACRIABÁ)</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -11850,7 +11860,7 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>66619</v>
+        <v>901000</v>
       </c>
       <c r="R169" t="n">
         <v>0</v>
@@ -11890,7 +11900,7 @@
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
-          <t>PONTE CÓRREGO PERUAÇU, TRECHO CÔNEGO MARINHO - MIRAVÂNIA (RESERVA XACRIABÁ)</t>
+          <t>PONTE CÓRREGO RIBEIRÃO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -11916,7 +11926,7 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>901000</v>
+        <v>100000</v>
       </c>
       <c r="R170" t="n">
         <v>0</v>
@@ -11956,7 +11966,7 @@
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
-          <t>PONTE CÓRREGO RIBEIRÃO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
+          <t>PONTE SOBRE O EXTRAVASOR DA CEMIG, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -11982,7 +11992,7 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>100000</v>
+        <v>170000</v>
       </c>
       <c r="R171" t="n">
         <v>0</v>
@@ -12022,7 +12032,7 @@
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O EXTRAVASOR DA CEMIG, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
+          <t>PONTE SOBRE O RIBEIRÃO MATA BOI NA RODOVIA MG-414, TRECHO ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -12048,7 +12058,7 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>170000</v>
+        <v>2940000</v>
       </c>
       <c r="R172" t="n">
         <v>0</v>
@@ -12088,7 +12098,7 @@
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIBEIRÃO MATA BOI NA RODOVIA MG-414, TRECHO ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO</t>
+          <t>PONTE SOBRE O RIBEIRÃO PANDEIROS, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -12114,7 +12124,7 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>2940000</v>
+        <v>810000</v>
       </c>
       <c r="R173" t="n">
         <v>0</v>
@@ -12154,7 +12164,7 @@
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIBEIRÃO PANDEIROS, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
+          <t>PONTE SOBRE O RIO ARAGUARI (TROCA DOS APARELHOS DE DO 1º E 5º VÃOS), TRECHO ENTR. MG-190 - ZELÂNDIA (USINA SANTA JULIANA), DIMENSÕES 130,00X12,20M, RODOVIA AMG-0730</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -12180,7 +12190,7 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>810000</v>
+        <v>542000</v>
       </c>
       <c r="R174" t="n">
         <v>0</v>
@@ -12220,7 +12230,7 @@
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIO ARAGUARI (TROCA DOS APARELHOS DE DO 1º E 5º VÃOS), TRECHO ENTR. MG-190 - ZELÂNDIA (USINA SANTA JULIANA), DIMENSÕES 130,00X12,20M, RODOVIA AMG-0730</t>
+          <t>PONTE SOBRE O RIO CORRENTE -  MG-460, NO TRECHO DE MUNHOZ - TOLEDO ( E SEMI-INTEGRADA)</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -12246,7 +12256,7 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>542000</v>
+        <v>2163814</v>
       </c>
       <c r="R175" t="n">
         <v>0</v>
@@ -12286,7 +12296,7 @@
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIO CORRENTE -  MG-460, NO TRECHO DE MUNHOZ - TOLEDO ( E SEMI-INTEGRADA)</t>
+          <t>PONTE SOBRE O RIO SÃO FRANCISCO - ENTR. MGC-135 (MANGA) ¿ PORTO DE MATIAS CARDOSO, NA RODOVIA MG-401</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -12312,7 +12322,7 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>2163814</v>
+        <v>25000000</v>
       </c>
       <c r="R176" t="n">
         <v>0</v>
@@ -12352,7 +12362,7 @@
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIO SÃO FRANCISCO - ENTR. MGC-135 (MANGA) ¿ PORTO DE MATIAS CARDOSO, NA RODOVIA MG-401</t>
+          <t>PONTES SOBRE OS RIOS SUAÇUI PEQUENO I E II, TRECHO PEÇANHA - COROACI, NA MG-314</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -12378,7 +12388,7 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>25000000</v>
+        <v>500000</v>
       </c>
       <c r="R177" t="n">
         <v>0</v>
@@ -12418,7 +12428,7 @@
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
-          <t>PONTES SOBRE OS RIOS SUAÇUI PEQUENO I E II, TRECHO PEÇANHA - COROACI, NA MG-314</t>
+          <t>RECUPERAÇÃO DA PONTE S/ O RIO JEQUITINHONHA- DIAMANTINA - COUTO MAGALHÃES.</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -12444,7 +12454,7 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>500000</v>
+        <v>1382535</v>
       </c>
       <c r="R178" t="n">
         <v>0</v>
@@ -12484,7 +12494,7 @@
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO DA PONTE S/ O RIO JEQUITINHONHA- DIAMANTINA - COUTO MAGALHÃES.</t>
+          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -12510,7 +12520,7 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>1382535</v>
+        <v>1000000</v>
       </c>
       <c r="R179" t="n">
         <v>0</v>
@@ -12550,7 +12560,7 @@
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
+          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO (ENTR. MG-408) - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -12576,7 +12586,7 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>1000000</v>
+        <v>900000</v>
       </c>
       <c r="R180" t="n">
         <v>0</v>
@@ -12616,7 +12626,7 @@
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO (ENTR. MG-408) - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
+          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO DAS ARARAS I, TRECHO GUANHÃES - SÃO PEDRO DO SUAÇUÍ, NA CMG-120</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -12642,7 +12652,7 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>900000</v>
+        <v>168000</v>
       </c>
       <c r="R181" t="n">
         <v>0</v>
@@ -12682,7 +12692,7 @@
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
-          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO DAS ARARAS I, TRECHO GUANHÃES - SÃO PEDRO DO SUAÇUÍ, NA CMG-120</t>
+          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO MACAÚBAS, TRECHO SANTA LUZIA - JABOTICATUBAS, MG-020</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -12708,7 +12718,7 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>168000</v>
+        <v>249000</v>
       </c>
       <c r="R182" t="n">
         <v>0</v>
@@ -12748,7 +12758,7 @@
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
-          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO MACAÚBAS, TRECHO SANTA LUZIA - JABOTICATUBAS, MG-020</t>
+          <t>REFORÇO DA FUNDAÇÃO DO VIADUTO II NA PISTA DIREITA DA INTERSEÇÃO 3 (ACESSO AO INHOTIM, ESTACA 138)</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -12774,7 +12784,7 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>249000</v>
+        <v>705000</v>
       </c>
       <c r="R183" t="n">
         <v>0</v>
@@ -12814,7 +12824,7 @@
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
-          <t>REFORÇO DA FUNDAÇÃO DO VIADUTO II NA PISTA DIREITA DA INTERSEÇÃO 3 (ACESSO AO INHOTIM, ESTACA 138)</t>
+          <t>REFORÇO DE FUNDAÇÃO CÓRREGO DOIDOS, TRECHO SÃO FRANCISCO DE PAULA - ENTR. BR-354</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -12840,7 +12850,7 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>705000</v>
+        <v>58800</v>
       </c>
       <c r="R184" t="n">
         <v>0</v>
@@ -12880,7 +12890,7 @@
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
-          <t>REFORÇO DE FUNDAÇÃO CÓRREGO DOIDOS, TRECHO SÃO FRANCISCO DE PAULA - ENTR. BR-354</t>
+          <t>REFORÇO NA FUNDAÇÃO DA PONTE SOBRE O RIO VERMELHO, TRECHO SANTA BÁRBARA - CATAS ALTAS, NA MG-129</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -12906,7 +12916,7 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>58800</v>
+        <v>725000</v>
       </c>
       <c r="R185" t="n">
         <v>0</v>
@@ -12932,7 +12942,7 @@
         <v>81</v>
       </c>
       <c r="E186" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F186" t="n">
         <v>1</v>
@@ -12946,7 +12956,7 @@
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
-          <t>REFORÇO NA FUNDAÇÃO DA PONTE SOBRE O RIO VERMELHO, TRECHO SANTA BÁRBARA - CATAS ALTAS, NA MG-129</t>
+          <t>PAVIMENTAÇÃO MG-326 (PONTE NOVA A BARRA LONGA)</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -12972,10 +12982,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>725000</v>
+        <v>0</v>
       </c>
       <c r="R186" t="n">
-        <v>0</v>
+        <v>82286728</v>
       </c>
       <c r="S186" t="inlineStr"/>
       <c r="T186" t="inlineStr"/>
@@ -13012,7 +13022,7 @@
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
-          <t>PAVIMENTAÇÃO MG-326 (PONTE NOVA A BARRA LONGA)</t>
+          <t>PAVIMENTAÇÃO DA MG-314 (ENTR. MG-416 (PEÇANHA) A LMG-744 (COROACI) ENTR. VIRGOLÂNDIA)</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -13041,7 +13051,7 @@
         <v>0</v>
       </c>
       <c r="R187" t="n">
-        <v>82286728</v>
+        <v>22137718</v>
       </c>
       <c r="S187" t="inlineStr"/>
       <c r="T187" t="inlineStr"/>
@@ -13078,7 +13088,7 @@
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr">
         <is>
-          <t>PAVIMENTAÇÃO DA MG-314 (ENTR. MG-416 (PEÇANHA) A LMG-744 (COROACI) ENTR. VIRGOLÂNDIA)</t>
+          <t>PAVIMENTAÇÃO DA RODOVIA MUNICIPAL (SANTA RITA DO ITUETO A ENTR. BR-259 (RESPLENDOR))</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -13107,7 +13117,7 @@
         <v>0</v>
       </c>
       <c r="R188" t="n">
-        <v>22137718</v>
+        <v>21757581</v>
       </c>
       <c r="S188" t="inlineStr"/>
       <c r="T188" t="inlineStr"/>
@@ -13144,7 +13154,7 @@
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
-          <t>PAVIMENTAÇÃO DA RODOVIA MUNICIPAL (SANTA RITA DO ITUETO A ENTR. BR-259 (RESPLENDOR))</t>
+          <t>RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 21,80 KM</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -13173,7 +13183,7 @@
         <v>0</v>
       </c>
       <c r="R189" t="n">
-        <v>21757581</v>
+        <v>8036364</v>
       </c>
       <c r="S189" t="inlineStr"/>
       <c r="T189" t="inlineStr"/>
@@ -13210,7 +13220,7 @@
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
-          <t>RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 21,80 KM</t>
+          <t>TRECHO ENTRº LMG-690 (PARACATU) - ENTRº ENTRE RIBEIROS (DISTRITO) - ENTRº MG-181 (ESTACA 1250 A 2000)</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -13239,7 +13249,7 @@
         <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>8036364</v>
+        <v>14063636</v>
       </c>
       <c r="S190" t="inlineStr"/>
       <c r="T190" t="inlineStr"/>
@@ -13276,7 +13286,7 @@
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
-          <t>TRECHO ENTRº LMG-690 (PARACATU) - ENTRº ENTRE RIBEIROS (DISTRITO) - ENTRº MG-181 (ESTACA 1250 A 2000)</t>
+          <t>RODOVIA MG-10 - TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 22,50 KM</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -13305,7 +13315,7 @@
         <v>0</v>
       </c>
       <c r="R191" t="n">
-        <v>14063636</v>
+        <v>8100000</v>
       </c>
       <c r="S191" t="inlineStr"/>
       <c r="T191" t="inlineStr"/>
@@ -13342,7 +13352,7 @@
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
-          <t>RODOVIA MG-10 - TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 22,50 KM</t>
+          <t>MELHORAMENTO E PAVIMENTAÇÃO DO CONTORNO DE ANDRADAS</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -13371,7 +13381,7 @@
         <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>8100000</v>
+        <v>4804860</v>
       </c>
       <c r="S192" t="inlineStr"/>
       <c r="T192" t="inlineStr"/>
@@ -13408,7 +13418,7 @@
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
-          <t>MELHORAMENTO E PAVIMENTAÇÃO DO CONTORNO DE ANDRADAS</t>
+          <t>EMPREENDIMENTO EM DEFINIÇÃO JUNTO AO BANCO DO BRASIL - CONTRATO DE FINANCIAMENTO Nº 20/00020-0 (PDMG)</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -13437,7 +13447,7 @@
         <v>0</v>
       </c>
       <c r="R193" t="n">
-        <v>4804860</v>
+        <v>6000001</v>
       </c>
       <c r="S193" t="inlineStr"/>
       <c r="T193" t="inlineStr"/>
@@ -13474,7 +13484,7 @@
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
-          <t>EMPREENDIMENTO EM DEFINIÇÃO JUNTO AO BANCO DO BRASIL - CONTRATO DE FINANCIAMENTO Nº 20/00020-0 (PDMG)</t>
+          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - (LOTE 1), SEGMENTO 1 (0 A 835), 16,70 KM E SEGMENTO 2 (835 A 1250), 8,30 KM</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -13500,10 +13510,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>0</v>
+        <v>11326937</v>
       </c>
       <c r="R194" t="n">
-        <v>6000001</v>
+        <v>0</v>
       </c>
       <c r="S194" t="inlineStr"/>
       <c r="T194" t="inlineStr"/>
@@ -13540,7 +13550,7 @@
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - (LOTE 1), SEGMENTO 1 (0 A 835), 16,70 KM E SEGMENTO 2 (835 A 1250), 8,30 KM</t>
+          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - ESTACA 2550 A 3281</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -13566,7 +13576,7 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>11326937</v>
+        <v>19000000</v>
       </c>
       <c r="R195" t="n">
         <v>0</v>
@@ -13606,7 +13616,7 @@
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - ESTACA 2550 A 3281</t>
+          <t>COMPLEMENTO S JANUÁRIA - PANDEIROS, NA RODOVIA MGC-479</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -13632,7 +13642,7 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>19000000</v>
+        <v>74941120</v>
       </c>
       <c r="R196" t="n">
         <v>0</v>
@@ -13672,7 +13682,7 @@
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
-          <t>COMPLEMENTO S JANUÁRIA - PANDEIROS, NA RODOVIA MGC-479</t>
+          <t>CONTORNO DE ANDRADAS (COMPLEMENTAÇÃO) - LOTE 01</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -13698,7 +13708,7 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>74941120</v>
+        <v>38460000</v>
       </c>
       <c r="R197" t="n">
         <v>0</v>
@@ -13738,7 +13748,7 @@
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
-          <t>CONTORNO DE ANDRADAS (COMPLEMENTAÇÃO) - LOTE 01</t>
+          <t>ENTR. MG-181 (BRASILÂNDIA DE MINAS) - ENTR. BR-365 (BURITIZEIRO), NA MG-408 - LOTE 01</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -13764,7 +13774,7 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>38460000</v>
+        <v>1000000</v>
       </c>
       <c r="R198" t="n">
         <v>0</v>
@@ -13804,7 +13814,7 @@
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
-          <t>ENTR. MG-181 (BRASILÂNDIA DE MINAS) - ENTR. BR-365 (BURITIZEIRO), NA MG-408 - LOTE 01</t>
+          <t>IBERTIOGA - PIEDADE DO RIO GRANDE, NA RODOVIA MG-338</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -13830,7 +13840,7 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>1000000</v>
+        <v>7000000</v>
       </c>
       <c r="R199" t="n">
         <v>0</v>
@@ -13870,7 +13880,7 @@
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
-          <t>IBERTIOGA - PIEDADE DO RIO GRANDE, NA RODOVIA MG-338</t>
+          <t>INTERSEÇÃO DE ACESSO A COUTO DE MAGALHÃES DE MINAS, NA MGC-367</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -13896,7 +13906,7 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>7000000</v>
+        <v>1000000</v>
       </c>
       <c r="R200" t="n">
         <v>0</v>
@@ -13936,7 +13946,7 @@
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
-          <t>INTERSEÇÃO DE ACESSO A COUTO DE MAGALHÃES DE MINAS, NA MGC-367</t>
+          <t>ITAPAGIPE - ENTR. BR-364 (CAMPINA VERDE), RODOVIA MGC-154</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -13962,7 +13972,7 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>1000000</v>
+        <v>6121131</v>
       </c>
       <c r="R201" t="n">
         <v>0</v>
@@ -14002,7 +14012,7 @@
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
-          <t>ITAPAGIPE - ENTR. BR-364 (CAMPINA VERDE), RODOVIA MGC-154</t>
+          <t>MG-631 - SÃO JOÃO DA PONTE A CAPITÃO ENÉAS</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -14028,7 +14038,7 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>6121131</v>
+        <v>1000000</v>
       </c>
       <c r="R202" t="n">
         <v>0</v>
@@ -14068,7 +14078,7 @@
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
-          <t>MG-631 - SÃO JOÃO DA PONTE A CAPITÃO ENÉAS</t>
+          <t>MELHORAMENTO E PAVIMENTAÇÃO DA RODOVIA LMG-706, SEGMENTO 01: ENTR. BR-040 - VARIANTE (PONTE RIO ESCURO); SEGMENTO 02: VAZAMOR - VAZANTE; SEGMENTO 03: CONTORNO DE VAZANTE - ENTR. BR-354</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -14134,7 +14144,7 @@
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
-          <t>MELHORAMENTO E PAVIMENTAÇÃO DA RODOVIA LMG-706, SEGMENTO 01: ENTR. BR-040 - VARIANTE (PONTE RIO ESCURO); SEGMENTO 02: VAZAMOR - VAZANTE; SEGMENTO 03: CONTORNO DE VAZANTE - ENTR. BR-354</t>
+          <t>ACESSO AO PRESÍDIO DE ITURAMA</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -14200,7 +14210,7 @@
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
-          <t>ACESSO AO PRESÍDIO DE ITURAMA</t>
+          <t>MONTE CARMELO (ENTR. MG-190) - ENTR. LMG-742 (CHAPADA DE MINAS P/ GRUPIARA), NA LMG-746 - LOTE 01 9,50 KM</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -14266,7 +14276,7 @@
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
-          <t>MONTE CARMELO (ENTR. MG-190) - ENTR. LMG-742 (CHAPADA DE MINAS P/ GRUPIARA), NA LMG-746 - LOTE 01 9,50 KM</t>
+          <t>MONTE CARMELO A CHAPADA DE MINAS - LOTE 2</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -14332,7 +14342,7 @@
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
-          <t>MONTE CARMELO A CHAPADA DE MINAS - LOTE 2</t>
+          <t>NATALÂNDIA - ENTR. BR-251, NA LMG-622</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -14398,7 +14408,7 @@
       <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr">
         <is>
-          <t>NATALÂNDIA - ENTR. BR-251, NA LMG-622</t>
+          <t>PEÇANHA (ENTR. MG-416) - LMG-744 (COROACI), NA MG-314</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -14424,7 +14434,7 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>1000000</v>
+        <v>431808</v>
       </c>
       <c r="R208" t="n">
         <v>0</v>
@@ -14464,7 +14474,7 @@
       <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr">
         <is>
-          <t>PEÇANHA (ENTR. MG-416) - LMG-744 (COROACI), NA MG-314</t>
+          <t>PEDRA AZUL (ENTR. MG-105) - DISTRITO DE PEDRA GRANDE - ALMENARA, MG-251/MG-406, LOTE 01 35 KM</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -14490,7 +14500,7 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>431808</v>
+        <v>1000000</v>
       </c>
       <c r="R209" t="n">
         <v>0</v>
@@ -14530,7 +14540,7 @@
       <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
-          <t>PEDRA AZUL (ENTR. MG-105) - DISTRITO DE PEDRA GRANDE - ALMENARA, MG-251/MG-406, LOTE 01 35 KM</t>
+          <t>PEDRA BONITA - ENTR. BR-116 E INTERSEÇÃO ENTR. BR-116 (COMPLEMENTAÇÃO), RODOVIA LMG-840</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -14596,7 +14606,7 @@
       <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
-          <t>PEDRA BONITA - ENTR. BR-116 E INTERSEÇÃO ENTR. BR-116 (COMPLEMENTAÇÃO), RODOVIA LMG-840</t>
+          <t>PRESIDENTE OLEGÁRIO - GALENA, NA LMG-726</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -14662,7 +14672,7 @@
       <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr">
         <is>
-          <t>PRESIDENTE OLEGÁRIO - GALENA, NA LMG-726</t>
+          <t>SANTA RITA DO ITUETO - ENTR. BR-259 (RESPLENDOR) (COMPLEMENTAÇÃO), MUNICIPAL AMG-2320</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -14688,7 +14698,7 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>1000000</v>
+        <v>14356788</v>
       </c>
       <c r="R212" t="n">
         <v>0</v>
@@ -14728,7 +14738,7 @@
       <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
-          <t>SANTA RITA DO ITUETO - ENTR. BR-259 (RESPLENDOR) (COMPLEMENTAÇÃO), MUNICIPAL AMG-2320</t>
+          <t>SÃO DOMINGOS DO PRATA - DOM SILVÉRIO, NA MGC-120</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -14754,7 +14764,7 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>14356788</v>
+        <v>100000</v>
       </c>
       <c r="R213" t="n">
         <v>0</v>
@@ -14794,7 +14804,7 @@
       <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
-          <t>SÃO DOMINGOS DO PRATA - DOM SILVÉRIO, NA MGC-120</t>
+          <t>UNAÍ (ENTR. BR-251) - PARACATU (ENTR. BR-040) (ESTRADA DO MUNDO NOVO), NA LMG-658 - LOTE 01</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -14820,7 +14830,7 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>100000</v>
+        <v>1000000</v>
       </c>
       <c r="R214" t="n">
         <v>0</v>
@@ -14860,7 +14870,7 @@
       <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr">
         <is>
-          <t>UNAÍ (ENTR. BR-251) - PARACATU (ENTR. BR-040) (ESTRADA DO MUNDO NOVO), NA LMG-658 - LOTE 01</t>
+          <t>ARAÇAÍ - SETE LAGOAS, RODOVIA MUNICIPAL</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -14886,7 +14896,7 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>1000000</v>
+        <v>35359852</v>
       </c>
       <c r="R215" t="n">
         <v>0</v>
@@ -14926,7 +14936,7 @@
       <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
-          <t>ARAÇAÍ - SETE LAGOAS, RODOVIA MUNICIPAL</t>
+          <t>ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO, NA MG-414</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -14952,7 +14962,7 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>35359852</v>
+        <v>29030000</v>
       </c>
       <c r="R216" t="n">
         <v>0</v>
@@ -14992,7 +15002,7 @@
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
-          <t>ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO, NA MG-414</t>
+          <t>CAMPO VERDE (DISTRITO E NOVORIZONTE) - FRUTA DE LEITE, NA LMG-626 (LOTE 01 TSD)</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -15018,7 +15028,7 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>29030000</v>
+        <v>1000000</v>
       </c>
       <c r="R217" t="n">
         <v>0</v>
@@ -15058,7 +15068,7 @@
       <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
-          <t>CAMPO VERDE (DISTRITO E NOVORIZONTE) - FRUTA DE LEITE, NA LMG-626 (LOTE 01 TSD)</t>
+          <t>JABOTICATUBAS - LAGOA SANTA, RODOVIA MUNICIPAL - LOTE 01</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -15084,7 +15094,7 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>1000000</v>
+        <v>3541727</v>
       </c>
       <c r="R218" t="n">
         <v>0</v>
@@ -15124,7 +15134,7 @@
       <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr">
         <is>
-          <t>JABOTICATUBAS - LAGOA SANTA, RODOVIA MUNICIPAL - LOTE 01</t>
+          <t xml:space="preserve">LMG-629 (RIO PARDO DE MINAS A ENTRº LMG-635) - LOTE 2 </t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -15150,7 +15160,7 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>3541727</v>
+        <v>31280000</v>
       </c>
       <c r="R219" t="n">
         <v>0</v>
@@ -15176,7 +15186,7 @@
         <v>81</v>
       </c>
       <c r="E220" t="n">
-        <v>4275</v>
+        <v>4287</v>
       </c>
       <c r="F220" t="n">
         <v>1</v>
@@ -15190,7 +15200,7 @@
       <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
-          <t xml:space="preserve">LMG-629 (RIO PARDO DE MINAS A ENTRº LMG-635) - LOTE 2 </t>
+          <t>Empreendimentos do Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -15216,7 +15226,7 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>31280000</v>
+        <v>1000</v>
       </c>
       <c r="R220" t="n">
         <v>0</v>
@@ -15242,7 +15252,7 @@
         <v>81</v>
       </c>
       <c r="E221" t="n">
-        <v>4287</v>
+        <v>4289</v>
       </c>
       <c r="F221" t="n">
         <v>1</v>
@@ -15256,7 +15266,7 @@
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Empreendimentos do Acordo Judicial do Rio Doce</t>
+          <t>Empreendimentos do Acordo Judicial de Brumadinho</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -15308,7 +15318,7 @@
         <v>81</v>
       </c>
       <c r="E222" t="n">
-        <v>4289</v>
+        <v>4293</v>
       </c>
       <c r="F222" t="n">
         <v>1</v>
@@ -15322,7 +15332,7 @@
       <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Empreendimentos do Acordo Judicial de Brumadinho</t>
+          <t>PROGRAMA DE MICRORREVESTIMENTO ASFÁLTICO</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -15348,7 +15358,7 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>1000</v>
+        <v>10000000</v>
       </c>
       <c r="R222" t="n">
         <v>0</v>
@@ -15388,7 +15398,7 @@
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
-          <t>PROGRAMA DE MICRORREVESTIMENTO ASFÁLTICO</t>
+          <t>REALINHAMENTO DE PREÇOS DO FORNECIMENTO DO MATERIAL BETUMINOSO</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -15414,7 +15424,7 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>10000000</v>
+        <v>1406178</v>
       </c>
       <c r="R223" t="n">
         <v>0</v>
@@ -15454,7 +15464,7 @@
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr">
         <is>
-          <t>REALINHAMENTO DE PREÇOS DO FORNECIMENTO DO MATERIAL BETUMINOSO</t>
+          <t>04ª URG BARBACENA</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -15480,10 +15490,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>1406178</v>
+        <v>0</v>
       </c>
       <c r="R224" t="n">
-        <v>0</v>
+        <v>12870000</v>
       </c>
       <c r="S224" t="inlineStr"/>
       <c r="T224" t="inlineStr"/>
@@ -15520,7 +15530,7 @@
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr">
         <is>
-          <t>04ª URG BARBACENA</t>
+          <t>20ª URG FORMIGA</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -15586,7 +15596,7 @@
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
-          <t>20ª URG FORMIGA</t>
+          <t>28ª URG TEÓFILO OTONI</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -15615,7 +15625,7 @@
         <v>0</v>
       </c>
       <c r="R226" t="n">
-        <v>12870000</v>
+        <v>9575065</v>
       </c>
       <c r="S226" t="inlineStr"/>
       <c r="T226" t="inlineStr"/>
@@ -15652,7 +15662,7 @@
       <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr">
         <is>
-          <t>28ª URG TEÓFILO OTONI</t>
+          <t>30ª URG JUIZ DE FORA</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -15681,7 +15691,7 @@
         <v>0</v>
       </c>
       <c r="R227" t="n">
-        <v>9575065</v>
+        <v>12375000</v>
       </c>
       <c r="S227" t="inlineStr"/>
       <c r="T227" t="inlineStr"/>
@@ -15718,7 +15728,7 @@
       <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
-          <t>30ª URG JUIZ DE FORA</t>
+          <t>01ª URG BELO HORIZONTE - SUL</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -15747,7 +15757,7 @@
         <v>0</v>
       </c>
       <c r="R228" t="n">
-        <v>12375000</v>
+        <v>14850000</v>
       </c>
       <c r="S228" t="inlineStr"/>
       <c r="T228" t="inlineStr"/>
@@ -15784,7 +15794,7 @@
       <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
-          <t>01ª URG BELO HORIZONTE - SUL</t>
+          <t>01ª URG BELO HORIZONTE - NORTE</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -15850,7 +15860,7 @@
       <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr">
         <is>
-          <t>01ª URG BELO HORIZONTE - NORTE</t>
+          <t>31ª URG ITUIUTABA</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -15879,7 +15889,7 @@
         <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>14850000</v>
+        <v>9900000</v>
       </c>
       <c r="S230" t="inlineStr"/>
       <c r="T230" t="inlineStr"/>
@@ -15916,7 +15926,7 @@
       <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr">
         <is>
-          <t>31ª URG ITUIUTABA</t>
+          <t>CONSERVAÇÃO DA MALHA VIÁRIA DAS 40ª URG`S</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -15942,10 +15952,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>0</v>
+        <v>654124898</v>
       </c>
       <c r="R231" t="n">
-        <v>9900000</v>
+        <v>0</v>
       </c>
       <c r="S231" t="inlineStr"/>
       <c r="T231" t="inlineStr"/>
@@ -15982,7 +15992,7 @@
       <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr">
         <is>
-          <t>CONSERVAÇÃO DA MALHA VIÁRIA DAS 40ª URG`S</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA EXECUÇÃO DE SERVIÇOS DE NATUREZA CONTÍNUA DE SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, EM REGIME DE EMPREITADA POR PREÇO UNITÁRIO, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -16008,7 +16018,7 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>654124898</v>
+        <v>30767861</v>
       </c>
       <c r="R232" t="n">
         <v>0</v>
@@ -16048,7 +16058,7 @@
       <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA EXECUÇÃO DE SERVIÇOS DE NATUREZA CONTÍNUA DE SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, EM REGIME DE EMPREITADA POR PREÇO UNITÁRIO, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE</t>
+          <t>MANUTENÇÃO LINHA VERDE E COMPLEXO CIDADE ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -16074,7 +16084,7 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>30767861</v>
+        <v>19976964</v>
       </c>
       <c r="R233" t="n">
         <v>0</v>
@@ -16114,7 +16124,7 @@
       <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO LINHA VERDE E COMPLEXO CIDADE ADMINISTRATIVA</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 1</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -16140,7 +16150,7 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>19976964</v>
+        <v>12895888</v>
       </c>
       <c r="R234" t="n">
         <v>0</v>
@@ -16180,7 +16190,7 @@
       <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 1</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 2</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -16206,7 +16216,7 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>12895888</v>
+        <v>11846334</v>
       </c>
       <c r="R235" t="n">
         <v>0</v>
@@ -16246,7 +16256,7 @@
       <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 2</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 3</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -16272,7 +16282,7 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>11846334</v>
+        <v>15201174</v>
       </c>
       <c r="R236" t="n">
         <v>0</v>
@@ -16312,7 +16322,7 @@
       <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 3</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 4</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -16338,7 +16348,7 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>15201174</v>
+        <v>12921920</v>
       </c>
       <c r="R237" t="n">
         <v>0</v>
@@ -16364,7 +16374,7 @@
         <v>81</v>
       </c>
       <c r="E238" t="n">
-        <v>4293</v>
+        <v>4385</v>
       </c>
       <c r="F238" t="n">
         <v>1</v>
@@ -16378,7 +16388,7 @@
       <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 4</t>
+          <t>RECUPERAÇÃO FUNCIONAL MG-232 (BRAÚNAS (DIV. 40ª/ 2ª) - IPATINGA)</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -16404,7 +16414,7 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>12921920</v>
+        <v>6382601</v>
       </c>
       <c r="R238" t="n">
         <v>0</v>
@@ -16444,7 +16454,7 @@
       <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO FUNCIONAL MG-232 (BRAÚNAS (DIV. 40ª/ 2ª) - IPATINGA)</t>
+          <t>RECUPERAÇÃO FUNCIONAL MGC-259 ( SABINÓPOLIS - SERRO, GUANHÃES - SABINÓPOLIS E ALVORADA MINAS - SERRO) *</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -16470,7 +16480,7 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>6382601</v>
+        <v>30000000</v>
       </c>
       <c r="R239" t="n">
         <v>0</v>
@@ -16510,7 +16520,7 @@
       <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO FUNCIONAL MGC-259 ( SABINÓPOLIS - SERRO, GUANHÃES - SABINÓPOLIS E ALVORADA MINAS - SERRO) *</t>
+          <t>RECUPERAÇÃO FUNCIONAL MGC-455 (PIRAJUBA - ENTRº BR-364 (PLANURA)</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -16536,7 +16546,7 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>30000000</v>
+        <v>4000000</v>
       </c>
       <c r="R240" t="n">
         <v>0</v>
@@ -16559,10 +16569,10 @@
         <v>782</v>
       </c>
       <c r="D241" t="n">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="E241" t="n">
-        <v>4385</v>
+        <v>4280</v>
       </c>
       <c r="F241" t="n">
         <v>1</v>
@@ -16576,7 +16586,7 @@
       <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO FUNCIONAL MGC-455 (PIRAJUBA - ENTRº BR-364 (PLANURA)</t>
+          <t>PONTO CRÍTICO: ENTRº BR-040 (BARREIRA DOTRIUNFO) - ENTRº MG-353 (GOIANÁ)</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -16642,7 +16652,7 @@
       <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: ENTRº BR-040 (BARREIRA DOTRIUNFO) - ENTRº MG-353 (GOIANÁ)</t>
+          <t>PONTO CRÍTICO: ENTRº MGC-265 (RIO POMBA) - PONTE RIO POMBA</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -16668,7 +16678,7 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>4000000</v>
+        <v>470000</v>
       </c>
       <c r="R242" t="n">
         <v>0</v>
@@ -16708,7 +16718,7 @@
       <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: ENTRº MGC-265 (RIO POMBA) - PONTE RIO POMBA</t>
+          <t>PONTO CRÍTICO: ENTRº P/ MARIA DA FÉ - INÍCIO DO PERÍMETRO URBANO DE ITAJUBÁ (2  PONTOS)</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -16734,7 +16744,7 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>470000</v>
+        <v>4000000</v>
       </c>
       <c r="R243" t="n">
         <v>0</v>
@@ -16774,7 +16784,7 @@
       <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: ENTRº P/ MARIA DA FÉ - INÍCIO DO PERÍMETRO URBANO DE ITAJUBÁ (2  PONTOS)</t>
+          <t>PONTO CRÍTICO: PALMÓPOLIS - RIO DO PRADO (6 PONTOS)/ PONTE SOBRE O RIBEIRÃO JOSÉ FERREIRA (1 PONTO)</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -16800,7 +16810,7 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>4000000</v>
+        <v>1000000</v>
       </c>
       <c r="R244" t="n">
         <v>0</v>
@@ -16840,7 +16850,7 @@
       <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: PALMÓPOLIS - RIO DO PRADO (6 PONTOS)/ PONTE SOBRE O RIBEIRÃO JOSÉ FERREIRA (1 PONTO)</t>
+          <t>PONTO CRÍTICO: RODEIRO - ENTRº MG-285</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -16866,7 +16876,7 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>1000000</v>
+        <v>420000</v>
       </c>
       <c r="R245" t="n">
         <v>0</v>
@@ -16906,7 +16916,7 @@
       <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: RODEIRO - ENTRº MG-285</t>
+          <t>PONTO CRÍTICO: SABARÁ-CAETÉ (3 PONTOS)</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -16932,7 +16942,7 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>420000</v>
+        <v>790000</v>
       </c>
       <c r="R246" t="n">
         <v>0</v>
@@ -16946,19 +16956,19 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>2301</v>
+        <v>2311</v>
       </c>
       <c r="B247" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C247" t="n">
-        <v>782</v>
+        <v>363</v>
       </c>
       <c r="D247" t="n">
-        <v>139</v>
+        <v>7</v>
       </c>
       <c r="E247" t="n">
-        <v>4280</v>
+        <v>4006</v>
       </c>
       <c r="F247" t="n">
         <v>1</v>
@@ -16972,33 +16982,39 @@
       <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: SABARÁ-CAETÉ (3 PONTOS)</t>
+          <t>Construção da escola do Brasil Profissionalizado no município de Unaí-MG</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L247" t="inlineStr"/>
-      <c r="M247" t="inlineStr"/>
+          <t>PARALISADO</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>METRO QUADRADO</t>
+        </is>
+      </c>
+      <c r="M247" t="n">
+        <v>5000</v>
+      </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>UNAÍ</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>790000</v>
+        <v>5000000</v>
       </c>
       <c r="R247" t="n">
         <v>0</v>
@@ -17012,19 +17028,19 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>2311</v>
+        <v>2321</v>
       </c>
       <c r="B248" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C248" t="n">
-        <v>363</v>
+        <v>302</v>
       </c>
       <c r="D248" t="n">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="E248" t="n">
-        <v>4006</v>
+        <v>4222</v>
       </c>
       <c r="F248" t="n">
         <v>1</v>
@@ -17038,39 +17054,33 @@
       <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Construção da escola do Brasil Profissionalizado no município de Unaí-MG</t>
+          <t xml:space="preserve">Projetos em unidade diversas </t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
-        </is>
-      </c>
-      <c r="L248" t="inlineStr">
-        <is>
-          <t>METRO QUADRADO</t>
-        </is>
-      </c>
-      <c r="M248" t="n">
-        <v>5000</v>
-      </c>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr"/>
       <c r="N248" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>UNAÍ</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>5000000</v>
+        <v>800291</v>
       </c>
       <c r="R248" t="n">
         <v>0</v>
@@ -17132,11 +17142,11 @@
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>800291</v>
+        <v>174673</v>
       </c>
       <c r="R249" t="n">
         <v>0</v>
@@ -17173,15 +17183,17 @@
       <c r="H250" t="n">
         <v>249</v>
       </c>
-      <c r="I250" t="inlineStr"/>
+      <c r="I250" t="n">
+        <v>11877</v>
+      </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Projetos em unidade diversas </t>
+          <t>Contrato a obra de reforma e ampliação</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L250" t="inlineStr"/>
@@ -17193,16 +17205,16 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Barbacena</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>SÃO JOÃO DEL REI</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>174673</v>
+        <v>1088908</v>
       </c>
       <c r="R250" t="n">
         <v>0</v>
@@ -17216,19 +17228,19 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>2321</v>
+        <v>2361</v>
       </c>
       <c r="B251" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C251" t="n">
-        <v>302</v>
+        <v>846</v>
       </c>
       <c r="D251" t="n">
-        <v>87</v>
+        <v>705</v>
       </c>
       <c r="E251" t="n">
-        <v>4222</v>
+        <v>7004</v>
       </c>
       <c r="F251" t="n">
         <v>1</v>
@@ -17239,12 +17251,10 @@
       <c r="H251" t="n">
         <v>250</v>
       </c>
-      <c r="I251" t="n">
-        <v>11877</v>
-      </c>
+      <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Contrato a obra de reforma e ampliação</t>
+          <t>Possível adequação da sede</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -17259,22 +17269,10 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="O251" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Barbacena</t>
-        </is>
-      </c>
-      <c r="P251" t="inlineStr">
-        <is>
-          <t>SÃO JOÃO DEL REI</t>
-        </is>
-      </c>
-      <c r="Q251" t="n">
-        <v>1088908</v>
-      </c>
-      <c r="R251" t="n">
-        <v>0</v>
-      </c>
+      <c r="O251" t="inlineStr"/>
+      <c r="P251" t="inlineStr"/>
+      <c r="Q251" t="inlineStr"/>
+      <c r="R251" t="inlineStr"/>
       <c r="S251" t="inlineStr"/>
       <c r="T251" t="inlineStr"/>
       <c r="U251" t="inlineStr"/>
@@ -17287,16 +17285,16 @@
         <v>2361</v>
       </c>
       <c r="B252" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C252" t="n">
-        <v>846</v>
+        <v>274</v>
       </c>
       <c r="D252" t="n">
-        <v>705</v>
+        <v>766</v>
       </c>
       <c r="E252" t="n">
-        <v>7004</v>
+        <v>2113</v>
       </c>
       <c r="F252" t="n">
         <v>1</v>
@@ -17347,10 +17345,10 @@
         <v>274</v>
       </c>
       <c r="D253" t="n">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="E253" t="n">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="F253" t="n">
         <v>1</v>
@@ -17364,7 +17362,7 @@
       <c r="I253" t="inlineStr"/>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Possível adequação da sede</t>
+          <t>Possível obras de adequação da sede.</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
@@ -17379,10 +17377,22 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="O253" t="inlineStr"/>
-      <c r="P253" t="inlineStr"/>
-      <c r="Q253" t="inlineStr"/>
-      <c r="R253" t="inlineStr"/>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>BELO HORIZONTE</t>
+        </is>
+      </c>
+      <c r="Q253" t="n">
+        <v>0</v>
+      </c>
+      <c r="R253" t="n">
+        <v>2754406</v>
+      </c>
       <c r="S253" t="inlineStr"/>
       <c r="T253" t="inlineStr"/>
       <c r="U253" t="inlineStr"/>
@@ -17392,19 +17402,19 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>2361</v>
+        <v>2371</v>
       </c>
       <c r="B254" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C254" t="n">
-        <v>274</v>
+        <v>609</v>
       </c>
       <c r="D254" t="n">
-        <v>767</v>
+        <v>78</v>
       </c>
       <c r="E254" t="n">
-        <v>2114</v>
+        <v>4238</v>
       </c>
       <c r="F254" t="n">
         <v>1</v>
@@ -17418,7 +17428,7 @@
       <c r="I254" t="inlineStr"/>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Possível obras de adequação da sede.</t>
+          <t>Reestruturação física e ampliação do Laboratório de Química Agropecuária do Instituto Mineiro de Agropecuária - IMA</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -17444,10 +17454,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>0</v>
+        <v>8311374</v>
       </c>
       <c r="R254" t="n">
-        <v>2754406</v>
+        <v>0</v>
       </c>
       <c r="S254" t="inlineStr"/>
       <c r="T254" t="inlineStr"/>
@@ -17458,19 +17468,19 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>2371</v>
+        <v>2421</v>
       </c>
       <c r="B255" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C255" t="n">
-        <v>609</v>
+        <v>544</v>
       </c>
       <c r="D255" t="n">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="E255" t="n">
-        <v>4238</v>
+        <v>1016</v>
       </c>
       <c r="F255" t="n">
         <v>1</v>
@@ -17484,7 +17494,7 @@
       <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Reestruturação física e ampliação do Laboratório de Química Agropecuária do Instituto Mineiro de Agropecuária - IMA</t>
+          <t>Perfuração de Sistemas de Abastecimento de Agua conforme demanda dos municípios atendidos pelo IDENE</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -17501,16 +17511,16 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>8311374</v>
+        <v>477508</v>
       </c>
       <c r="R255" t="n">
         <v>0</v>
@@ -17524,19 +17534,19 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>2421</v>
+        <v>3051</v>
       </c>
       <c r="B256" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C256" t="n">
-        <v>544</v>
+        <v>364</v>
       </c>
       <c r="D256" t="n">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="E256" t="n">
-        <v>1016</v>
+        <v>4016</v>
       </c>
       <c r="F256" t="n">
         <v>1</v>
@@ -17550,7 +17560,7 @@
       <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr">
         <is>
-          <t>Perfuração de Sistemas de Abastecimento de Agua conforme demanda dos municípios atendidos pelo IDENE</t>
+          <t>Instalações do curso de Agropecuária de Precisão, com 1.070 m² de área total, além de 5 unidades de tratamento de águas residuárias.</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -17567,16 +17577,16 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>477508</v>
+        <v>4825656</v>
       </c>
       <c r="R256" t="n">
         <v>0</v>
@@ -17616,7 +17626,7 @@
       <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Instalações do curso de Agropecuária de Precisão, com 1.070 m² de área total, além de 5 unidades de tratamento de águas residuárias.</t>
+          <t>Construção de novas instalações no Instituto Tecnológico de Agropecuária de Pitangui - ITAP, totalizando 3.214 m², para salas de aula, plantas-piloto de produção e laboratórios de apoio.</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -17642,7 +17652,7 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>4825656</v>
+        <v>12649000</v>
       </c>
       <c r="R257" t="n">
         <v>0</v>
@@ -17682,7 +17692,7 @@
       <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr">
         <is>
-          <t>Construção de novas instalações no Instituto Tecnológico de Agropecuária de Pitangui - ITAP, totalizando 3.214 m², para salas de aula, plantas-piloto de produção e laboratórios de apoio.</t>
+          <t xml:space="preserve">Reforma do edifício histórico do Instituto de Laticínios Cândido Tostes, localizado no município dde juiz de Fora. </t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -17708,7 +17718,7 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>12649000</v>
+        <v>3715000</v>
       </c>
       <c r="R258" t="n">
         <v>0</v>
@@ -17725,16 +17735,16 @@
         <v>3051</v>
       </c>
       <c r="B259" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C259" t="n">
-        <v>364</v>
+        <v>571</v>
       </c>
       <c r="D259" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E259" t="n">
-        <v>4016</v>
+        <v>4018</v>
       </c>
       <c r="F259" t="n">
         <v>1</v>
@@ -17748,7 +17758,7 @@
       <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reforma do edifício histórico do Instituto de Laticínios Cândido Tostes, localizado no município dde juiz de Fora. </t>
+          <t>Melhoria na infraestrutura das unidades de pesquisa.</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -17774,10 +17784,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>3715000</v>
+        <v>0</v>
       </c>
       <c r="R259" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="S259" t="inlineStr"/>
       <c r="T259" t="inlineStr"/>
@@ -17788,19 +17798,19 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>3051</v>
+        <v>4031</v>
       </c>
       <c r="B260" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C260" t="n">
-        <v>571</v>
+        <v>61</v>
       </c>
       <c r="D260" t="n">
-        <v>16</v>
+        <v>706</v>
       </c>
       <c r="E260" t="n">
-        <v>4018</v>
+        <v>2091</v>
       </c>
       <c r="F260" t="n">
         <v>1</v>
@@ -17811,39 +17821,47 @@
       <c r="H260" t="n">
         <v>259</v>
       </c>
-      <c r="I260" t="inlineStr"/>
+      <c r="I260" t="n">
+        <v>12054</v>
+      </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>Melhoria na infraestrutura das unidades de pesquisa.</t>
+          <t xml:space="preserve"> Construção do novo prédio do Fórum da Comarca de Betim/MG</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L260" t="inlineStr"/>
-      <c r="M260" t="inlineStr"/>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M260" t="n">
+        <v>1</v>
+      </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q260" t="n">
         <v>0</v>
       </c>
       <c r="R260" t="n">
-        <v>250000</v>
+        <v>11016496</v>
       </c>
       <c r="S260" t="inlineStr"/>
       <c r="T260" t="inlineStr"/>
@@ -17878,11 +17896,11 @@
         <v>260</v>
       </c>
       <c r="I261" t="n">
-        <v>12054</v>
+        <v>12806</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Construção do novo prédio do Fórum da Comarca de Betim/MG</t>
+          <t>Campo Belo/MG - Construção do novo Fórum da Comarca de Campo Belo</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -17905,19 +17923,19 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>CAMPO BELO</t>
         </is>
       </c>
       <c r="Q261" t="n">
         <v>0</v>
       </c>
       <c r="R261" t="n">
-        <v>11016496</v>
+        <v>19994210</v>
       </c>
       <c r="S261" t="inlineStr"/>
       <c r="T261" t="inlineStr"/>
@@ -17952,11 +17970,11 @@
         <v>261</v>
       </c>
       <c r="I262" t="n">
-        <v>12806</v>
+        <v>12638</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Campo Belo/MG - Construção do novo Fórum da Comarca de Campo Belo</t>
+          <t>Obra de construção do novo Fórum da Comarca de Carangola.</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
@@ -17979,19 +17997,19 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>CAMPO BELO</t>
+          <t>CARANGOLA</t>
         </is>
       </c>
       <c r="Q262" t="n">
         <v>0</v>
       </c>
       <c r="R262" t="n">
-        <v>19994210</v>
+        <v>12843388</v>
       </c>
       <c r="S262" t="inlineStr"/>
       <c r="T262" t="inlineStr"/>
@@ -18026,11 +18044,11 @@
         <v>262</v>
       </c>
       <c r="I263" t="n">
-        <v>12638</v>
+        <v>12400</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Carangola.</t>
+          <t xml:space="preserve"> Contrato a execução da obra de reforma e ampliação do Fórum da Comarca de Ipatinga/MG</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -18053,19 +18071,19 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>CARANGOLA</t>
+          <t>IPATINGA</t>
         </is>
       </c>
       <c r="Q263" t="n">
         <v>0</v>
       </c>
       <c r="R263" t="n">
-        <v>12843388</v>
+        <v>18849069</v>
       </c>
       <c r="S263" t="inlineStr"/>
       <c r="T263" t="inlineStr"/>
@@ -18100,11 +18118,11 @@
         <v>263</v>
       </c>
       <c r="I264" t="n">
-        <v>12400</v>
+        <v>12288</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Contrato a execução da obra de reforma e ampliação do Fórum da Comarca de Ipatinga/MG</t>
+          <t xml:space="preserve"> Reforma e Ampliação do Fórum da Comarca de Monte Belo/MG</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -18127,19 +18145,19 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>IPATINGA</t>
+          <t>MONTE BELO</t>
         </is>
       </c>
       <c r="Q264" t="n">
         <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>18849069</v>
+        <v>1950000</v>
       </c>
       <c r="S264" t="inlineStr"/>
       <c r="T264" t="inlineStr"/>
@@ -18174,11 +18192,11 @@
         <v>264</v>
       </c>
       <c r="I265" t="n">
-        <v>12288</v>
+        <v>12816</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reforma e Ampliação do Fórum da Comarca de Monte Belo/MG</t>
+          <t>Obra de construção do novo Fórum da Comarca de Pirapora/MG</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -18201,19 +18219,19 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>MONTE BELO</t>
+          <t>PIRAPORA</t>
         </is>
       </c>
       <c r="Q265" t="n">
         <v>0</v>
       </c>
       <c r="R265" t="n">
-        <v>1950000</v>
+        <v>22776109</v>
       </c>
       <c r="S265" t="inlineStr"/>
       <c r="T265" t="inlineStr"/>
@@ -18248,11 +18266,11 @@
         <v>265</v>
       </c>
       <c r="I266" t="n">
-        <v>12816</v>
+        <v>12781</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Pirapora/MG</t>
+          <t>Construção do novo fórum da Comarca de São Gonçalo do Sapucaí/MG</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -18275,19 +18293,19 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P266" t="inlineStr">
         <is>
-          <t>PIRAPORA</t>
+          <t>SÃO GONÇALO DO SAPUCAÍ</t>
         </is>
       </c>
       <c r="Q266" t="n">
         <v>0</v>
       </c>
       <c r="R266" t="n">
-        <v>22776109</v>
+        <v>14670005</v>
       </c>
       <c r="S266" t="inlineStr"/>
       <c r="T266" t="inlineStr"/>
@@ -18322,11 +18340,11 @@
         <v>266</v>
       </c>
       <c r="I267" t="n">
-        <v>12781</v>
+        <v>12799</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>Construção do novo fórum da Comarca de São Gonçalo do Sapucaí/MG</t>
+          <t xml:space="preserve">Construção do novo Fórum da Comarca de Timóteo/MG </t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -18349,19 +18367,19 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>SÃO GONÇALO DO SAPUCAÍ</t>
+          <t>TIMÓTEO</t>
         </is>
       </c>
       <c r="Q267" t="n">
         <v>0</v>
       </c>
       <c r="R267" t="n">
-        <v>14670005</v>
+        <v>19506288</v>
       </c>
       <c r="S267" t="inlineStr"/>
       <c r="T267" t="inlineStr"/>
@@ -18396,16 +18414,16 @@
         <v>267</v>
       </c>
       <c r="I268" t="n">
-        <v>12799</v>
+        <v>12833</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construção do novo Fórum da Comarca de Timóteo/MG </t>
+          <t>Obra de construção do novo Fórum da Comarca de Rio Novo.</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -18423,19 +18441,19 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>TIMÓTEO</t>
+          <t>RIO NOVO</t>
         </is>
       </c>
       <c r="Q268" t="n">
         <v>0</v>
       </c>
       <c r="R268" t="n">
-        <v>19506288</v>
+        <v>4976096</v>
       </c>
       <c r="S268" t="inlineStr"/>
       <c r="T268" t="inlineStr"/>
@@ -18470,11 +18488,11 @@
         <v>268</v>
       </c>
       <c r="I269" t="n">
-        <v>12833</v>
+        <v>12629</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Rio Novo.</t>
+          <t>Obra de construção do novo Fórum da Comarca de Luz.</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -18497,19 +18515,19 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>RIO NOVO</t>
+          <t>LUZ</t>
         </is>
       </c>
       <c r="Q269" t="n">
         <v>0</v>
       </c>
       <c r="R269" t="n">
-        <v>4976096</v>
+        <v>7654409</v>
       </c>
       <c r="S269" t="inlineStr"/>
       <c r="T269" t="inlineStr"/>
@@ -18544,16 +18562,16 @@
         <v>269</v>
       </c>
       <c r="I270" t="n">
-        <v>12629</v>
+        <v>12607</v>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Luz.</t>
+          <t>Reforma e ampliação do Fórum da Comarca de Sete Lagoas/MG.</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -18571,19 +18589,19 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>LUZ</t>
+          <t>SETE LAGOAS</t>
         </is>
       </c>
       <c r="Q270" t="n">
         <v>0</v>
       </c>
       <c r="R270" t="n">
-        <v>7654409</v>
+        <v>32235085</v>
       </c>
       <c r="S270" t="inlineStr"/>
       <c r="T270" t="inlineStr"/>
@@ -18618,11 +18636,11 @@
         <v>270</v>
       </c>
       <c r="I271" t="n">
-        <v>12607</v>
+        <v>12639</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>Reforma e ampliação do Fórum da Comarca de Sete Lagoas/MG.</t>
+          <t>Obra de construção do novo Fórum da Comarca de Três Pontas</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -18645,19 +18663,19 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>SETE LAGOAS</t>
+          <t>TRÊS PONTAS</t>
         </is>
       </c>
       <c r="Q271" t="n">
         <v>0</v>
       </c>
       <c r="R271" t="n">
-        <v>32235085</v>
+        <v>9489687</v>
       </c>
       <c r="S271" t="inlineStr"/>
       <c r="T271" t="inlineStr"/>
@@ -18692,16 +18710,16 @@
         <v>271</v>
       </c>
       <c r="I272" t="n">
-        <v>12639</v>
+        <v>11547</v>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Três Pontas</t>
+          <t>RETOMADA DA OBRA DE CONSTRUÇÃO DO NOVO PRÉDIO DO FÓRUM DA COMARCA DE ITAJUBÁ/MG</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -18719,19 +18737,19 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>TRÊS PONTAS</t>
+          <t>ITAJUBÁ</t>
         </is>
       </c>
       <c r="Q272" t="n">
         <v>0</v>
       </c>
       <c r="R272" t="n">
-        <v>9489687</v>
+        <v>9366263</v>
       </c>
       <c r="S272" t="inlineStr"/>
       <c r="T272" t="inlineStr"/>
@@ -18766,11 +18784,11 @@
         <v>272</v>
       </c>
       <c r="I273" t="n">
-        <v>11547</v>
+        <v>12856</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>RETOMADA DA OBRA DE CONSTRUÇÃO DO NOVO PRÉDIO DO FÓRUM DA COMARCA DE ITAJUBÁ/MG</t>
+          <t>Retomada da obra de construção do novo Fórum da Comarca de Poços de Caldas.</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -18798,14 +18816,14 @@
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>ITAJUBÁ</t>
+          <t>POÇOS DE CALDAS</t>
         </is>
       </c>
       <c r="Q273" t="n">
         <v>0</v>
       </c>
       <c r="R273" t="n">
-        <v>9366263</v>
+        <v>11009635</v>
       </c>
       <c r="S273" t="inlineStr"/>
       <c r="T273" t="inlineStr"/>
@@ -18840,11 +18858,11 @@
         <v>273</v>
       </c>
       <c r="I274" t="n">
-        <v>12856</v>
+        <v>12344</v>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>Retomada da obra de construção do novo Fórum da Comarca de Poços de Caldas.</t>
+          <t>Construção do novo prédio do Fórum da Comarca de Camanducaia/MG</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
@@ -18872,14 +18890,14 @@
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>POÇOS DE CALDAS</t>
+          <t>CAMANDUCAIA</t>
         </is>
       </c>
       <c r="Q274" t="n">
         <v>0</v>
       </c>
       <c r="R274" t="n">
-        <v>11009635</v>
+        <v>4627222</v>
       </c>
       <c r="S274" t="inlineStr"/>
       <c r="T274" t="inlineStr"/>
@@ -18913,12 +18931,10 @@
       <c r="H275" t="n">
         <v>274</v>
       </c>
-      <c r="I275" t="n">
-        <v>12344</v>
-      </c>
+      <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr">
         <is>
-          <t>Construção do novo prédio do Fórum da Comarca de Camanducaia/MG</t>
+          <t>Obra de construção do novo Fórum da Comarca de São João do Paraíso</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
@@ -18941,19 +18957,19 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>Região Intermediária de Pouso Alegre</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>CAMANDUCAIA</t>
+          <t>SÃO JOÃO DO PARAÍSO</t>
         </is>
       </c>
       <c r="Q275" t="n">
         <v>0</v>
       </c>
       <c r="R275" t="n">
-        <v>4627222</v>
+        <v>7290196</v>
       </c>
       <c r="S275" t="inlineStr"/>
       <c r="T275" t="inlineStr"/>
@@ -18990,7 +19006,7 @@
       <c r="I276" t="inlineStr"/>
       <c r="J276" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de São João do Paraíso</t>
+          <t>Implantação do Fórum Digital no município de Brasilândia de Minas</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -19013,19 +19029,19 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>SÃO JOÃO DO PARAÍSO</t>
+          <t>BRASILÂNDIA DE MINAS</t>
         </is>
       </c>
       <c r="Q276" t="n">
         <v>0</v>
       </c>
       <c r="R276" t="n">
-        <v>7290196</v>
+        <v>1373680</v>
       </c>
       <c r="S276" t="inlineStr"/>
       <c r="T276" t="inlineStr"/>
@@ -19062,7 +19078,7 @@
       <c r="I277" t="inlineStr"/>
       <c r="J277" t="inlineStr">
         <is>
-          <t>Implantação do Fórum Digital no município de Brasilândia de Minas</t>
+          <t>Implantação do Fórum Digital no município de São Gonçalo do Abaeté</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -19090,7 +19106,7 @@
       </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>BRASILÂNDIA DE MINAS</t>
+          <t>SÃO GONÇALO DO ABAETÉ</t>
         </is>
       </c>
       <c r="Q277" t="n">
@@ -19134,7 +19150,7 @@
       <c r="I278" t="inlineStr"/>
       <c r="J278" t="inlineStr">
         <is>
-          <t>Implantação do Fórum Digital no município de São Gonçalo do Abaeté</t>
+          <t>Implantação do Fórum Digital no município de Ponto Chique</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
@@ -19157,19 +19173,19 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>SÃO GONÇALO DO ABAETÉ</t>
+          <t>PONTO CHIQUE</t>
         </is>
       </c>
       <c r="Q278" t="n">
         <v>0</v>
       </c>
       <c r="R278" t="n">
-        <v>1373680</v>
+        <v>1760000</v>
       </c>
       <c r="S278" t="inlineStr"/>
       <c r="T278" t="inlineStr"/>
@@ -19203,15 +19219,17 @@
       <c r="H279" t="n">
         <v>278</v>
       </c>
-      <c r="I279" t="inlineStr"/>
+      <c r="I279" t="n">
+        <v>12627</v>
+      </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>Implantação do Fórum Digital no município de Ponto Chique</t>
+          <t>Execução da 4ª (quarta) parcela da reforma parcial do Edifício-Sede do TRIBUNAL.</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -19229,19 +19247,19 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>PONTO CHIQUE</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q279" t="n">
         <v>0</v>
       </c>
       <c r="R279" t="n">
-        <v>1760000</v>
+        <v>38084213</v>
       </c>
       <c r="S279" t="inlineStr"/>
       <c r="T279" t="inlineStr"/>
@@ -19276,11 +19294,11 @@
         <v>279</v>
       </c>
       <c r="I280" t="n">
-        <v>12627</v>
+        <v>12146</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Execução da 4ª (quarta) parcela da reforma parcial do Edifício-Sede do TRIBUNAL.</t>
+          <t>Reforma geral do Fórum Lafayette, em Belo Horizonte/MG</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -19315,7 +19333,7 @@
         <v>0</v>
       </c>
       <c r="R280" t="n">
-        <v>38084213</v>
+        <v>135013067</v>
       </c>
       <c r="S280" t="inlineStr"/>
       <c r="T280" t="inlineStr"/>
@@ -19350,11 +19368,11 @@
         <v>280</v>
       </c>
       <c r="I281" t="n">
-        <v>12146</v>
+        <v>12703</v>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>Reforma geral do Fórum Lafayette, em Belo Horizonte/MG</t>
+          <t>Cincão - Reforma parcial para adequações da estrutura física dos Armazéns 6, 7 e 8, Galpão 2, Arquivo Central e Permanente</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -19389,7 +19407,7 @@
         <v>0</v>
       </c>
       <c r="R281" t="n">
-        <v>135013067</v>
+        <v>1052449</v>
       </c>
       <c r="S281" t="inlineStr"/>
       <c r="T281" t="inlineStr"/>
@@ -19423,17 +19441,15 @@
       <c r="H282" t="n">
         <v>281</v>
       </c>
-      <c r="I282" t="n">
-        <v>12703</v>
-      </c>
+      <c r="I282" t="inlineStr"/>
       <c r="J282" t="inlineStr">
         <is>
-          <t>Cincão - Reforma parcial para adequações da estrutura física dos Armazéns 6, 7 e 8, Galpão 2, Arquivo Central e Permanente</t>
+          <t>Obra de construção do novo Fórum da Comarca de Monte Alegre de Minas</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -19451,19 +19467,19 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>MONTE ALEGRE DE MINAS</t>
         </is>
       </c>
       <c r="Q282" t="n">
         <v>0</v>
       </c>
       <c r="R282" t="n">
-        <v>1052449</v>
+        <v>6139672</v>
       </c>
       <c r="S282" t="inlineStr"/>
       <c r="T282" t="inlineStr"/>
@@ -19474,19 +19490,19 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>4031</v>
+        <v>5011</v>
       </c>
       <c r="B283" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C283" t="n">
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="D283" t="n">
-        <v>706</v>
+        <v>133</v>
       </c>
       <c r="E283" t="n">
-        <v>2091</v>
+        <v>3017</v>
       </c>
       <c r="F283" t="n">
         <v>1</v>
@@ -19500,7 +19516,7 @@
       <c r="I283" t="inlineStr"/>
       <c r="J283" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Monte Alegre de Minas</t>
+          <t>CENTRO DE CULTURA PRESIDENTE ITAMAR FRANCO</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -19508,34 +19524,28 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L283" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M283" t="n">
-        <v>1</v>
-      </c>
+      <c r="L283" t="inlineStr"/>
+      <c r="M283" t="inlineStr"/>
       <c r="N283" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P283" t="inlineStr">
         <is>
-          <t>MONTE ALEGRE DE MINAS</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q283" t="n">
         <v>0</v>
       </c>
       <c r="R283" t="n">
-        <v>6139672</v>
+        <v>800000</v>
       </c>
       <c r="S283" t="inlineStr"/>
       <c r="T283" t="inlineStr"/>
@@ -19546,19 +19556,19 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>5011</v>
+        <v>5031</v>
       </c>
       <c r="B284" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C284" t="n">
-        <v>122</v>
+        <v>572</v>
       </c>
       <c r="D284" t="n">
         <v>133</v>
       </c>
       <c r="E284" t="n">
-        <v>3017</v>
+        <v>3015</v>
       </c>
       <c r="F284" t="n">
         <v>1</v>
@@ -19572,7 +19582,7 @@
       <c r="I284" t="inlineStr"/>
       <c r="J284" t="inlineStr">
         <is>
-          <t>CENTRO DE CULTURA PRESIDENTE ITAMAR FRANCO</t>
+          <t>BALNEÁRIO ÁGUAS SANTAS - TIRADENTES/MG | BARREIO DE ARAXÁ</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -19601,7 +19611,7 @@
         <v>0</v>
       </c>
       <c r="R284" t="n">
-        <v>800000</v>
+        <v>4782988</v>
       </c>
       <c r="S284" t="inlineStr"/>
       <c r="T284" t="inlineStr"/>
@@ -19612,19 +19622,19 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>5031</v>
+        <v>5141</v>
       </c>
       <c r="B285" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C285" t="n">
-        <v>572</v>
+        <v>126</v>
       </c>
       <c r="D285" t="n">
-        <v>133</v>
+        <v>30</v>
       </c>
       <c r="E285" t="n">
-        <v>3015</v>
+        <v>6006</v>
       </c>
       <c r="F285" t="n">
         <v>1</v>
@@ -19638,7 +19648,7 @@
       <c r="I285" t="inlineStr"/>
       <c r="J285" t="inlineStr">
         <is>
-          <t>BALNEÁRIO ÁGUAS SANTAS - TIRADENTES/MG | BARREIO DE ARAXÁ</t>
+          <t>ELABORAÇÃO E EXECUÇÃO DE PROJETOS RELACIONADOS À REFORMA, MODERNIZAÇÃO E ADEQUAÇÃO DAS INSTALAÇÕES PREDIAIS DA COMPANHIA.</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
@@ -19667,7 +19677,7 @@
         <v>0</v>
       </c>
       <c r="R285" t="n">
-        <v>4782988</v>
+        <v>16317109</v>
       </c>
       <c r="S285" t="inlineStr"/>
       <c r="T285" t="inlineStr"/>
@@ -19678,19 +19688,19 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>5141</v>
+        <v>5251</v>
       </c>
       <c r="B286" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C286" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D286" t="n">
-        <v>30</v>
+        <v>133</v>
       </c>
       <c r="E286" t="n">
-        <v>6006</v>
+        <v>3018</v>
       </c>
       <c r="F286" t="n">
         <v>1</v>
@@ -19704,12 +19714,12 @@
       <c r="I286" t="inlineStr"/>
       <c r="J286" t="inlineStr">
         <is>
-          <t>ELABORAÇÃO E EXECUÇÃO DE PROJETOS RELACIONADOS À REFORMA, MODERNIZAÇÃO E ADEQUAÇÃO DAS INSTALAÇÕES PREDIAIS DA COMPANHIA.</t>
+          <t>Projeto de Expansão</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L286" t="inlineStr"/>
@@ -19721,19 +19731,19 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P286" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q286" t="n">
         <v>0</v>
       </c>
       <c r="R286" t="n">
-        <v>16317109</v>
+        <v>457766318</v>
       </c>
       <c r="S286" t="inlineStr"/>
       <c r="T286" t="inlineStr"/>
@@ -19744,19 +19754,19 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>5251</v>
+        <v>5391</v>
       </c>
       <c r="B287" t="n">
         <v>25</v>
       </c>
       <c r="C287" t="n">
-        <v>121</v>
+        <v>752</v>
       </c>
       <c r="D287" t="n">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="E287" t="n">
-        <v>3018</v>
+        <v>3004</v>
       </c>
       <c r="F287" t="n">
         <v>1</v>
@@ -19770,12 +19780,12 @@
       <c r="I287" t="inlineStr"/>
       <c r="J287" t="inlineStr">
         <is>
-          <t>Projeto de Expansão</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L287" t="inlineStr"/>
@@ -19792,14 +19802,14 @@
       </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q287" t="n">
         <v>0</v>
       </c>
       <c r="R287" t="n">
-        <v>457766318</v>
+        <v>92004926</v>
       </c>
       <c r="S287" t="inlineStr"/>
       <c r="T287" t="inlineStr"/>
@@ -19853,19 +19863,19 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P288" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q288" t="n">
         <v>0</v>
       </c>
       <c r="R288" t="n">
-        <v>92004926</v>
+        <v>10705994</v>
       </c>
       <c r="S288" t="inlineStr"/>
       <c r="T288" t="inlineStr"/>
@@ -19919,19 +19929,19 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P289" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
         </is>
       </c>
       <c r="Q289" t="n">
         <v>0</v>
       </c>
       <c r="R289" t="n">
-        <v>10705994</v>
+        <v>10464844</v>
       </c>
       <c r="S289" t="inlineStr"/>
       <c r="T289" t="inlineStr"/>
@@ -19985,19 +19995,19 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P290" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q290" t="n">
         <v>0</v>
       </c>
       <c r="R290" t="n">
-        <v>10464844</v>
+        <v>2098278</v>
       </c>
       <c r="S290" t="inlineStr"/>
       <c r="T290" t="inlineStr"/>
@@ -20051,19 +20061,19 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P291" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q291" t="n">
         <v>0</v>
       </c>
       <c r="R291" t="n">
-        <v>2098278</v>
+        <v>96721858</v>
       </c>
       <c r="S291" t="inlineStr"/>
       <c r="T291" t="inlineStr"/>
@@ -20117,19 +20127,19 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P292" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
         </is>
       </c>
       <c r="Q292" t="n">
         <v>0</v>
       </c>
       <c r="R292" t="n">
-        <v>96721858</v>
+        <v>16415074</v>
       </c>
       <c r="S292" t="inlineStr"/>
       <c r="T292" t="inlineStr"/>
@@ -20183,19 +20193,19 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P293" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
         </is>
       </c>
       <c r="Q293" t="n">
         <v>0</v>
       </c>
       <c r="R293" t="n">
-        <v>16415074</v>
+        <v>1</v>
       </c>
       <c r="S293" t="inlineStr"/>
       <c r="T293" t="inlineStr"/>
@@ -20218,7 +20228,7 @@
         <v>92</v>
       </c>
       <c r="E294" t="n">
-        <v>3004</v>
+        <v>3005</v>
       </c>
       <c r="F294" t="n">
         <v>1</v>
@@ -20232,7 +20242,7 @@
       <c r="I294" t="inlineStr"/>
       <c r="J294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -20249,19 +20259,19 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P294" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q294" t="n">
         <v>0</v>
       </c>
       <c r="R294" t="n">
-        <v>1</v>
+        <v>126817302</v>
       </c>
       <c r="S294" t="inlineStr"/>
       <c r="T294" t="inlineStr"/>
@@ -20315,19 +20325,19 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P295" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q295" t="n">
         <v>0</v>
       </c>
       <c r="R295" t="n">
-        <v>126817302</v>
+        <v>16058991</v>
       </c>
       <c r="S295" t="inlineStr"/>
       <c r="T295" t="inlineStr"/>
@@ -20381,19 +20391,19 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P296" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
         </is>
       </c>
       <c r="Q296" t="n">
         <v>0</v>
       </c>
       <c r="R296" t="n">
-        <v>16058991</v>
+        <v>65795530</v>
       </c>
       <c r="S296" t="inlineStr"/>
       <c r="T296" t="inlineStr"/>
@@ -20447,19 +20457,19 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P297" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q297" t="n">
         <v>0</v>
       </c>
       <c r="R297" t="n">
-        <v>65795530</v>
+        <v>44156794</v>
       </c>
       <c r="S297" t="inlineStr"/>
       <c r="T297" t="inlineStr"/>
@@ -20513,19 +20523,19 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q298" t="n">
         <v>0</v>
       </c>
       <c r="R298" t="n">
-        <v>44156794</v>
+        <v>140716908</v>
       </c>
       <c r="S298" t="inlineStr"/>
       <c r="T298" t="inlineStr"/>
@@ -20579,19 +20589,19 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
         </is>
       </c>
       <c r="Q299" t="n">
         <v>0</v>
       </c>
       <c r="R299" t="n">
-        <v>140716908</v>
+        <v>8715687</v>
       </c>
       <c r="S299" t="inlineStr"/>
       <c r="T299" t="inlineStr"/>
@@ -20645,19 +20655,19 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
         </is>
       </c>
       <c r="Q300" t="n">
         <v>0</v>
       </c>
       <c r="R300" t="n">
-        <v>8715687</v>
+        <v>24622611</v>
       </c>
       <c r="S300" t="inlineStr"/>
       <c r="T300" t="inlineStr"/>
@@ -20677,10 +20687,10 @@
         <v>752</v>
       </c>
       <c r="D301" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E301" t="n">
-        <v>3005</v>
+        <v>3001</v>
       </c>
       <c r="F301" t="n">
         <v>1</v>
@@ -20694,7 +20704,7 @@
       <c r="I301" t="inlineStr"/>
       <c r="J301" t="inlineStr">
         <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
+          <t>Expansão do Sistema de Geração</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
@@ -20711,19 +20721,19 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P301" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q301" t="n">
         <v>0</v>
       </c>
       <c r="R301" t="n">
-        <v>24622611</v>
+        <v>1</v>
       </c>
       <c r="S301" t="inlineStr"/>
       <c r="T301" t="inlineStr"/>
@@ -20732,72 +20742,6 @@
       <c r="W301" t="inlineStr"/>
       <c r="X301" t="inlineStr"/>
     </row>
-    <row r="302">
-      <c r="A302" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B302" t="n">
-        <v>25</v>
-      </c>
-      <c r="C302" t="n">
-        <v>752</v>
-      </c>
-      <c r="D302" t="n">
-        <v>94</v>
-      </c>
-      <c r="E302" t="n">
-        <v>3001</v>
-      </c>
-      <c r="F302" t="n">
-        <v>1</v>
-      </c>
-      <c r="G302" t="n">
-        <v>0</v>
-      </c>
-      <c r="H302" t="n">
-        <v>301</v>
-      </c>
-      <c r="I302" t="inlineStr"/>
-      <c r="J302" t="inlineStr">
-        <is>
-          <t>Expansão do Sistema de Geração</t>
-        </is>
-      </c>
-      <c r="K302" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L302" t="inlineStr"/>
-      <c r="M302" t="inlineStr"/>
-      <c r="N302" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O302" t="inlineStr">
-        <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="P302" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
-      <c r="R302" t="n">
-        <v>1</v>
-      </c>
-      <c r="S302" t="inlineStr"/>
-      <c r="T302" t="inlineStr"/>
-      <c r="U302" t="inlineStr"/>
-      <c r="V302" t="inlineStr"/>
-      <c r="W302" t="inlineStr"/>
-      <c r="X302" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/data/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X301"/>
+  <dimension ref="A1:X268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9788,7 +9788,7 @@
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
-          <t>ARCOS - CORUMBÁ - RODOVIA: MG-170 (ENTR BR-354 - AGRIMIG)</t>
+          <t>MG-129 - OURO PRETO A OURO BRANCO</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -9814,7 +9814,7 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>9792000</v>
+        <v>1000000</v>
       </c>
       <c r="R138" t="n">
         <v>0</v>
@@ -9854,7 +9854,7 @@
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
-          <t>MG-129 - OURO PRETO A OURO BRANCO</t>
+          <t>RECUPERAÇÃO DE EROSÃO EM TALUDE DE CORTE NA RODOVIA MGC-354, KM 167,8, TRECHO: RIBEIRÃO DA MATA - AV MARABÁ (PATOS DE MINAS)</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -9880,7 +9880,7 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>1000000</v>
+        <v>143000</v>
       </c>
       <c r="R139" t="n">
         <v>0</v>
@@ -9920,7 +9920,7 @@
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO DE EROSÃO EM TALUDE DE CORTE NA RODOVIA MGC-354, KM 167,8, TRECHO: RIBEIRÃO DA MATA - AV MARABÁ (PATOS DE MINAS)</t>
+          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 150,9, TRECHO: TRAVESSIA URBANA DE PRESIDENTE OLEGÁRIO</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9946,7 +9946,7 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>143000</v>
+        <v>5876140</v>
       </c>
       <c r="R140" t="n">
         <v>0</v>
@@ -9986,7 +9986,7 @@
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 150,9, TRECHO: TRAVESSIA URBANA DE PRESIDENTE OLEGÁRIO</t>
+          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 176,2, TRECHO: AV MARABÁ (PATOS DE MINAS) - ENTR BR 365</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -10012,7 +10012,7 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>5876140</v>
+        <v>1132500</v>
       </c>
       <c r="R141" t="n">
         <v>0</v>
@@ -10052,7 +10052,7 @@
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 176,2, TRECHO: AV MARABÁ (PATOS DE MINAS) - ENTR BR 365</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE (3ª FAIXA) DO TRECHO SERRA DO SALITRE - SALITRE DE MINAS, NA MG-230</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -10078,7 +10078,7 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>1132500</v>
+        <v>34710000</v>
       </c>
       <c r="R142" t="n">
         <v>0</v>
@@ -10118,7 +10118,7 @@
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E 3ª FAIXA, TRECHO ENTR. BR-354 (CAXAMBÚ) - ENTR. BR-381 (PALMELA DISTRITO DE CAMPANHA), NA MGC-267</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO MG-344 (ENTR. P/ CÁSSIA) - DIVISA MG/SP, NA MG-444, EXT. 23,9 KM</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -10144,7 +10144,7 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>1000000</v>
+        <v>59000000</v>
       </c>
       <c r="R143" t="n">
         <v>0</v>
@@ -10184,7 +10184,7 @@
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE (3ª FAIXA) DO TRECHO SERRA DO SALITRE - SALITRE DE MINAS, NA MG-230</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO PARÁ DE MINAS - PAPAGAIOS (3ª FAIXA) - LOTE 1</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -10210,7 +10210,7 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>34710000</v>
+        <v>1000000</v>
       </c>
       <c r="R144" t="n">
         <v>0</v>
@@ -10250,7 +10250,7 @@
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO MG-344 (ENTR. P/ CÁSSIA) - DIVISA MG/SP, NA MG-444, EXT. 23,9 KM</t>
+          <t>RESTAURAÇÃO TIMÓTEO - ENTR. LMG-760 (CAVA GRANDE), NA MG-425</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -10276,7 +10276,7 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>59000000</v>
+        <v>200000</v>
       </c>
       <c r="R145" t="n">
         <v>0</v>
@@ -10316,7 +10316,7 @@
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO PARÁ DE MINAS - PAPAGAIOS (3ª FAIXA) - LOTE 1</t>
+          <t>RESTAURAÇÃO TRECHO ENTR. MGC-120 (B) (DONA EUZÉBIA) - ENTR. MGC-265, NA MG-285</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -10342,7 +10342,7 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>1000000</v>
+        <v>30980000</v>
       </c>
       <c r="R146" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO: UNAÍ A GARAPUAVA</t>
+          <t>RESTAURAÇÃO TRECHO ENTR. MGC-265/MG-452 (P/ PAIVA) - ENTR. BR-040, NA MG-448</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -10408,7 +10408,7 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>1000000</v>
+        <v>25655000</v>
       </c>
       <c r="R147" t="n">
         <v>0</v>
@@ -10448,7 +10448,7 @@
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TIMÓTEO - ENTR. LMG-760 (CAVA GRANDE), NA MG-425</t>
+          <t>RESTAURAÇÃO TRECHO PIRAÚBA (ENTR. MG-285) - PAIVA (ENTR. MG-488/MG-455), NA MG-265 E 3ª FAIXA</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -10474,7 +10474,7 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>200000</v>
+        <v>66560000</v>
       </c>
       <c r="R148" t="n">
         <v>0</v>
@@ -10514,7 +10514,7 @@
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO ENTR. LMG764 (P/ MATUTINA) - SÃO GOTARDO, NA MG- 235 - 3ª FAIXA</t>
+          <t>RESTAURAÇÃO TRÊS PONTAS - VARGINHA, NA MG-167</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>1000000</v>
+        <v>25464500</v>
       </c>
       <c r="R149" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
         <v>81</v>
       </c>
       <c r="E150" t="n">
-        <v>4268</v>
+        <v>4272</v>
       </c>
       <c r="F150" t="n">
         <v>1</v>
@@ -10580,7 +10580,7 @@
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO ENTR. MGC-120 (B) (DONA EUZÉBIA) - ENTR. MGC-265, NA MG-285</t>
+          <t>COMPLEMENTAÇÃO DA CONSTRUÇÃO DA PONTE SOBRE O RIO SÃO FRANCISCO, PINTÓPOLIS</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -10606,7 +10606,7 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>30980000</v>
+        <v>1202905</v>
       </c>
       <c r="R150" t="n">
         <v>0</v>
@@ -10632,7 +10632,7 @@
         <v>81</v>
       </c>
       <c r="E151" t="n">
-        <v>4268</v>
+        <v>4272</v>
       </c>
       <c r="F151" t="n">
         <v>1</v>
@@ -10646,7 +10646,7 @@
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO ENTR. MGC-265/MG-452 (P/ PAIVA) - ENTR. BR-040, NA MG-448</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O CÓRREGO DAS LAJES, TRECHO ENTR. MGC-479 (SERRA DAS ARARAS) - ENTR. MG-402, NA LMG-622</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -10672,7 +10672,7 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>25655000</v>
+        <v>1000000</v>
       </c>
       <c r="R151" t="n">
         <v>0</v>
@@ -10698,7 +10698,7 @@
         <v>81</v>
       </c>
       <c r="E152" t="n">
-        <v>4268</v>
+        <v>4272</v>
       </c>
       <c r="F152" t="n">
         <v>1</v>
@@ -10712,7 +10712,7 @@
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO PIRAÚBA (ENTR. MG-285) - PAIVA (ENTR. MG-488/MG-455), NA MG-265 E 3ª FAIXA</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SÃO JOÃO, TRECHO IGARATINGA - ENTR. MG-252, NA MG-430 (SEMI-INTEGRADA)</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -10738,7 +10738,7 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>66560000</v>
+        <v>14920000</v>
       </c>
       <c r="R152" t="n">
         <v>0</v>
@@ -10764,7 +10764,7 @@
         <v>81</v>
       </c>
       <c r="E153" t="n">
-        <v>4268</v>
+        <v>4272</v>
       </c>
       <c r="F153" t="n">
         <v>1</v>
@@ -10778,7 +10778,7 @@
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO SÃO GOTARDO - ENTR. BR-354 (P/ PATOS DE MINAS), NA MG-235</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SERRA BRANCA, TRECHO PAI PEDRO - CATUTI, NA MGC-122</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -10804,7 +10804,7 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>1000000</v>
+        <v>8798400</v>
       </c>
       <c r="R153" t="n">
         <v>0</v>
@@ -10830,7 +10830,7 @@
         <v>81</v>
       </c>
       <c r="E154" t="n">
-        <v>4268</v>
+        <v>4272</v>
       </c>
       <c r="F154" t="n">
         <v>1</v>
@@ -10844,7 +10844,7 @@
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRÊS PONTAS - VARGINHA, NA MG-167</t>
+          <t>LMG-722 (ROCHINHA A LAGAMAR, PONTE SOBRE O RIO PARANAÍBA)</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -10870,7 +10870,7 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>25464500</v>
+        <v>1000000</v>
       </c>
       <c r="R154" t="n">
         <v>0</v>
@@ -10910,7 +10910,7 @@
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
-          <t>BDCC 3X3 CÓRREGO CAVALO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
+          <t>MGC-267 (CORDISLÂNDIA A CARVALHÓPOLIS, PONTE SOBRE O RIO SAPUCAÍ -  LOTE 01)</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -10936,7 +10936,7 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>100000</v>
+        <v>1203643</v>
       </c>
       <c r="R155" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO DA CONSTRUÇÃO DA PONTE SOBRE O RIO SÃO FRANCISCO, PINTÓPOLIS</t>
+          <t>PASSARELA MG-010 (CIDADE ADMINISTRATIVA)</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -11002,7 +11002,7 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>24000000</v>
+        <v>66620</v>
       </c>
       <c r="R156" t="n">
         <v>0</v>
@@ -11042,7 +11042,7 @@
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE CÓRREGO SÃO BARTOLOMEU E ENCABEÇAMENTO CÓRREGO BARBADINHO, TRECHO CANABRAVA (JOÃO PINHEIRO) - ENTR. MG-181, NA LMG-698</t>
+          <t>PONTE SOBRE O EXTRAVASOR DA CEMIG, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -11068,7 +11068,7 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>252000</v>
+        <v>1000000</v>
       </c>
       <c r="R157" t="n">
         <v>0</v>
@@ -11108,7 +11108,7 @@
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO AMENDOIM, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
+          <t>PONTE SOBRE O RIBEIRÃO MATA BOI NA RODOVIA MG-414, TRECHO ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -11134,7 +11134,7 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>319200</v>
+        <v>2940000</v>
       </c>
       <c r="R158" t="n">
         <v>0</v>
@@ -11174,7 +11174,7 @@
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO BOI PRETO, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
+          <t>PONTE SOBRE O RIBEIRÃO PANDEIROS, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -11200,7 +11200,7 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>495600</v>
+        <v>1000000</v>
       </c>
       <c r="R159" t="n">
         <v>0</v>
@@ -11240,7 +11240,7 @@
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O CÓRREGO DAS LAJES, TRECHO ENTR. MGC-479 (SERRA DAS ARARAS) - ENTR. MG-402, NA LMG-622</t>
+          <t>PONTE SOBRE O RIO ARAGUARI (TROCA DOS APARELHOS DE DO 1º E 5º VÃOS), TRECHO ENTR. MG-190 - ZELÂNDIA (USINA SANTA JULIANA), DIMENSÕES 130,00X12,20M, RODOVIA AMG-0730</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -11266,7 +11266,7 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>679000</v>
+        <v>542000</v>
       </c>
       <c r="R160" t="n">
         <v>0</v>
@@ -11306,7 +11306,7 @@
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SANTO INÁCIO, TRECHO ENTR. MG-188 (COROMANDEL) - DISTRITO DE VEREDA, NA LMG-747</t>
+          <t>PONTE SOBRE O RIO CORRENTE -  MG-460, NO TRECHO DE MUNHOZ - TOLEDO ( E SEMI-INTEGRADA)</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -11332,7 +11332,7 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>440000</v>
+        <v>2163814</v>
       </c>
       <c r="R161" t="n">
         <v>0</v>
@@ -11372,7 +11372,7 @@
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SÃO JOÃO, TRECHO IGARATINGA - ENTR. MG-252, NA MG-430 (SEMI-INTEGRADA)</t>
+          <t>PONTE SOBRE O RIO SÃO FRANCISCO - ENTR. MGC-135 (MANGA) ¿ PORTO DE MATIAS CARDOSO, NA RODOVIA MG-401</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -11398,7 +11398,7 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>14920000</v>
+        <v>11974837</v>
       </c>
       <c r="R162" t="n">
         <v>0</v>
@@ -11438,7 +11438,7 @@
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SERRA BRANCA, TRECHO PAI PEDRO - CATUTI, NA MGC-122</t>
+          <t>RECUPERAÇÃO DA PONTE S/ O RIO JEQUITINHONHA- DIAMANTINA - COUTO MAGALHÃES.</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -11464,7 +11464,7 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>8798400</v>
+        <v>1382535</v>
       </c>
       <c r="R163" t="n">
         <v>0</v>
@@ -11490,7 +11490,7 @@
         <v>81</v>
       </c>
       <c r="E164" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F164" t="n">
         <v>1</v>
@@ -11504,7 +11504,7 @@
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTOS E PONTES SOBRE CÓRREGO VEREDINHA E RIBEIRÃO MARQUES, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
+          <t>ACESSO AO PRESÍDIO DE ITURAMA</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -11530,7 +11530,7 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>369600</v>
+        <v>1000000</v>
       </c>
       <c r="R164" t="n">
         <v>0</v>
@@ -11556,7 +11556,7 @@
         <v>81</v>
       </c>
       <c r="E165" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F165" t="n">
         <v>1</v>
@@ -11570,7 +11570,7 @@
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
-          <t>LMG-722 (ROCHINHA A LAGAMAR, PONTE SOBRE O RIO PARANAÍBA)</t>
+          <t>ARAÇAÍ - SETE LAGOAS, RODOVIA MUNICIPAL</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -11596,7 +11596,7 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>1000000</v>
+        <v>35359853</v>
       </c>
       <c r="R165" t="n">
         <v>0</v>
@@ -11622,7 +11622,7 @@
         <v>81</v>
       </c>
       <c r="E166" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F166" t="n">
         <v>1</v>
@@ -11636,7 +11636,7 @@
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
-          <t>MGC-267 (CORDISLÂNDIA A CARVALHÓPOLIS, PONTE SOBRE O RIO SAPUCAÍ -  LOTE 01)</t>
+          <t>ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO, NA MG-414</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -11662,7 +11662,7 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>1203643</v>
+        <v>13982612</v>
       </c>
       <c r="R166" t="n">
         <v>0</v>
@@ -11688,7 +11688,7 @@
         <v>81</v>
       </c>
       <c r="E167" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F167" t="n">
         <v>1</v>
@@ -11702,7 +11702,7 @@
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
-          <t>OLHOS D´AGUA DO OESTE A SANTA LUZIA DA SERRA - CÓRREGO SÃO BARTOLOMEU</t>
+          <t>CAMPO VERDE (DISTRITO E NOVORIZONTE) - FRUTA DE LEITE, NA LMG-626 (LOTE 01 TSD)</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -11728,7 +11728,7 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>730000</v>
+        <v>1000000</v>
       </c>
       <c r="R167" t="n">
         <v>0</v>
@@ -11754,7 +11754,7 @@
         <v>81</v>
       </c>
       <c r="E168" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F168" t="n">
         <v>1</v>
@@ -11768,7 +11768,7 @@
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
-          <t>PASSARELA MG-010 (CIDADE ADMINISTRATIVA)</t>
+          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - (LOTE 1), SEGMENTO 1 (0 A 835), 16,70 KM E SEGMENTO 2 (835 A 1250), 8,30 KM</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>66619</v>
+        <v>10459632</v>
       </c>
       <c r="R168" t="n">
         <v>0</v>
@@ -11820,7 +11820,7 @@
         <v>81</v>
       </c>
       <c r="E169" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F169" t="n">
         <v>1</v>
@@ -11834,7 +11834,7 @@
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
-          <t>PONTE CÓRREGO PERUAÇU, TRECHO CÔNEGO MARINHO - MIRAVÂNIA (RESERVA XACRIABÁ)</t>
+          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - ESTACA 2550 A 3281</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -11860,7 +11860,7 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>901000</v>
+        <v>17000000</v>
       </c>
       <c r="R169" t="n">
         <v>0</v>
@@ -11886,7 +11886,7 @@
         <v>81</v>
       </c>
       <c r="E170" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F170" t="n">
         <v>1</v>
@@ -11900,7 +11900,7 @@
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
-          <t>PONTE CÓRREGO RIBEIRÃO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
+          <t>COMPLEMENTO S JANUÁRIA - PANDEIROS, NA RODOVIA MGC-479</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -11926,7 +11926,7 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>100000</v>
+        <v>74941121</v>
       </c>
       <c r="R170" t="n">
         <v>0</v>
@@ -11952,7 +11952,7 @@
         <v>81</v>
       </c>
       <c r="E171" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F171" t="n">
         <v>1</v>
@@ -11966,7 +11966,7 @@
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O EXTRAVASOR DA CEMIG, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
+          <t>CONTORNO DE ANDRADAS (COMPLEMENTAÇÃO) - LOTE 01</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -11992,7 +11992,7 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>170000</v>
+        <v>38460000</v>
       </c>
       <c r="R171" t="n">
         <v>0</v>
@@ -12018,7 +12018,7 @@
         <v>81</v>
       </c>
       <c r="E172" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F172" t="n">
         <v>1</v>
@@ -12032,7 +12032,7 @@
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIBEIRÃO MATA BOI NA RODOVIA MG-414, TRECHO ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO</t>
+          <t>ENTR. MG-181 (BRASILÂNDIA DE MINAS) - ENTR. BR-365 (BURITIZEIRO), NA MG-408 - LOTE 01</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -12058,7 +12058,7 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>2940000</v>
+        <v>1000000</v>
       </c>
       <c r="R172" t="n">
         <v>0</v>
@@ -12084,7 +12084,7 @@
         <v>81</v>
       </c>
       <c r="E173" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F173" t="n">
         <v>1</v>
@@ -12098,7 +12098,7 @@
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIBEIRÃO PANDEIROS, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
+          <t>IBERTIOGA - PIEDADE DO RIO GRANDE, NA RODOVIA MG-338</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -12124,7 +12124,7 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>810000</v>
+        <v>7000000</v>
       </c>
       <c r="R173" t="n">
         <v>0</v>
@@ -12150,7 +12150,7 @@
         <v>81</v>
       </c>
       <c r="E174" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F174" t="n">
         <v>1</v>
@@ -12164,7 +12164,7 @@
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIO ARAGUARI (TROCA DOS APARELHOS DE DO 1º E 5º VÃOS), TRECHO ENTR. MG-190 - ZELÂNDIA (USINA SANTA JULIANA), DIMENSÕES 130,00X12,20M, RODOVIA AMG-0730</t>
+          <t>INTERSEÇÃO DE ACESSO A COUTO DE MAGALHÃES DE MINAS, NA MGC-367</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -12190,7 +12190,7 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>542000</v>
+        <v>1000000</v>
       </c>
       <c r="R174" t="n">
         <v>0</v>
@@ -12216,7 +12216,7 @@
         <v>81</v>
       </c>
       <c r="E175" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F175" t="n">
         <v>1</v>
@@ -12230,7 +12230,7 @@
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIO CORRENTE -  MG-460, NO TRECHO DE MUNHOZ - TOLEDO ( E SEMI-INTEGRADA)</t>
+          <t>PAVIMENTAÇÃO MG-326 (PONTE NOVA A BARRA LONGA)</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -12256,10 +12256,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>2163814</v>
+        <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>0</v>
+        <v>82286724</v>
       </c>
       <c r="S175" t="inlineStr"/>
       <c r="T175" t="inlineStr"/>
@@ -12282,7 +12282,7 @@
         <v>81</v>
       </c>
       <c r="E176" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F176" t="n">
         <v>1</v>
@@ -12296,7 +12296,7 @@
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIO SÃO FRANCISCO - ENTR. MGC-135 (MANGA) ¿ PORTO DE MATIAS CARDOSO, NA RODOVIA MG-401</t>
+          <t>PAVIMENTAÇÃO DA MG-314 (ENTR. MG-416 (PEÇANHA) A LMG-744 (COROACI) ENTR. VIRGOLÂNDIA)</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -12322,10 +12322,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>25000000</v>
+        <v>0</v>
       </c>
       <c r="R176" t="n">
-        <v>0</v>
+        <v>22137718</v>
       </c>
       <c r="S176" t="inlineStr"/>
       <c r="T176" t="inlineStr"/>
@@ -12348,7 +12348,7 @@
         <v>81</v>
       </c>
       <c r="E177" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F177" t="n">
         <v>1</v>
@@ -12362,7 +12362,7 @@
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
-          <t>PONTES SOBRE OS RIOS SUAÇUI PEQUENO I E II, TRECHO PEÇANHA - COROACI, NA MG-314</t>
+          <t>PAVIMENTAÇÃO DA RODOVIA MUNICIPAL (SANTA RITA DO ITUETO A ENTR. BR-259 (RESPLENDOR))</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -12388,10 +12388,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>0</v>
+        <v>21757581</v>
       </c>
       <c r="S177" t="inlineStr"/>
       <c r="T177" t="inlineStr"/>
@@ -12414,7 +12414,7 @@
         <v>81</v>
       </c>
       <c r="E178" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F178" t="n">
         <v>1</v>
@@ -12428,7 +12428,7 @@
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO DA PONTE S/ O RIO JEQUITINHONHA- DIAMANTINA - COUTO MAGALHÃES.</t>
+          <t>RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 21,80 KM</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -12454,10 +12454,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>1382535</v>
+        <v>0</v>
       </c>
       <c r="R178" t="n">
-        <v>0</v>
+        <v>8036364</v>
       </c>
       <c r="S178" t="inlineStr"/>
       <c r="T178" t="inlineStr"/>
@@ -12480,7 +12480,7 @@
         <v>81</v>
       </c>
       <c r="E179" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F179" t="n">
         <v>1</v>
@@ -12494,7 +12494,7 @@
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
+          <t>TRECHO ENTRº LMG-690 (PARACATU) - ENTRº ENTRE RIBEIROS (DISTRITO) - ENTRº MG-181 (ESTACA 1250 A 2000)</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -12520,10 +12520,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="R179" t="n">
-        <v>0</v>
+        <v>14063636</v>
       </c>
       <c r="S179" t="inlineStr"/>
       <c r="T179" t="inlineStr"/>
@@ -12546,7 +12546,7 @@
         <v>81</v>
       </c>
       <c r="E180" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F180" t="n">
         <v>1</v>
@@ -12560,7 +12560,7 @@
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO (ENTR. MG-408) - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
+          <t>RODOVIA MG-10 - TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 22,50 KM</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -12586,10 +12586,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>900000</v>
+        <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>0</v>
+        <v>8100000</v>
       </c>
       <c r="S180" t="inlineStr"/>
       <c r="T180" t="inlineStr"/>
@@ -12612,7 +12612,7 @@
         <v>81</v>
       </c>
       <c r="E181" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F181" t="n">
         <v>1</v>
@@ -12626,7 +12626,7 @@
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
-          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO DAS ARARAS I, TRECHO GUANHÃES - SÃO PEDRO DO SUAÇUÍ, NA CMG-120</t>
+          <t>MELHORAMENTO E PAVIMENTAÇÃO DO CONTORNO DE ANDRADAS</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -12652,10 +12652,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>168000</v>
+        <v>0</v>
       </c>
       <c r="R181" t="n">
-        <v>0</v>
+        <v>4804860</v>
       </c>
       <c r="S181" t="inlineStr"/>
       <c r="T181" t="inlineStr"/>
@@ -12678,7 +12678,7 @@
         <v>81</v>
       </c>
       <c r="E182" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F182" t="n">
         <v>1</v>
@@ -12692,7 +12692,7 @@
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
-          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO MACAÚBAS, TRECHO SANTA LUZIA - JABOTICATUBAS, MG-020</t>
+          <t>EMPREENDIMENTO EM DEFINIÇÃO JUNTO AO BANCO DO BRASIL - CONTRATO DE FINANCIAMENTO Nº 20/00020-0 (PDMG)</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -12718,10 +12718,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>249000</v>
+        <v>0</v>
       </c>
       <c r="R182" t="n">
-        <v>0</v>
+        <v>6000001</v>
       </c>
       <c r="S182" t="inlineStr"/>
       <c r="T182" t="inlineStr"/>
@@ -12744,7 +12744,7 @@
         <v>81</v>
       </c>
       <c r="E183" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F183" t="n">
         <v>1</v>
@@ -12758,7 +12758,7 @@
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
-          <t>REFORÇO DA FUNDAÇÃO DO VIADUTO II NA PISTA DIREITA DA INTERSEÇÃO 3 (ACESSO AO INHOTIM, ESTACA 138)</t>
+          <t>SÃO DOMINGOS DO PRATA - DOM SILVÉRIO, NA MGC-120</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -12784,7 +12784,7 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>705000</v>
+        <v>100000</v>
       </c>
       <c r="R183" t="n">
         <v>0</v>
@@ -12810,7 +12810,7 @@
         <v>81</v>
       </c>
       <c r="E184" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F184" t="n">
         <v>1</v>
@@ -12824,7 +12824,7 @@
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
-          <t>REFORÇO DE FUNDAÇÃO CÓRREGO DOIDOS, TRECHO SÃO FRANCISCO DE PAULA - ENTR. BR-354</t>
+          <t>ITAPAGIPE - ENTR. BR-364 (CAMPINA VERDE), RODOVIA MGC-154</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -12850,7 +12850,7 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>58800</v>
+        <v>6121132</v>
       </c>
       <c r="R184" t="n">
         <v>0</v>
@@ -12876,7 +12876,7 @@
         <v>81</v>
       </c>
       <c r="E185" t="n">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="F185" t="n">
         <v>1</v>
@@ -12890,7 +12890,7 @@
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
-          <t>REFORÇO NA FUNDAÇÃO DA PONTE SOBRE O RIO VERMELHO, TRECHO SANTA BÁRBARA - CATAS ALTAS, NA MG-129</t>
+          <t>JABOTICATUBAS - LAGOA SANTA, RODOVIA MUNICIPAL - LOTE 01</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -12916,7 +12916,7 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>725000</v>
+        <v>3541728</v>
       </c>
       <c r="R185" t="n">
         <v>0</v>
@@ -12956,7 +12956,7 @@
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
-          <t>PAVIMENTAÇÃO MG-326 (PONTE NOVA A BARRA LONGA)</t>
+          <t>LMG-629 (RIO PARDO DE MINAS A ENTRº LMG-635) - LOTE 2</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -12982,10 +12982,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>0</v>
+        <v>22254062</v>
       </c>
       <c r="R186" t="n">
-        <v>82286728</v>
+        <v>0</v>
       </c>
       <c r="S186" t="inlineStr"/>
       <c r="T186" t="inlineStr"/>
@@ -13022,7 +13022,7 @@
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
-          <t>PAVIMENTAÇÃO DA MG-314 (ENTR. MG-416 (PEÇANHA) A LMG-744 (COROACI) ENTR. VIRGOLÂNDIA)</t>
+          <t>MELHORAMENTO E PAVIMENTAÇÃO DA RODOVIA LMG-706, SEGMENTO 01: ENTR. BR-040 - VARIANTE (PONTE RIO ESCURO); SEGMENTO 02: VAZAMOR - VAZANTE; SEGMENTO 03: CONTORNO DE VAZANTE - ENTR. BR-354</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -13048,10 +13048,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="R187" t="n">
-        <v>22137718</v>
+        <v>0</v>
       </c>
       <c r="S187" t="inlineStr"/>
       <c r="T187" t="inlineStr"/>
@@ -13088,7 +13088,7 @@
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr">
         <is>
-          <t>PAVIMENTAÇÃO DA RODOVIA MUNICIPAL (SANTA RITA DO ITUETO A ENTR. BR-259 (RESPLENDOR))</t>
+          <t>MONTE CARMELO (ENTR. MG-190) - ENTR. LMG-742 (CHAPADA DE MINAS P/ GRUPIARA), NA LMG-746 - LOTE 01 9,50 KM</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -13114,10 +13114,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="R188" t="n">
-        <v>21757581</v>
+        <v>0</v>
       </c>
       <c r="S188" t="inlineStr"/>
       <c r="T188" t="inlineStr"/>
@@ -13154,7 +13154,7 @@
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
-          <t>RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 21,80 KM</t>
+          <t>PEÇANHA (ENTR. MG-416) - LMG-744 (COROACI), NA MG-314</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -13180,10 +13180,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>0</v>
+        <v>431809</v>
       </c>
       <c r="R189" t="n">
-        <v>8036364</v>
+        <v>0</v>
       </c>
       <c r="S189" t="inlineStr"/>
       <c r="T189" t="inlineStr"/>
@@ -13220,7 +13220,7 @@
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
-          <t>TRECHO ENTRº LMG-690 (PARACATU) - ENTRº ENTRE RIBEIROS (DISTRITO) - ENTRº MG-181 (ESTACA 1250 A 2000)</t>
+          <t>PEDRA BONITA - ENTR. BR-116 E INTERSEÇÃO ENTR. BR-116 (COMPLEMENTAÇÃO), RODOVIA LMG-840</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -13246,10 +13246,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="R190" t="n">
-        <v>14063636</v>
+        <v>0</v>
       </c>
       <c r="S190" t="inlineStr"/>
       <c r="T190" t="inlineStr"/>
@@ -13286,7 +13286,7 @@
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
-          <t>RODOVIA MG-10 - TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 22,50 KM</t>
+          <t>SANTA RITA DO ITUETO - ENTR. BR-259 (RESPLENDOR) (COMPLEMENTAÇÃO), MUNICIPAL AMG-2320</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -13312,10 +13312,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>0</v>
+        <v>14356790</v>
       </c>
       <c r="R191" t="n">
-        <v>8100000</v>
+        <v>0</v>
       </c>
       <c r="S191" t="inlineStr"/>
       <c r="T191" t="inlineStr"/>
@@ -13338,7 +13338,7 @@
         <v>81</v>
       </c>
       <c r="E192" t="n">
-        <v>4275</v>
+        <v>4287</v>
       </c>
       <c r="F192" t="n">
         <v>1</v>
@@ -13352,7 +13352,7 @@
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
-          <t>MELHORAMENTO E PAVIMENTAÇÃO DO CONTORNO DE ANDRADAS</t>
+          <t>Empreendimentos do Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -13378,10 +13378,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="R192" t="n">
-        <v>4804860</v>
+        <v>0</v>
       </c>
       <c r="S192" t="inlineStr"/>
       <c r="T192" t="inlineStr"/>
@@ -13404,7 +13404,7 @@
         <v>81</v>
       </c>
       <c r="E193" t="n">
-        <v>4275</v>
+        <v>4289</v>
       </c>
       <c r="F193" t="n">
         <v>1</v>
@@ -13418,7 +13418,7 @@
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
-          <t>EMPREENDIMENTO EM DEFINIÇÃO JUNTO AO BANCO DO BRASIL - CONTRATO DE FINANCIAMENTO Nº 20/00020-0 (PDMG)</t>
+          <t>Empreendimentos do Acordo Judicial de Brumadinho</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -13444,10 +13444,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="R193" t="n">
-        <v>6000001</v>
+        <v>0</v>
       </c>
       <c r="S193" t="inlineStr"/>
       <c r="T193" t="inlineStr"/>
@@ -13470,7 +13470,7 @@
         <v>81</v>
       </c>
       <c r="E194" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F194" t="n">
         <v>1</v>
@@ -13484,7 +13484,7 @@
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - (LOTE 1), SEGMENTO 1 (0 A 835), 16,70 KM E SEGMENTO 2 (835 A 1250), 8,30 KM</t>
+          <t>04ª URG BARBACENA</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -13510,10 +13510,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>11326937</v>
+        <v>0</v>
       </c>
       <c r="R194" t="n">
-        <v>0</v>
+        <v>12870000</v>
       </c>
       <c r="S194" t="inlineStr"/>
       <c r="T194" t="inlineStr"/>
@@ -13536,7 +13536,7 @@
         <v>81</v>
       </c>
       <c r="E195" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F195" t="n">
         <v>1</v>
@@ -13550,7 +13550,7 @@
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - ESTACA 2550 A 3281</t>
+          <t>20ª URG FORMIGA</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -13576,10 +13576,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>19000000</v>
+        <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>12870000</v>
       </c>
       <c r="S195" t="inlineStr"/>
       <c r="T195" t="inlineStr"/>
@@ -13602,7 +13602,7 @@
         <v>81</v>
       </c>
       <c r="E196" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F196" t="n">
         <v>1</v>
@@ -13616,7 +13616,7 @@
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
-          <t>COMPLEMENTO S JANUÁRIA - PANDEIROS, NA RODOVIA MGC-479</t>
+          <t>28ª URG TEÓFILO OTONI</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -13642,10 +13642,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>74941120</v>
+        <v>0</v>
       </c>
       <c r="R196" t="n">
-        <v>0</v>
+        <v>9575065</v>
       </c>
       <c r="S196" t="inlineStr"/>
       <c r="T196" t="inlineStr"/>
@@ -13668,7 +13668,7 @@
         <v>81</v>
       </c>
       <c r="E197" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F197" t="n">
         <v>1</v>
@@ -13682,7 +13682,7 @@
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
-          <t>CONTORNO DE ANDRADAS (COMPLEMENTAÇÃO) - LOTE 01</t>
+          <t>30ª URG JUIZ DE FORA</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -13708,10 +13708,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>38460000</v>
+        <v>0</v>
       </c>
       <c r="R197" t="n">
-        <v>0</v>
+        <v>12375000</v>
       </c>
       <c r="S197" t="inlineStr"/>
       <c r="T197" t="inlineStr"/>
@@ -13734,7 +13734,7 @@
         <v>81</v>
       </c>
       <c r="E198" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F198" t="n">
         <v>1</v>
@@ -13748,7 +13748,7 @@
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
-          <t>ENTR. MG-181 (BRASILÂNDIA DE MINAS) - ENTR. BR-365 (BURITIZEIRO), NA MG-408 - LOTE 01</t>
+          <t>01ª URG BELO HORIZONTE - SUL</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -13774,10 +13774,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>0</v>
+        <v>14850000</v>
       </c>
       <c r="S198" t="inlineStr"/>
       <c r="T198" t="inlineStr"/>
@@ -13800,7 +13800,7 @@
         <v>81</v>
       </c>
       <c r="E199" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F199" t="n">
         <v>1</v>
@@ -13814,7 +13814,7 @@
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
-          <t>IBERTIOGA - PIEDADE DO RIO GRANDE, NA RODOVIA MG-338</t>
+          <t>01ª URG BELO HORIZONTE - NORTE</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -13840,10 +13840,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>7000000</v>
+        <v>0</v>
       </c>
       <c r="R199" t="n">
-        <v>0</v>
+        <v>14850000</v>
       </c>
       <c r="S199" t="inlineStr"/>
       <c r="T199" t="inlineStr"/>
@@ -13866,7 +13866,7 @@
         <v>81</v>
       </c>
       <c r="E200" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F200" t="n">
         <v>1</v>
@@ -13880,7 +13880,7 @@
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
-          <t>INTERSEÇÃO DE ACESSO A COUTO DE MAGALHÃES DE MINAS, NA MGC-367</t>
+          <t>31ª URG ITUIUTABA</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -13906,10 +13906,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="R200" t="n">
-        <v>0</v>
+        <v>9900000</v>
       </c>
       <c r="S200" t="inlineStr"/>
       <c r="T200" t="inlineStr"/>
@@ -13932,7 +13932,7 @@
         <v>81</v>
       </c>
       <c r="E201" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F201" t="n">
         <v>1</v>
@@ -13946,7 +13946,7 @@
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
-          <t>ITAPAGIPE - ENTR. BR-364 (CAMPINA VERDE), RODOVIA MGC-154</t>
+          <t>PROGRAMA DE MICRORREVESTIMENTO ASFÁLTICO</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -13972,7 +13972,7 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>6121131</v>
+        <v>50000000</v>
       </c>
       <c r="R201" t="n">
         <v>0</v>
@@ -13998,7 +13998,7 @@
         <v>81</v>
       </c>
       <c r="E202" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F202" t="n">
         <v>1</v>
@@ -14012,7 +14012,7 @@
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
-          <t>MG-631 - SÃO JOÃO DA PONTE A CAPITÃO ENÉAS</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 1</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -14038,7 +14038,7 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>1000000</v>
+        <v>8151612</v>
       </c>
       <c r="R202" t="n">
         <v>0</v>
@@ -14064,7 +14064,7 @@
         <v>81</v>
       </c>
       <c r="E203" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F203" t="n">
         <v>1</v>
@@ -14078,7 +14078,7 @@
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
-          <t>MELHORAMENTO E PAVIMENTAÇÃO DA RODOVIA LMG-706, SEGMENTO 01: ENTR. BR-040 - VARIANTE (PONTE RIO ESCURO); SEGMENTO 02: VAZAMOR - VAZANTE; SEGMENTO 03: CONTORNO DE VAZANTE - ENTR. BR-354</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 2</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -14104,7 +14104,7 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>1000000</v>
+        <v>7488179</v>
       </c>
       <c r="R203" t="n">
         <v>0</v>
@@ -14130,7 +14130,7 @@
         <v>81</v>
       </c>
       <c r="E204" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F204" t="n">
         <v>1</v>
@@ -14144,7 +14144,7 @@
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
-          <t>ACESSO AO PRESÍDIO DE ITURAMA</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 3</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -14170,7 +14170,7 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>1000000</v>
+        <v>9608804</v>
       </c>
       <c r="R204" t="n">
         <v>0</v>
@@ -14196,7 +14196,7 @@
         <v>81</v>
       </c>
       <c r="E205" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F205" t="n">
         <v>1</v>
@@ -14210,7 +14210,7 @@
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
-          <t>MONTE CARMELO (ENTR. MG-190) - ENTR. LMG-742 (CHAPADA DE MINAS P/ GRUPIARA), NA LMG-746 - LOTE 01 9,50 KM</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 4</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -14236,7 +14236,7 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>1000000</v>
+        <v>8168067</v>
       </c>
       <c r="R205" t="n">
         <v>0</v>
@@ -14262,7 +14262,7 @@
         <v>81</v>
       </c>
       <c r="E206" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F206" t="n">
         <v>1</v>
@@ -14276,7 +14276,7 @@
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
-          <t>MONTE CARMELO A CHAPADA DE MINAS - LOTE 2</t>
+          <t>CONSERVAÇÃO DA MALHA VIÁRIA DAS 40ª URG`S</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -14302,7 +14302,7 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>1000000</v>
+        <v>571386707</v>
       </c>
       <c r="R206" t="n">
         <v>0</v>
@@ -14328,7 +14328,7 @@
         <v>81</v>
       </c>
       <c r="E207" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F207" t="n">
         <v>1</v>
@@ -14342,7 +14342,7 @@
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
-          <t>NATALÂNDIA - ENTR. BR-251, NA LMG-622</t>
+          <t>MANUTENÇÃO LINHA VERDE E COMPLEXO CIDADE ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -14368,7 +14368,7 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>1000000</v>
+        <v>15000000</v>
       </c>
       <c r="R207" t="n">
         <v>0</v>
@@ -14394,7 +14394,7 @@
         <v>81</v>
       </c>
       <c r="E208" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F208" t="n">
         <v>1</v>
@@ -14408,7 +14408,7 @@
       <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr">
         <is>
-          <t>PEÇANHA (ENTR. MG-416) - LMG-744 (COROACI), NA MG-314</t>
+          <t>REALINHAMENTO DE PREÇOS DO FORNECIMENTO DO MATERIAL BETUMINOSO</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -14434,7 +14434,7 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>431808</v>
+        <v>1406178</v>
       </c>
       <c r="R208" t="n">
         <v>0</v>
@@ -14460,7 +14460,7 @@
         <v>81</v>
       </c>
       <c r="E209" t="n">
-        <v>4275</v>
+        <v>4293</v>
       </c>
       <c r="F209" t="n">
         <v>1</v>
@@ -14474,7 +14474,7 @@
       <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr">
         <is>
-          <t>PEDRA AZUL (ENTR. MG-105) - DISTRITO DE PEDRA GRANDE - ALMENARA, MG-251/MG-406, LOTE 01 35 KM</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA EXECUÇÃO DE SERVIÇOS DE NATUREZA CONTÍNUA DE SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, EM REGIME DE EMPREITADA POR PREÇO UNITÁRIO, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -14500,7 +14500,7 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>1000000</v>
+        <v>19448656</v>
       </c>
       <c r="R209" t="n">
         <v>0</v>
@@ -14526,7 +14526,7 @@
         <v>81</v>
       </c>
       <c r="E210" t="n">
-        <v>4275</v>
+        <v>4385</v>
       </c>
       <c r="F210" t="n">
         <v>1</v>
@@ -14540,7 +14540,7 @@
       <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
-          <t>PEDRA BONITA - ENTR. BR-116 E INTERSEÇÃO ENTR. BR-116 (COMPLEMENTAÇÃO), RODOVIA LMG-840</t>
+          <t>RECUPERAÇÃO FUNCIONAL MG-232 (BRAÚNAS (DIV. 40ª/ 2ª) - IPATINGA)</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -14592,7 +14592,7 @@
         <v>81</v>
       </c>
       <c r="E211" t="n">
-        <v>4275</v>
+        <v>4385</v>
       </c>
       <c r="F211" t="n">
         <v>1</v>
@@ -14606,7 +14606,7 @@
       <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
-          <t>PRESIDENTE OLEGÁRIO - GALENA, NA LMG-726</t>
+          <t>RECUPERAÇÃO FUNCIONAL MGC-259 ( SABINÓPOLIS - SERRO, GUANHÃES - SABINÓPOLIS E ALVORADA MINAS - SERRO) *</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -14632,7 +14632,7 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>1000000</v>
+        <v>30000000</v>
       </c>
       <c r="R211" t="n">
         <v>0</v>
@@ -14658,7 +14658,7 @@
         <v>81</v>
       </c>
       <c r="E212" t="n">
-        <v>4275</v>
+        <v>4385</v>
       </c>
       <c r="F212" t="n">
         <v>1</v>
@@ -14672,7 +14672,7 @@
       <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr">
         <is>
-          <t>SANTA RITA DO ITUETO - ENTR. BR-259 (RESPLENDOR) (COMPLEMENTAÇÃO), MUNICIPAL AMG-2320</t>
+          <t>RECUPERAÇÃO FUNCIONAL MGC-455 (PIRAJUBA - ENTRº BR-364 (PLANURA)</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -14698,7 +14698,7 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>14356788</v>
+        <v>1000000</v>
       </c>
       <c r="R212" t="n">
         <v>0</v>
@@ -14721,10 +14721,10 @@
         <v>782</v>
       </c>
       <c r="D213" t="n">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="E213" t="n">
-        <v>4275</v>
+        <v>4280</v>
       </c>
       <c r="F213" t="n">
         <v>1</v>
@@ -14738,7 +14738,7 @@
       <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
-          <t>SÃO DOMINGOS DO PRATA - DOM SILVÉRIO, NA MGC-120</t>
+          <t>PONTO CRÍTICO: ENTRº BR-040 (BARREIRA DOTRIUNFO) - ENTRº MG-353 (GOIANÁ)</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -14764,7 +14764,7 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>100000</v>
+        <v>4000000</v>
       </c>
       <c r="R213" t="n">
         <v>0</v>
@@ -14787,10 +14787,10 @@
         <v>782</v>
       </c>
       <c r="D214" t="n">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="E214" t="n">
-        <v>4275</v>
+        <v>4280</v>
       </c>
       <c r="F214" t="n">
         <v>1</v>
@@ -14804,7 +14804,7 @@
       <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
-          <t>UNAÍ (ENTR. BR-251) - PARACATU (ENTR. BR-040) (ESTRADA DO MUNDO NOVO), NA LMG-658 - LOTE 01</t>
+          <t>PONTO CRÍTICO: ENTRº P/ MARIA DA FÉ - INÍCIO DO PERÍMETRO URBANO DE ITAJUBÁ (2  PONTOS)</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -14830,7 +14830,7 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>1000000</v>
+        <v>4000000</v>
       </c>
       <c r="R214" t="n">
         <v>0</v>
@@ -14853,10 +14853,10 @@
         <v>782</v>
       </c>
       <c r="D215" t="n">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="E215" t="n">
-        <v>4275</v>
+        <v>4280</v>
       </c>
       <c r="F215" t="n">
         <v>1</v>
@@ -14870,7 +14870,7 @@
       <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr">
         <is>
-          <t>ARAÇAÍ - SETE LAGOAS, RODOVIA MUNICIPAL</t>
+          <t>PONTO CRÍTICO: PALMÓPOLIS - RIO DO PRADO (6 PONTOS)/ PONTE SOBRE O RIBEIRÃO JOSÉ FERREIRA (1 PONTO)</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -14896,7 +14896,7 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>35359852</v>
+        <v>1000000</v>
       </c>
       <c r="R215" t="n">
         <v>0</v>
@@ -14910,19 +14910,19 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>2301</v>
+        <v>2311</v>
       </c>
       <c r="B216" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C216" t="n">
-        <v>782</v>
+        <v>363</v>
       </c>
       <c r="D216" t="n">
-        <v>81</v>
+        <v>7</v>
       </c>
       <c r="E216" t="n">
-        <v>4275</v>
+        <v>4006</v>
       </c>
       <c r="F216" t="n">
         <v>1</v>
@@ -14936,33 +14936,39 @@
       <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
-          <t>ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO, NA MG-414</t>
+          <t>Construção da escola do Brasil Profissionalizado no município de Unaí-MG</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L216" t="inlineStr"/>
-      <c r="M216" t="inlineStr"/>
+          <t>PARALISADO</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>METRO QUADRADO</t>
+        </is>
+      </c>
+      <c r="M216" t="n">
+        <v>5000</v>
+      </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>UNAÍ</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>29030000</v>
+        <v>5000000</v>
       </c>
       <c r="R216" t="n">
         <v>0</v>
@@ -14976,19 +14982,19 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>2301</v>
+        <v>2321</v>
       </c>
       <c r="B217" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C217" t="n">
-        <v>782</v>
+        <v>302</v>
       </c>
       <c r="D217" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E217" t="n">
-        <v>4275</v>
+        <v>4222</v>
       </c>
       <c r="F217" t="n">
         <v>1</v>
@@ -15002,12 +15008,12 @@
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
-          <t>CAMPO VERDE (DISTRITO E NOVORIZONTE) - FRUTA DE LEITE, NA LMG-626 (LOTE 01 TSD)</t>
+          <t xml:space="preserve">Projetos em unidade diversas </t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L217" t="inlineStr"/>
@@ -15019,16 +15025,16 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>1000000</v>
+        <v>800291</v>
       </c>
       <c r="R217" t="n">
         <v>0</v>
@@ -15042,19 +15048,19 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>2301</v>
+        <v>2321</v>
       </c>
       <c r="B218" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C218" t="n">
-        <v>782</v>
+        <v>302</v>
       </c>
       <c r="D218" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E218" t="n">
-        <v>4275</v>
+        <v>4222</v>
       </c>
       <c r="F218" t="n">
         <v>1</v>
@@ -15068,12 +15074,12 @@
       <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
-          <t>JABOTICATUBAS - LAGOA SANTA, RODOVIA MUNICIPAL - LOTE 01</t>
+          <t xml:space="preserve">Projetos em unidade diversas </t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L218" t="inlineStr"/>
@@ -15085,16 +15091,16 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>3541727</v>
+        <v>174673</v>
       </c>
       <c r="R218" t="n">
         <v>0</v>
@@ -15108,19 +15114,19 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>2301</v>
+        <v>2321</v>
       </c>
       <c r="B219" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C219" t="n">
-        <v>782</v>
+        <v>302</v>
       </c>
       <c r="D219" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E219" t="n">
-        <v>4275</v>
+        <v>4222</v>
       </c>
       <c r="F219" t="n">
         <v>1</v>
@@ -15131,10 +15137,12 @@
       <c r="H219" t="n">
         <v>218</v>
       </c>
-      <c r="I219" t="inlineStr"/>
+      <c r="I219" t="n">
+        <v>11877</v>
+      </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t xml:space="preserve">LMG-629 (RIO PARDO DE MINAS A ENTRº LMG-635) - LOTE 2 </t>
+          <t>Contrato a obra de reforma e ampliação</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -15151,16 +15159,16 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Barbacena</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>SÃO JOÃO DEL REI</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>31280000</v>
+        <v>1088908</v>
       </c>
       <c r="R219" t="n">
         <v>0</v>
@@ -15174,19 +15182,19 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>2301</v>
+        <v>2361</v>
       </c>
       <c r="B220" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C220" t="n">
-        <v>782</v>
+        <v>274</v>
       </c>
       <c r="D220" t="n">
-        <v>81</v>
+        <v>767</v>
       </c>
       <c r="E220" t="n">
-        <v>4287</v>
+        <v>2114</v>
       </c>
       <c r="F220" t="n">
         <v>1</v>
@@ -15200,7 +15208,7 @@
       <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Empreendimentos do Acordo Judicial do Rio Doce</t>
+          <t>Possível obras de adequação da sede.</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -15217,19 +15225,19 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="R220" t="n">
-        <v>0</v>
+        <v>2754406</v>
       </c>
       <c r="S220" t="inlineStr"/>
       <c r="T220" t="inlineStr"/>
@@ -15240,19 +15248,19 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>2301</v>
+        <v>2371</v>
       </c>
       <c r="B221" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C221" t="n">
-        <v>782</v>
+        <v>609</v>
       </c>
       <c r="D221" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E221" t="n">
-        <v>4289</v>
+        <v>4238</v>
       </c>
       <c r="F221" t="n">
         <v>1</v>
@@ -15266,7 +15274,7 @@
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Empreendimentos do Acordo Judicial de Brumadinho</t>
+          <t>Reestruturação física e ampliação do Laboratório de Química Agropecuária do Instituto Mineiro de Agropecuária - IMA</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -15283,16 +15291,16 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>1000</v>
+        <v>8311374</v>
       </c>
       <c r="R221" t="n">
         <v>0</v>
@@ -15306,19 +15314,19 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>2301</v>
+        <v>2421</v>
       </c>
       <c r="B222" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C222" t="n">
-        <v>782</v>
+        <v>544</v>
       </c>
       <c r="D222" t="n">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="E222" t="n">
-        <v>4293</v>
+        <v>1016</v>
       </c>
       <c r="F222" t="n">
         <v>1</v>
@@ -15332,7 +15340,7 @@
       <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr">
         <is>
-          <t>PROGRAMA DE MICRORREVESTIMENTO ASFÁLTICO</t>
+          <t>Perfuração de Sistemas de Abastecimento de Agua conforme demanda dos municípios atendidos pelo IDENE</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -15349,16 +15357,16 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>10000000</v>
+        <v>477508</v>
       </c>
       <c r="R222" t="n">
         <v>0</v>
@@ -15372,19 +15380,19 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>2301</v>
+        <v>3051</v>
       </c>
       <c r="B223" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C223" t="n">
-        <v>782</v>
+        <v>364</v>
       </c>
       <c r="D223" t="n">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="E223" t="n">
-        <v>4293</v>
+        <v>4016</v>
       </c>
       <c r="F223" t="n">
         <v>1</v>
@@ -15398,7 +15406,7 @@
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
-          <t>REALINHAMENTO DE PREÇOS DO FORNECIMENTO DO MATERIAL BETUMINOSO</t>
+          <t>Instalações do curso de Agropecuária de Precisão, com 1.070 m² de área total, além de 5 unidades de tratamento de águas residuárias.</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -15424,7 +15432,7 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>1406178</v>
+        <v>4825656</v>
       </c>
       <c r="R223" t="n">
         <v>0</v>
@@ -15438,19 +15446,19 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>2301</v>
+        <v>3051</v>
       </c>
       <c r="B224" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C224" t="n">
-        <v>782</v>
+        <v>364</v>
       </c>
       <c r="D224" t="n">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="E224" t="n">
-        <v>4293</v>
+        <v>4016</v>
       </c>
       <c r="F224" t="n">
         <v>1</v>
@@ -15464,7 +15472,7 @@
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr">
         <is>
-          <t>04ª URG BARBACENA</t>
+          <t>Construção de novas instalações no Instituto Tecnológico de Agropecuária de Pitangui - ITAP, totalizando 3.214 m², para salas de aula, plantas-piloto de produção e laboratórios de apoio.</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -15490,10 +15498,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>0</v>
+        <v>12649000</v>
       </c>
       <c r="R224" t="n">
-        <v>12870000</v>
+        <v>0</v>
       </c>
       <c r="S224" t="inlineStr"/>
       <c r="T224" t="inlineStr"/>
@@ -15504,19 +15512,19 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>2301</v>
+        <v>3051</v>
       </c>
       <c r="B225" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C225" t="n">
-        <v>782</v>
+        <v>364</v>
       </c>
       <c r="D225" t="n">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="E225" t="n">
-        <v>4293</v>
+        <v>4016</v>
       </c>
       <c r="F225" t="n">
         <v>1</v>
@@ -15530,7 +15538,7 @@
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr">
         <is>
-          <t>20ª URG FORMIGA</t>
+          <t xml:space="preserve">Reforma do edifício histórico do Instituto de Laticínios Cândido Tostes, localizado no município dde juiz de Fora. </t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -15556,10 +15564,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>0</v>
+        <v>3715000</v>
       </c>
       <c r="R225" t="n">
-        <v>12870000</v>
+        <v>0</v>
       </c>
       <c r="S225" t="inlineStr"/>
       <c r="T225" t="inlineStr"/>
@@ -15570,19 +15578,19 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>2301</v>
+        <v>3051</v>
       </c>
       <c r="B226" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C226" t="n">
-        <v>782</v>
+        <v>571</v>
       </c>
       <c r="D226" t="n">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="E226" t="n">
-        <v>4293</v>
+        <v>4018</v>
       </c>
       <c r="F226" t="n">
         <v>1</v>
@@ -15596,7 +15604,7 @@
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
-          <t>28ª URG TEÓFILO OTONI</t>
+          <t>Melhoria na infraestrutura das unidades de pesquisa.</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -15625,7 +15633,7 @@
         <v>0</v>
       </c>
       <c r="R226" t="n">
-        <v>9575065</v>
+        <v>250000</v>
       </c>
       <c r="S226" t="inlineStr"/>
       <c r="T226" t="inlineStr"/>
@@ -15636,19 +15644,19 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B227" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C227" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D227" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E227" t="n">
-        <v>4293</v>
+        <v>2091</v>
       </c>
       <c r="F227" t="n">
         <v>1</v>
@@ -15659,39 +15667,47 @@
       <c r="H227" t="n">
         <v>226</v>
       </c>
-      <c r="I227" t="inlineStr"/>
+      <c r="I227" t="n">
+        <v>12054</v>
+      </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>30ª URG JUIZ DE FORA</t>
+          <t xml:space="preserve"> Construção do novo prédio do Fórum da Comarca de Betim/MG</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L227" t="inlineStr"/>
-      <c r="M227" t="inlineStr"/>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M227" t="n">
+        <v>1</v>
+      </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q227" t="n">
         <v>0</v>
       </c>
       <c r="R227" t="n">
-        <v>12375000</v>
+        <v>11016496</v>
       </c>
       <c r="S227" t="inlineStr"/>
       <c r="T227" t="inlineStr"/>
@@ -15702,19 +15718,19 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B228" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C228" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D228" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E228" t="n">
-        <v>4293</v>
+        <v>2091</v>
       </c>
       <c r="F228" t="n">
         <v>1</v>
@@ -15725,39 +15741,47 @@
       <c r="H228" t="n">
         <v>227</v>
       </c>
-      <c r="I228" t="inlineStr"/>
+      <c r="I228" t="n">
+        <v>12806</v>
+      </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>01ª URG BELO HORIZONTE - SUL</t>
+          <t>Campo Belo/MG - Construção do novo Fórum da Comarca de Campo Belo</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L228" t="inlineStr"/>
-      <c r="M228" t="inlineStr"/>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M228" t="n">
+        <v>1</v>
+      </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>CAMPO BELO</t>
         </is>
       </c>
       <c r="Q228" t="n">
         <v>0</v>
       </c>
       <c r="R228" t="n">
-        <v>14850000</v>
+        <v>19994210</v>
       </c>
       <c r="S228" t="inlineStr"/>
       <c r="T228" t="inlineStr"/>
@@ -15768,19 +15792,19 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B229" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C229" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D229" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E229" t="n">
-        <v>4293</v>
+        <v>2091</v>
       </c>
       <c r="F229" t="n">
         <v>1</v>
@@ -15791,39 +15815,47 @@
       <c r="H229" t="n">
         <v>228</v>
       </c>
-      <c r="I229" t="inlineStr"/>
+      <c r="I229" t="n">
+        <v>12638</v>
+      </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>01ª URG BELO HORIZONTE - NORTE</t>
+          <t>Obra de construção do novo Fórum da Comarca de Carangola.</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L229" t="inlineStr"/>
-      <c r="M229" t="inlineStr"/>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M229" t="n">
+        <v>1</v>
+      </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>CARANGOLA</t>
         </is>
       </c>
       <c r="Q229" t="n">
         <v>0</v>
       </c>
       <c r="R229" t="n">
-        <v>14850000</v>
+        <v>12843388</v>
       </c>
       <c r="S229" t="inlineStr"/>
       <c r="T229" t="inlineStr"/>
@@ -15834,19 +15866,19 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B230" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C230" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D230" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E230" t="n">
-        <v>4293</v>
+        <v>2091</v>
       </c>
       <c r="F230" t="n">
         <v>1</v>
@@ -15857,39 +15889,47 @@
       <c r="H230" t="n">
         <v>229</v>
       </c>
-      <c r="I230" t="inlineStr"/>
+      <c r="I230" t="n">
+        <v>12400</v>
+      </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>31ª URG ITUIUTABA</t>
+          <t xml:space="preserve"> Contrato a execução da obra de reforma e ampliação do Fórum da Comarca de Ipatinga/MG</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L230" t="inlineStr"/>
-      <c r="M230" t="inlineStr"/>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M230" t="n">
+        <v>1</v>
+      </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>IPATINGA</t>
         </is>
       </c>
       <c r="Q230" t="n">
         <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>9900000</v>
+        <v>18849069</v>
       </c>
       <c r="S230" t="inlineStr"/>
       <c r="T230" t="inlineStr"/>
@@ -15900,19 +15940,19 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B231" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C231" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D231" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E231" t="n">
-        <v>4293</v>
+        <v>2091</v>
       </c>
       <c r="F231" t="n">
         <v>1</v>
@@ -15923,39 +15963,47 @@
       <c r="H231" t="n">
         <v>230</v>
       </c>
-      <c r="I231" t="inlineStr"/>
+      <c r="I231" t="n">
+        <v>12288</v>
+      </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>CONSERVAÇÃO DA MALHA VIÁRIA DAS 40ª URG`S</t>
+          <t xml:space="preserve"> Reforma e Ampliação do Fórum da Comarca de Monte Belo/MG</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L231" t="inlineStr"/>
-      <c r="M231" t="inlineStr"/>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M231" t="n">
+        <v>1</v>
+      </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>MONTE BELO</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>654124898</v>
+        <v>0</v>
       </c>
       <c r="R231" t="n">
-        <v>0</v>
+        <v>1950000</v>
       </c>
       <c r="S231" t="inlineStr"/>
       <c r="T231" t="inlineStr"/>
@@ -15966,19 +16014,19 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B232" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C232" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D232" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E232" t="n">
-        <v>4293</v>
+        <v>2091</v>
       </c>
       <c r="F232" t="n">
         <v>1</v>
@@ -15989,39 +16037,47 @@
       <c r="H232" t="n">
         <v>231</v>
       </c>
-      <c r="I232" t="inlineStr"/>
+      <c r="I232" t="n">
+        <v>12816</v>
+      </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA EXECUÇÃO DE SERVIÇOS DE NATUREZA CONTÍNUA DE SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, EM REGIME DE EMPREITADA POR PREÇO UNITÁRIO, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE</t>
+          <t>Obra de construção do novo Fórum da Comarca de Pirapora/MG</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L232" t="inlineStr"/>
-      <c r="M232" t="inlineStr"/>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M232" t="n">
+        <v>1</v>
+      </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>PIRAPORA</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>30767861</v>
+        <v>0</v>
       </c>
       <c r="R232" t="n">
-        <v>0</v>
+        <v>22776109</v>
       </c>
       <c r="S232" t="inlineStr"/>
       <c r="T232" t="inlineStr"/>
@@ -16032,19 +16088,19 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B233" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C233" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D233" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E233" t="n">
-        <v>4293</v>
+        <v>2091</v>
       </c>
       <c r="F233" t="n">
         <v>1</v>
@@ -16055,39 +16111,47 @@
       <c r="H233" t="n">
         <v>232</v>
       </c>
-      <c r="I233" t="inlineStr"/>
+      <c r="I233" t="n">
+        <v>12781</v>
+      </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO LINHA VERDE E COMPLEXO CIDADE ADMINISTRATIVA</t>
+          <t>Construção do novo fórum da Comarca de São Gonçalo do Sapucaí/MG</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L233" t="inlineStr"/>
-      <c r="M233" t="inlineStr"/>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M233" t="n">
+        <v>1</v>
+      </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>SÃO GONÇALO DO SAPUCAÍ</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>19976964</v>
+        <v>0</v>
       </c>
       <c r="R233" t="n">
-        <v>0</v>
+        <v>14670005</v>
       </c>
       <c r="S233" t="inlineStr"/>
       <c r="T233" t="inlineStr"/>
@@ -16098,19 +16162,19 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B234" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C234" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D234" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E234" t="n">
-        <v>4293</v>
+        <v>2091</v>
       </c>
       <c r="F234" t="n">
         <v>1</v>
@@ -16121,39 +16185,47 @@
       <c r="H234" t="n">
         <v>233</v>
       </c>
-      <c r="I234" t="inlineStr"/>
+      <c r="I234" t="n">
+        <v>12799</v>
+      </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 1</t>
+          <t xml:space="preserve">Construção do novo Fórum da Comarca de Timóteo/MG </t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr"/>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M234" t="n">
+        <v>1</v>
+      </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>TIMÓTEO</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>12895888</v>
+        <v>0</v>
       </c>
       <c r="R234" t="n">
-        <v>0</v>
+        <v>19506288</v>
       </c>
       <c r="S234" t="inlineStr"/>
       <c r="T234" t="inlineStr"/>
@@ -16164,19 +16236,19 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B235" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C235" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D235" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E235" t="n">
-        <v>4293</v>
+        <v>2091</v>
       </c>
       <c r="F235" t="n">
         <v>1</v>
@@ -16187,10 +16259,12 @@
       <c r="H235" t="n">
         <v>234</v>
       </c>
-      <c r="I235" t="inlineStr"/>
+      <c r="I235" t="n">
+        <v>12833</v>
+      </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 2</t>
+          <t>Obra de construção do novo Fórum da Comarca de Rio Novo.</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -16198,28 +16272,34 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L235" t="inlineStr"/>
-      <c r="M235" t="inlineStr"/>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M235" t="n">
+        <v>1</v>
+      </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>RIO NOVO</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>11846334</v>
+        <v>0</v>
       </c>
       <c r="R235" t="n">
-        <v>0</v>
+        <v>4976096</v>
       </c>
       <c r="S235" t="inlineStr"/>
       <c r="T235" t="inlineStr"/>
@@ -16230,19 +16310,19 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B236" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C236" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D236" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E236" t="n">
-        <v>4293</v>
+        <v>2091</v>
       </c>
       <c r="F236" t="n">
         <v>1</v>
@@ -16253,10 +16333,12 @@
       <c r="H236" t="n">
         <v>235</v>
       </c>
-      <c r="I236" t="inlineStr"/>
+      <c r="I236" t="n">
+        <v>12629</v>
+      </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 3</t>
+          <t>Obra de construção do novo Fórum da Comarca de Luz.</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -16264,28 +16346,34 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L236" t="inlineStr"/>
-      <c r="M236" t="inlineStr"/>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M236" t="n">
+        <v>1</v>
+      </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>LUZ</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>15201174</v>
+        <v>0</v>
       </c>
       <c r="R236" t="n">
-        <v>0</v>
+        <v>7654409</v>
       </c>
       <c r="S236" t="inlineStr"/>
       <c r="T236" t="inlineStr"/>
@@ -16296,19 +16384,19 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B237" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C237" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D237" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E237" t="n">
-        <v>4293</v>
+        <v>2091</v>
       </c>
       <c r="F237" t="n">
         <v>1</v>
@@ -16319,39 +16407,47 @@
       <c r="H237" t="n">
         <v>236</v>
       </c>
-      <c r="I237" t="inlineStr"/>
+      <c r="I237" t="n">
+        <v>12607</v>
+      </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 4</t>
+          <t>Reforma e ampliação do Fórum da Comarca de Sete Lagoas/MG.</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L237" t="inlineStr"/>
-      <c r="M237" t="inlineStr"/>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M237" t="n">
+        <v>1</v>
+      </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>SETE LAGOAS</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>12921920</v>
+        <v>0</v>
       </c>
       <c r="R237" t="n">
-        <v>0</v>
+        <v>32235085</v>
       </c>
       <c r="S237" t="inlineStr"/>
       <c r="T237" t="inlineStr"/>
@@ -16362,19 +16458,19 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B238" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C238" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D238" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E238" t="n">
-        <v>4385</v>
+        <v>2091</v>
       </c>
       <c r="F238" t="n">
         <v>1</v>
@@ -16385,39 +16481,47 @@
       <c r="H238" t="n">
         <v>237</v>
       </c>
-      <c r="I238" t="inlineStr"/>
+      <c r="I238" t="n">
+        <v>12639</v>
+      </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO FUNCIONAL MG-232 (BRAÚNAS (DIV. 40ª/ 2ª) - IPATINGA)</t>
+          <t>Obra de construção do novo Fórum da Comarca de Três Pontas</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L238" t="inlineStr"/>
-      <c r="M238" t="inlineStr"/>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M238" t="n">
+        <v>1</v>
+      </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>TRÊS PONTAS</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>6382601</v>
+        <v>0</v>
       </c>
       <c r="R238" t="n">
-        <v>0</v>
+        <v>9489687</v>
       </c>
       <c r="S238" t="inlineStr"/>
       <c r="T238" t="inlineStr"/>
@@ -16428,19 +16532,19 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B239" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C239" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D239" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E239" t="n">
-        <v>4385</v>
+        <v>2091</v>
       </c>
       <c r="F239" t="n">
         <v>1</v>
@@ -16451,10 +16555,12 @@
       <c r="H239" t="n">
         <v>238</v>
       </c>
-      <c r="I239" t="inlineStr"/>
+      <c r="I239" t="n">
+        <v>11547</v>
+      </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO FUNCIONAL MGC-259 ( SABINÓPOLIS - SERRO, GUANHÃES - SABINÓPOLIS E ALVORADA MINAS - SERRO) *</t>
+          <t>RETOMADA DA OBRA DE CONSTRUÇÃO DO NOVO PRÉDIO DO FÓRUM DA COMARCA DE ITAJUBÁ/MG</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -16462,28 +16568,34 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr"/>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M239" t="n">
+        <v>1</v>
+      </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>ITAJUBÁ</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>30000000</v>
+        <v>0</v>
       </c>
       <c r="R239" t="n">
-        <v>0</v>
+        <v>9366263</v>
       </c>
       <c r="S239" t="inlineStr"/>
       <c r="T239" t="inlineStr"/>
@@ -16494,19 +16606,19 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B240" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C240" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D240" t="n">
-        <v>81</v>
+        <v>706</v>
       </c>
       <c r="E240" t="n">
-        <v>4385</v>
+        <v>2091</v>
       </c>
       <c r="F240" t="n">
         <v>1</v>
@@ -16517,10 +16629,12 @@
       <c r="H240" t="n">
         <v>239</v>
       </c>
-      <c r="I240" t="inlineStr"/>
+      <c r="I240" t="n">
+        <v>12856</v>
+      </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO FUNCIONAL MGC-455 (PIRAJUBA - ENTRº BR-364 (PLANURA)</t>
+          <t>Retomada da obra de construção do novo Fórum da Comarca de Poços de Caldas.</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -16528,28 +16642,34 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L240" t="inlineStr"/>
-      <c r="M240" t="inlineStr"/>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M240" t="n">
+        <v>1</v>
+      </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>POÇOS DE CALDAS</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>4000000</v>
+        <v>0</v>
       </c>
       <c r="R240" t="n">
-        <v>0</v>
+        <v>11009635</v>
       </c>
       <c r="S240" t="inlineStr"/>
       <c r="T240" t="inlineStr"/>
@@ -16560,19 +16680,19 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B241" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C241" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D241" t="n">
-        <v>139</v>
+        <v>706</v>
       </c>
       <c r="E241" t="n">
-        <v>4280</v>
+        <v>2091</v>
       </c>
       <c r="F241" t="n">
         <v>1</v>
@@ -16583,10 +16703,12 @@
       <c r="H241" t="n">
         <v>240</v>
       </c>
-      <c r="I241" t="inlineStr"/>
+      <c r="I241" t="n">
+        <v>12344</v>
+      </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: ENTRº BR-040 (BARREIRA DOTRIUNFO) - ENTRº MG-353 (GOIANÁ)</t>
+          <t>Construção do novo prédio do Fórum da Comarca de Camanducaia/MG</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -16594,28 +16716,34 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L241" t="inlineStr"/>
-      <c r="M241" t="inlineStr"/>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M241" t="n">
+        <v>1</v>
+      </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>CAMANDUCAIA</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>4000000</v>
+        <v>0</v>
       </c>
       <c r="R241" t="n">
-        <v>0</v>
+        <v>4627222</v>
       </c>
       <c r="S241" t="inlineStr"/>
       <c r="T241" t="inlineStr"/>
@@ -16626,19 +16754,19 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B242" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C242" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D242" t="n">
-        <v>139</v>
+        <v>706</v>
       </c>
       <c r="E242" t="n">
-        <v>4280</v>
+        <v>2091</v>
       </c>
       <c r="F242" t="n">
         <v>1</v>
@@ -16652,7 +16780,7 @@
       <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: ENTRº MGC-265 (RIO POMBA) - PONTE RIO POMBA</t>
+          <t>Obra de construção do novo Fórum da Comarca de São João do Paraíso</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -16660,28 +16788,34 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L242" t="inlineStr"/>
-      <c r="M242" t="inlineStr"/>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M242" t="n">
+        <v>1</v>
+      </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>SÃO JOÃO DO PARAÍSO</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>470000</v>
+        <v>0</v>
       </c>
       <c r="R242" t="n">
-        <v>0</v>
+        <v>7290196</v>
       </c>
       <c r="S242" t="inlineStr"/>
       <c r="T242" t="inlineStr"/>
@@ -16692,19 +16826,19 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B243" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C243" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D243" t="n">
-        <v>139</v>
+        <v>706</v>
       </c>
       <c r="E243" t="n">
-        <v>4280</v>
+        <v>2091</v>
       </c>
       <c r="F243" t="n">
         <v>1</v>
@@ -16718,7 +16852,7 @@
       <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: ENTRº P/ MARIA DA FÉ - INÍCIO DO PERÍMETRO URBANO DE ITAJUBÁ (2  PONTOS)</t>
+          <t>Implantação do Fórum Digital no município de Brasilândia de Minas</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -16726,28 +16860,34 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L243" t="inlineStr"/>
-      <c r="M243" t="inlineStr"/>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M243" t="n">
+        <v>1</v>
+      </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BRASILÂNDIA DE MINAS</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>4000000</v>
+        <v>0</v>
       </c>
       <c r="R243" t="n">
-        <v>0</v>
+        <v>1373680</v>
       </c>
       <c r="S243" t="inlineStr"/>
       <c r="T243" t="inlineStr"/>
@@ -16758,19 +16898,19 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B244" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C244" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D244" t="n">
-        <v>139</v>
+        <v>706</v>
       </c>
       <c r="E244" t="n">
-        <v>4280</v>
+        <v>2091</v>
       </c>
       <c r="F244" t="n">
         <v>1</v>
@@ -16784,7 +16924,7 @@
       <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: PALMÓPOLIS - RIO DO PRADO (6 PONTOS)/ PONTE SOBRE O RIBEIRÃO JOSÉ FERREIRA (1 PONTO)</t>
+          <t>Implantação do Fórum Digital no município de São Gonçalo do Abaeté</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -16792,28 +16932,34 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L244" t="inlineStr"/>
-      <c r="M244" t="inlineStr"/>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M244" t="n">
+        <v>1</v>
+      </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>SÃO GONÇALO DO ABAETÉ</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="R244" t="n">
-        <v>0</v>
+        <v>1373680</v>
       </c>
       <c r="S244" t="inlineStr"/>
       <c r="T244" t="inlineStr"/>
@@ -16824,19 +16970,19 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B245" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C245" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D245" t="n">
-        <v>139</v>
+        <v>706</v>
       </c>
       <c r="E245" t="n">
-        <v>4280</v>
+        <v>2091</v>
       </c>
       <c r="F245" t="n">
         <v>1</v>
@@ -16850,7 +16996,7 @@
       <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: RODEIRO - ENTRº MG-285</t>
+          <t>Implantação do Fórum Digital no município de Ponto Chique</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -16858,28 +17004,34 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L245" t="inlineStr"/>
-      <c r="M245" t="inlineStr"/>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M245" t="n">
+        <v>1</v>
+      </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>PONTO CHIQUE</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>420000</v>
+        <v>0</v>
       </c>
       <c r="R245" t="n">
-        <v>0</v>
+        <v>1760000</v>
       </c>
       <c r="S245" t="inlineStr"/>
       <c r="T245" t="inlineStr"/>
@@ -16890,19 +17042,19 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>2301</v>
+        <v>4031</v>
       </c>
       <c r="B246" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C246" t="n">
-        <v>782</v>
+        <v>61</v>
       </c>
       <c r="D246" t="n">
-        <v>139</v>
+        <v>706</v>
       </c>
       <c r="E246" t="n">
-        <v>4280</v>
+        <v>2091</v>
       </c>
       <c r="F246" t="n">
         <v>1</v>
@@ -16913,39 +17065,47 @@
       <c r="H246" t="n">
         <v>245</v>
       </c>
-      <c r="I246" t="inlineStr"/>
+      <c r="I246" t="n">
+        <v>12627</v>
+      </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: SABARÁ-CAETÉ (3 PONTOS)</t>
+          <t>Execução da 4ª (quarta) parcela da reforma parcial do Edifício-Sede do TRIBUNAL.</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L246" t="inlineStr"/>
-      <c r="M246" t="inlineStr"/>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M246" t="n">
+        <v>1</v>
+      </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>790000</v>
+        <v>0</v>
       </c>
       <c r="R246" t="n">
-        <v>0</v>
+        <v>38084213</v>
       </c>
       <c r="S246" t="inlineStr"/>
       <c r="T246" t="inlineStr"/>
@@ -16956,19 +17116,19 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>2311</v>
+        <v>4031</v>
       </c>
       <c r="B247" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C247" t="n">
-        <v>363</v>
+        <v>61</v>
       </c>
       <c r="D247" t="n">
-        <v>7</v>
+        <v>706</v>
       </c>
       <c r="E247" t="n">
-        <v>4006</v>
+        <v>2091</v>
       </c>
       <c r="F247" t="n">
         <v>1</v>
@@ -16979,24 +17139,26 @@
       <c r="H247" t="n">
         <v>246</v>
       </c>
-      <c r="I247" t="inlineStr"/>
+      <c r="I247" t="n">
+        <v>12146</v>
+      </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Construção da escola do Brasil Profissionalizado no município de Unaí-MG</t>
+          <t>Reforma geral do Fórum Lafayette, em Belo Horizonte/MG</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>METRO QUADRADO</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M247" t="n">
-        <v>5000</v>
+        <v>1</v>
       </c>
       <c r="N247" t="inlineStr">
         <is>
@@ -17005,19 +17167,19 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>UNAÍ</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="R247" t="n">
-        <v>0</v>
+        <v>135013067</v>
       </c>
       <c r="S247" t="inlineStr"/>
       <c r="T247" t="inlineStr"/>
@@ -17028,19 +17190,19 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>2321</v>
+        <v>4031</v>
       </c>
       <c r="B248" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C248" t="n">
-        <v>302</v>
+        <v>61</v>
       </c>
       <c r="D248" t="n">
-        <v>87</v>
+        <v>706</v>
       </c>
       <c r="E248" t="n">
-        <v>4222</v>
+        <v>2091</v>
       </c>
       <c r="F248" t="n">
         <v>1</v>
@@ -17051,10 +17213,12 @@
       <c r="H248" t="n">
         <v>247</v>
       </c>
-      <c r="I248" t="inlineStr"/>
+      <c r="I248" t="n">
+        <v>12703</v>
+      </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Projetos em unidade diversas </t>
+          <t>Cincão - Reforma parcial para adequações da estrutura física dos Armazéns 6, 7 e 8, Galpão 2, Arquivo Central e Permanente</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -17062,11 +17226,17 @@
           <t>EXECUÇÃO</t>
         </is>
       </c>
-      <c r="L248" t="inlineStr"/>
-      <c r="M248" t="inlineStr"/>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M248" t="n">
+        <v>1</v>
+      </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">
@@ -17080,10 +17250,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>800291</v>
+        <v>0</v>
       </c>
       <c r="R248" t="n">
-        <v>0</v>
+        <v>1052449</v>
       </c>
       <c r="S248" t="inlineStr"/>
       <c r="T248" t="inlineStr"/>
@@ -17094,19 +17264,19 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>2321</v>
+        <v>4031</v>
       </c>
       <c r="B249" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C249" t="n">
-        <v>302</v>
+        <v>61</v>
       </c>
       <c r="D249" t="n">
-        <v>87</v>
+        <v>706</v>
       </c>
       <c r="E249" t="n">
-        <v>4222</v>
+        <v>2091</v>
       </c>
       <c r="F249" t="n">
         <v>1</v>
@@ -17120,36 +17290,42 @@
       <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Projetos em unidade diversas </t>
+          <t>Obra de construção do novo Fórum da Comarca de Monte Alegre de Minas</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr"/>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M249" t="n">
+        <v>1</v>
+      </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>MONTE ALEGRE DE MINAS</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>174673</v>
+        <v>0</v>
       </c>
       <c r="R249" t="n">
-        <v>0</v>
+        <v>6139672</v>
       </c>
       <c r="S249" t="inlineStr"/>
       <c r="T249" t="inlineStr"/>
@@ -17160,19 +17336,19 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>2321</v>
+        <v>5011</v>
       </c>
       <c r="B250" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C250" t="n">
-        <v>302</v>
+        <v>122</v>
       </c>
       <c r="D250" t="n">
-        <v>87</v>
+        <v>133</v>
       </c>
       <c r="E250" t="n">
-        <v>4222</v>
+        <v>3017</v>
       </c>
       <c r="F250" t="n">
         <v>1</v>
@@ -17183,12 +17359,10 @@
       <c r="H250" t="n">
         <v>249</v>
       </c>
-      <c r="I250" t="n">
-        <v>11877</v>
-      </c>
+      <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Contrato a obra de reforma e ampliação</t>
+          <t>CENTRO DE CULTURA PRESIDENTE ITAMAR FRANCO</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -17205,19 +17379,19 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>SÃO JOÃO DEL REI</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>1088908</v>
+        <v>0</v>
       </c>
       <c r="R250" t="n">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="S250" t="inlineStr"/>
       <c r="T250" t="inlineStr"/>
@@ -17228,19 +17402,19 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>2361</v>
+        <v>5031</v>
       </c>
       <c r="B251" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C251" t="n">
-        <v>846</v>
+        <v>572</v>
       </c>
       <c r="D251" t="n">
-        <v>705</v>
+        <v>133</v>
       </c>
       <c r="E251" t="n">
-        <v>7004</v>
+        <v>3015</v>
       </c>
       <c r="F251" t="n">
         <v>1</v>
@@ -17254,7 +17428,7 @@
       <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Possível adequação da sede</t>
+          <t>BALNEÁRIO ÁGUAS SANTAS - TIRADENTES/MG | BARREIO DE ARAXÁ</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -17269,10 +17443,22 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="O251" t="inlineStr"/>
-      <c r="P251" t="inlineStr"/>
-      <c r="Q251" t="inlineStr"/>
-      <c r="R251" t="inlineStr"/>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+        </is>
+      </c>
+      <c r="Q251" t="n">
+        <v>0</v>
+      </c>
+      <c r="R251" t="n">
+        <v>4782988</v>
+      </c>
       <c r="S251" t="inlineStr"/>
       <c r="T251" t="inlineStr"/>
       <c r="U251" t="inlineStr"/>
@@ -17282,19 +17468,19 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>2361</v>
+        <v>5141</v>
       </c>
       <c r="B252" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C252" t="n">
-        <v>274</v>
+        <v>126</v>
       </c>
       <c r="D252" t="n">
-        <v>766</v>
+        <v>30</v>
       </c>
       <c r="E252" t="n">
-        <v>2113</v>
+        <v>6006</v>
       </c>
       <c r="F252" t="n">
         <v>1</v>
@@ -17308,7 +17494,7 @@
       <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr">
         <is>
-          <t>Possível adequação da sede</t>
+          <t>ELABORAÇÃO E EXECUÇÃO DE PROJETOS RELACIONADOS À REFORMA, MODERNIZAÇÃO E ADEQUAÇÃO DAS INSTALAÇÕES PREDIAIS DA COMPANHIA.</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -17323,10 +17509,22 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="O252" t="inlineStr"/>
-      <c r="P252" t="inlineStr"/>
-      <c r="Q252" t="inlineStr"/>
-      <c r="R252" t="inlineStr"/>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+        </is>
+      </c>
+      <c r="Q252" t="n">
+        <v>0</v>
+      </c>
+      <c r="R252" t="n">
+        <v>16317109</v>
+      </c>
       <c r="S252" t="inlineStr"/>
       <c r="T252" t="inlineStr"/>
       <c r="U252" t="inlineStr"/>
@@ -17336,19 +17534,19 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>2361</v>
+        <v>5251</v>
       </c>
       <c r="B253" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C253" t="n">
-        <v>274</v>
+        <v>121</v>
       </c>
       <c r="D253" t="n">
-        <v>767</v>
+        <v>133</v>
       </c>
       <c r="E253" t="n">
-        <v>2114</v>
+        <v>3018</v>
       </c>
       <c r="F253" t="n">
         <v>1</v>
@@ -17362,12 +17560,12 @@
       <c r="I253" t="inlineStr"/>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Possível obras de adequação da sede.</t>
+          <t>Projeto de Expansão</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L253" t="inlineStr"/>
@@ -17391,7 +17589,7 @@
         <v>0</v>
       </c>
       <c r="R253" t="n">
-        <v>2754406</v>
+        <v>457766318</v>
       </c>
       <c r="S253" t="inlineStr"/>
       <c r="T253" t="inlineStr"/>
@@ -17402,19 +17600,19 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>2371</v>
+        <v>5391</v>
       </c>
       <c r="B254" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C254" t="n">
-        <v>609</v>
+        <v>752</v>
       </c>
       <c r="D254" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E254" t="n">
-        <v>4238</v>
+        <v>3004</v>
       </c>
       <c r="F254" t="n">
         <v>1</v>
@@ -17428,7 +17626,7 @@
       <c r="I254" t="inlineStr"/>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Reestruturação física e ampliação do Laboratório de Química Agropecuária do Instituto Mineiro de Agropecuária - IMA</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -17450,14 +17648,14 @@
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>8311374</v>
+        <v>0</v>
       </c>
       <c r="R254" t="n">
-        <v>0</v>
+        <v>92004926</v>
       </c>
       <c r="S254" t="inlineStr"/>
       <c r="T254" t="inlineStr"/>
@@ -17468,19 +17666,19 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>2421</v>
+        <v>5391</v>
       </c>
       <c r="B255" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C255" t="n">
-        <v>544</v>
+        <v>752</v>
       </c>
       <c r="D255" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="E255" t="n">
-        <v>1016</v>
+        <v>3004</v>
       </c>
       <c r="F255" t="n">
         <v>1</v>
@@ -17494,7 +17692,7 @@
       <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Perfuração de Sistemas de Abastecimento de Agua conforme demanda dos municípios atendidos pelo IDENE</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -17516,14 +17714,14 @@
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>477508</v>
+        <v>0</v>
       </c>
       <c r="R255" t="n">
-        <v>0</v>
+        <v>10705994</v>
       </c>
       <c r="S255" t="inlineStr"/>
       <c r="T255" t="inlineStr"/>
@@ -17534,19 +17732,19 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>3051</v>
+        <v>5391</v>
       </c>
       <c r="B256" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C256" t="n">
-        <v>364</v>
+        <v>752</v>
       </c>
       <c r="D256" t="n">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="E256" t="n">
-        <v>4016</v>
+        <v>3004</v>
       </c>
       <c r="F256" t="n">
         <v>1</v>
@@ -17560,7 +17758,7 @@
       <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr">
         <is>
-          <t>Instalações do curso de Agropecuária de Precisão, com 1.070 m² de área total, além de 5 unidades de tratamento de águas residuárias.</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -17577,19 +17775,19 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>4825656</v>
+        <v>0</v>
       </c>
       <c r="R256" t="n">
-        <v>0</v>
+        <v>10464844</v>
       </c>
       <c r="S256" t="inlineStr"/>
       <c r="T256" t="inlineStr"/>
@@ -17600,19 +17798,19 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>3051</v>
+        <v>5391</v>
       </c>
       <c r="B257" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C257" t="n">
-        <v>364</v>
+        <v>752</v>
       </c>
       <c r="D257" t="n">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="E257" t="n">
-        <v>4016</v>
+        <v>3004</v>
       </c>
       <c r="F257" t="n">
         <v>1</v>
@@ -17626,7 +17824,7 @@
       <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Construção de novas instalações no Instituto Tecnológico de Agropecuária de Pitangui - ITAP, totalizando 3.214 m², para salas de aula, plantas-piloto de produção e laboratórios de apoio.</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -17643,19 +17841,19 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>12649000</v>
+        <v>0</v>
       </c>
       <c r="R257" t="n">
-        <v>0</v>
+        <v>2098278</v>
       </c>
       <c r="S257" t="inlineStr"/>
       <c r="T257" t="inlineStr"/>
@@ -17666,19 +17864,19 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>3051</v>
+        <v>5391</v>
       </c>
       <c r="B258" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C258" t="n">
-        <v>364</v>
+        <v>752</v>
       </c>
       <c r="D258" t="n">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="E258" t="n">
-        <v>4016</v>
+        <v>3004</v>
       </c>
       <c r="F258" t="n">
         <v>1</v>
@@ -17692,7 +17890,7 @@
       <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reforma do edifício histórico do Instituto de Laticínios Cândido Tostes, localizado no município dde juiz de Fora. </t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -17718,10 +17916,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>3715000</v>
+        <v>0</v>
       </c>
       <c r="R258" t="n">
-        <v>0</v>
+        <v>96721858</v>
       </c>
       <c r="S258" t="inlineStr"/>
       <c r="T258" t="inlineStr"/>
@@ -17732,19 +17930,19 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>3051</v>
+        <v>5391</v>
       </c>
       <c r="B259" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C259" t="n">
-        <v>571</v>
+        <v>752</v>
       </c>
       <c r="D259" t="n">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="E259" t="n">
-        <v>4018</v>
+        <v>3004</v>
       </c>
       <c r="F259" t="n">
         <v>1</v>
@@ -17758,7 +17956,7 @@
       <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr">
         <is>
-          <t>Melhoria na infraestrutura das unidades de pesquisa.</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -17775,19 +17973,19 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
         </is>
       </c>
       <c r="Q259" t="n">
         <v>0</v>
       </c>
       <c r="R259" t="n">
-        <v>250000</v>
+        <v>16415074</v>
       </c>
       <c r="S259" t="inlineStr"/>
       <c r="T259" t="inlineStr"/>
@@ -17798,19 +17996,19 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>4031</v>
+        <v>5391</v>
       </c>
       <c r="B260" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C260" t="n">
-        <v>61</v>
+        <v>752</v>
       </c>
       <c r="D260" t="n">
-        <v>706</v>
+        <v>92</v>
       </c>
       <c r="E260" t="n">
-        <v>2091</v>
+        <v>3004</v>
       </c>
       <c r="F260" t="n">
         <v>1</v>
@@ -17821,47 +18019,39 @@
       <c r="H260" t="n">
         <v>259</v>
       </c>
-      <c r="I260" t="n">
-        <v>12054</v>
-      </c>
+      <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Construção do novo prédio do Fórum da Comarca de Betim/MG</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L260" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M260" t="n">
-        <v>1</v>
-      </c>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr"/>
       <c r="N260" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
         </is>
       </c>
       <c r="Q260" t="n">
         <v>0</v>
       </c>
       <c r="R260" t="n">
-        <v>11016496</v>
+        <v>1</v>
       </c>
       <c r="S260" t="inlineStr"/>
       <c r="T260" t="inlineStr"/>
@@ -17872,19 +18062,19 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>4031</v>
+        <v>5391</v>
       </c>
       <c r="B261" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C261" t="n">
-        <v>61</v>
+        <v>752</v>
       </c>
       <c r="D261" t="n">
-        <v>706</v>
+        <v>92</v>
       </c>
       <c r="E261" t="n">
-        <v>2091</v>
+        <v>3005</v>
       </c>
       <c r="F261" t="n">
         <v>1</v>
@@ -17895,47 +18085,39 @@
       <c r="H261" t="n">
         <v>260</v>
       </c>
-      <c r="I261" t="n">
-        <v>12806</v>
-      </c>
+      <c r="I261" t="inlineStr"/>
       <c r="J261" t="inlineStr">
         <is>
-          <t>Campo Belo/MG - Construção do novo Fórum da Comarca de Campo Belo</t>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L261" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M261" t="n">
-        <v>1</v>
-      </c>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr"/>
       <c r="N261" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>CAMPO BELO</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q261" t="n">
         <v>0</v>
       </c>
       <c r="R261" t="n">
-        <v>19994210</v>
+        <v>126817302</v>
       </c>
       <c r="S261" t="inlineStr"/>
       <c r="T261" t="inlineStr"/>
@@ -17946,19 +18128,19 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>4031</v>
+        <v>5391</v>
       </c>
       <c r="B262" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C262" t="n">
-        <v>61</v>
+        <v>752</v>
       </c>
       <c r="D262" t="n">
-        <v>706</v>
+        <v>92</v>
       </c>
       <c r="E262" t="n">
-        <v>2091</v>
+        <v>3005</v>
       </c>
       <c r="F262" t="n">
         <v>1</v>
@@ -17969,47 +18151,39 @@
       <c r="H262" t="n">
         <v>261</v>
       </c>
-      <c r="I262" t="n">
-        <v>12638</v>
-      </c>
+      <c r="I262" t="inlineStr"/>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Carangola.</t>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L262" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M262" t="n">
-        <v>1</v>
-      </c>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr"/>
+      <c r="M262" t="inlineStr"/>
       <c r="N262" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>CARANGOLA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q262" t="n">
         <v>0</v>
       </c>
       <c r="R262" t="n">
-        <v>12843388</v>
+        <v>16058991</v>
       </c>
       <c r="S262" t="inlineStr"/>
       <c r="T262" t="inlineStr"/>
@@ -18020,19 +18194,19 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>4031</v>
+        <v>5391</v>
       </c>
       <c r="B263" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C263" t="n">
-        <v>61</v>
+        <v>752</v>
       </c>
       <c r="D263" t="n">
-        <v>706</v>
+        <v>92</v>
       </c>
       <c r="E263" t="n">
-        <v>2091</v>
+        <v>3005</v>
       </c>
       <c r="F263" t="n">
         <v>1</v>
@@ -18043,47 +18217,39 @@
       <c r="H263" t="n">
         <v>262</v>
       </c>
-      <c r="I263" t="n">
-        <v>12400</v>
-      </c>
+      <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Contrato a execução da obra de reforma e ampliação do Fórum da Comarca de Ipatinga/MG</t>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L263" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M263" t="n">
-        <v>1</v>
-      </c>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr"/>
       <c r="N263" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>IPATINGA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
         </is>
       </c>
       <c r="Q263" t="n">
         <v>0</v>
       </c>
       <c r="R263" t="n">
-        <v>18849069</v>
+        <v>65795530</v>
       </c>
       <c r="S263" t="inlineStr"/>
       <c r="T263" t="inlineStr"/>
@@ -18094,19 +18260,19 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>4031</v>
+        <v>5391</v>
       </c>
       <c r="B264" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C264" t="n">
-        <v>61</v>
+        <v>752</v>
       </c>
       <c r="D264" t="n">
-        <v>706</v>
+        <v>92</v>
       </c>
       <c r="E264" t="n">
-        <v>2091</v>
+        <v>3005</v>
       </c>
       <c r="F264" t="n">
         <v>1</v>
@@ -18117,47 +18283,39 @@
       <c r="H264" t="n">
         <v>263</v>
       </c>
-      <c r="I264" t="n">
-        <v>12288</v>
-      </c>
+      <c r="I264" t="inlineStr"/>
       <c r="J264" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reforma e Ampliação do Fórum da Comarca de Monte Belo/MG</t>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L264" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M264" t="n">
-        <v>1</v>
-      </c>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr"/>
       <c r="N264" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>MONTE BELO</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q264" t="n">
         <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>1950000</v>
+        <v>44156794</v>
       </c>
       <c r="S264" t="inlineStr"/>
       <c r="T264" t="inlineStr"/>
@@ -18168,19 +18326,19 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>4031</v>
+        <v>5391</v>
       </c>
       <c r="B265" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C265" t="n">
-        <v>61</v>
+        <v>752</v>
       </c>
       <c r="D265" t="n">
-        <v>706</v>
+        <v>92</v>
       </c>
       <c r="E265" t="n">
-        <v>2091</v>
+        <v>3005</v>
       </c>
       <c r="F265" t="n">
         <v>1</v>
@@ -18191,47 +18349,39 @@
       <c r="H265" t="n">
         <v>264</v>
       </c>
-      <c r="I265" t="n">
-        <v>12816</v>
-      </c>
+      <c r="I265" t="inlineStr"/>
       <c r="J265" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Pirapora/MG</t>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L265" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M265" t="n">
-        <v>1</v>
-      </c>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr"/>
       <c r="N265" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>PIRAPORA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q265" t="n">
         <v>0</v>
       </c>
       <c r="R265" t="n">
-        <v>22776109</v>
+        <v>140716908</v>
       </c>
       <c r="S265" t="inlineStr"/>
       <c r="T265" t="inlineStr"/>
@@ -18242,19 +18392,19 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>4031</v>
+        <v>5391</v>
       </c>
       <c r="B266" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C266" t="n">
-        <v>61</v>
+        <v>752</v>
       </c>
       <c r="D266" t="n">
-        <v>706</v>
+        <v>92</v>
       </c>
       <c r="E266" t="n">
-        <v>2091</v>
+        <v>3005</v>
       </c>
       <c r="F266" t="n">
         <v>1</v>
@@ -18265,47 +18415,39 @@
       <c r="H266" t="n">
         <v>265</v>
       </c>
-      <c r="I266" t="n">
-        <v>12781</v>
-      </c>
+      <c r="I266" t="inlineStr"/>
       <c r="J266" t="inlineStr">
         <is>
-          <t>Construção do novo fórum da Comarca de São Gonçalo do Sapucaí/MG</t>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L266" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M266" t="n">
-        <v>1</v>
-      </c>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="inlineStr"/>
       <c r="N266" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P266" t="inlineStr">
         <is>
-          <t>SÃO GONÇALO DO SAPUCAÍ</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
         </is>
       </c>
       <c r="Q266" t="n">
         <v>0</v>
       </c>
       <c r="R266" t="n">
-        <v>14670005</v>
+        <v>8715687</v>
       </c>
       <c r="S266" t="inlineStr"/>
       <c r="T266" t="inlineStr"/>
@@ -18316,19 +18458,19 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>4031</v>
+        <v>5391</v>
       </c>
       <c r="B267" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C267" t="n">
-        <v>61</v>
+        <v>752</v>
       </c>
       <c r="D267" t="n">
-        <v>706</v>
+        <v>92</v>
       </c>
       <c r="E267" t="n">
-        <v>2091</v>
+        <v>3005</v>
       </c>
       <c r="F267" t="n">
         <v>1</v>
@@ -18339,47 +18481,39 @@
       <c r="H267" t="n">
         <v>266</v>
       </c>
-      <c r="I267" t="n">
-        <v>12799</v>
-      </c>
+      <c r="I267" t="inlineStr"/>
       <c r="J267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construção do novo Fórum da Comarca de Timóteo/MG </t>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L267" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M267" t="n">
-        <v>1</v>
-      </c>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr"/>
+      <c r="M267" t="inlineStr"/>
       <c r="N267" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>TIMÓTEO</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
         </is>
       </c>
       <c r="Q267" t="n">
         <v>0</v>
       </c>
       <c r="R267" t="n">
-        <v>19506288</v>
+        <v>24622611</v>
       </c>
       <c r="S267" t="inlineStr"/>
       <c r="T267" t="inlineStr"/>
@@ -18390,19 +18524,19 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>4031</v>
+        <v>5391</v>
       </c>
       <c r="B268" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C268" t="n">
-        <v>61</v>
+        <v>752</v>
       </c>
       <c r="D268" t="n">
-        <v>706</v>
+        <v>94</v>
       </c>
       <c r="E268" t="n">
-        <v>2091</v>
+        <v>3001</v>
       </c>
       <c r="F268" t="n">
         <v>1</v>
@@ -18413,12 +18547,10 @@
       <c r="H268" t="n">
         <v>267</v>
       </c>
-      <c r="I268" t="n">
-        <v>12833</v>
-      </c>
+      <c r="I268" t="inlineStr"/>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Rio Novo.</t>
+          <t>Expansão do Sistema de Geração</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -18426,34 +18558,28 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L268" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M268" t="n">
-        <v>1</v>
-      </c>
+      <c r="L268" t="inlineStr"/>
+      <c r="M268" t="inlineStr"/>
       <c r="N268" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>RIO NOVO</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q268" t="n">
         <v>0</v>
       </c>
       <c r="R268" t="n">
-        <v>4976096</v>
+        <v>1</v>
       </c>
       <c r="S268" t="inlineStr"/>
       <c r="T268" t="inlineStr"/>
@@ -18462,2286 +18588,6 @@
       <c r="W268" t="inlineStr"/>
       <c r="X268" t="inlineStr"/>
     </row>
-    <row r="269">
-      <c r="A269" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B269" t="n">
-        <v>2</v>
-      </c>
-      <c r="C269" t="n">
-        <v>61</v>
-      </c>
-      <c r="D269" t="n">
-        <v>706</v>
-      </c>
-      <c r="E269" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F269" t="n">
-        <v>1</v>
-      </c>
-      <c r="G269" t="n">
-        <v>0</v>
-      </c>
-      <c r="H269" t="n">
-        <v>268</v>
-      </c>
-      <c r="I269" t="n">
-        <v>12629</v>
-      </c>
-      <c r="J269" t="inlineStr">
-        <is>
-          <t>Obra de construção do novo Fórum da Comarca de Luz.</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L269" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M269" t="n">
-        <v>1</v>
-      </c>
-      <c r="N269" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O269" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Divinópolis</t>
-        </is>
-      </c>
-      <c r="P269" t="inlineStr">
-        <is>
-          <t>LUZ</t>
-        </is>
-      </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
-      <c r="R269" t="n">
-        <v>7654409</v>
-      </c>
-      <c r="S269" t="inlineStr"/>
-      <c r="T269" t="inlineStr"/>
-      <c r="U269" t="inlineStr"/>
-      <c r="V269" t="inlineStr"/>
-      <c r="W269" t="inlineStr"/>
-      <c r="X269" t="inlineStr"/>
-    </row>
-    <row r="270">
-      <c r="A270" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B270" t="n">
-        <v>2</v>
-      </c>
-      <c r="C270" t="n">
-        <v>61</v>
-      </c>
-      <c r="D270" t="n">
-        <v>706</v>
-      </c>
-      <c r="E270" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F270" t="n">
-        <v>1</v>
-      </c>
-      <c r="G270" t="n">
-        <v>0</v>
-      </c>
-      <c r="H270" t="n">
-        <v>269</v>
-      </c>
-      <c r="I270" t="n">
-        <v>12607</v>
-      </c>
-      <c r="J270" t="inlineStr">
-        <is>
-          <t>Reforma e ampliação do Fórum da Comarca de Sete Lagoas/MG.</t>
-        </is>
-      </c>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L270" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M270" t="n">
-        <v>1</v>
-      </c>
-      <c r="N270" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O270" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Belo Horizonte</t>
-        </is>
-      </c>
-      <c r="P270" t="inlineStr">
-        <is>
-          <t>SETE LAGOAS</t>
-        </is>
-      </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
-      <c r="R270" t="n">
-        <v>32235085</v>
-      </c>
-      <c r="S270" t="inlineStr"/>
-      <c r="T270" t="inlineStr"/>
-      <c r="U270" t="inlineStr"/>
-      <c r="V270" t="inlineStr"/>
-      <c r="W270" t="inlineStr"/>
-      <c r="X270" t="inlineStr"/>
-    </row>
-    <row r="271">
-      <c r="A271" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B271" t="n">
-        <v>2</v>
-      </c>
-      <c r="C271" t="n">
-        <v>61</v>
-      </c>
-      <c r="D271" t="n">
-        <v>706</v>
-      </c>
-      <c r="E271" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F271" t="n">
-        <v>1</v>
-      </c>
-      <c r="G271" t="n">
-        <v>0</v>
-      </c>
-      <c r="H271" t="n">
-        <v>270</v>
-      </c>
-      <c r="I271" t="n">
-        <v>12639</v>
-      </c>
-      <c r="J271" t="inlineStr">
-        <is>
-          <t>Obra de construção do novo Fórum da Comarca de Três Pontas</t>
-        </is>
-      </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L271" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M271" t="n">
-        <v>1</v>
-      </c>
-      <c r="N271" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O271" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Varginha</t>
-        </is>
-      </c>
-      <c r="P271" t="inlineStr">
-        <is>
-          <t>TRÊS PONTAS</t>
-        </is>
-      </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
-      <c r="R271" t="n">
-        <v>9489687</v>
-      </c>
-      <c r="S271" t="inlineStr"/>
-      <c r="T271" t="inlineStr"/>
-      <c r="U271" t="inlineStr"/>
-      <c r="V271" t="inlineStr"/>
-      <c r="W271" t="inlineStr"/>
-      <c r="X271" t="inlineStr"/>
-    </row>
-    <row r="272">
-      <c r="A272" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B272" t="n">
-        <v>2</v>
-      </c>
-      <c r="C272" t="n">
-        <v>61</v>
-      </c>
-      <c r="D272" t="n">
-        <v>706</v>
-      </c>
-      <c r="E272" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F272" t="n">
-        <v>1</v>
-      </c>
-      <c r="G272" t="n">
-        <v>0</v>
-      </c>
-      <c r="H272" t="n">
-        <v>271</v>
-      </c>
-      <c r="I272" t="n">
-        <v>11547</v>
-      </c>
-      <c r="J272" t="inlineStr">
-        <is>
-          <t>RETOMADA DA OBRA DE CONSTRUÇÃO DO NOVO PRÉDIO DO FÓRUM DA COMARCA DE ITAJUBÁ/MG</t>
-        </is>
-      </c>
-      <c r="K272" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L272" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M272" t="n">
-        <v>1</v>
-      </c>
-      <c r="N272" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O272" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Pouso Alegre</t>
-        </is>
-      </c>
-      <c r="P272" t="inlineStr">
-        <is>
-          <t>ITAJUBÁ</t>
-        </is>
-      </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
-      <c r="R272" t="n">
-        <v>9366263</v>
-      </c>
-      <c r="S272" t="inlineStr"/>
-      <c r="T272" t="inlineStr"/>
-      <c r="U272" t="inlineStr"/>
-      <c r="V272" t="inlineStr"/>
-      <c r="W272" t="inlineStr"/>
-      <c r="X272" t="inlineStr"/>
-    </row>
-    <row r="273">
-      <c r="A273" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B273" t="n">
-        <v>2</v>
-      </c>
-      <c r="C273" t="n">
-        <v>61</v>
-      </c>
-      <c r="D273" t="n">
-        <v>706</v>
-      </c>
-      <c r="E273" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F273" t="n">
-        <v>1</v>
-      </c>
-      <c r="G273" t="n">
-        <v>0</v>
-      </c>
-      <c r="H273" t="n">
-        <v>272</v>
-      </c>
-      <c r="I273" t="n">
-        <v>12856</v>
-      </c>
-      <c r="J273" t="inlineStr">
-        <is>
-          <t>Retomada da obra de construção do novo Fórum da Comarca de Poços de Caldas.</t>
-        </is>
-      </c>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L273" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M273" t="n">
-        <v>1</v>
-      </c>
-      <c r="N273" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O273" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Pouso Alegre</t>
-        </is>
-      </c>
-      <c r="P273" t="inlineStr">
-        <is>
-          <t>POÇOS DE CALDAS</t>
-        </is>
-      </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
-      <c r="R273" t="n">
-        <v>11009635</v>
-      </c>
-      <c r="S273" t="inlineStr"/>
-      <c r="T273" t="inlineStr"/>
-      <c r="U273" t="inlineStr"/>
-      <c r="V273" t="inlineStr"/>
-      <c r="W273" t="inlineStr"/>
-      <c r="X273" t="inlineStr"/>
-    </row>
-    <row r="274">
-      <c r="A274" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B274" t="n">
-        <v>2</v>
-      </c>
-      <c r="C274" t="n">
-        <v>61</v>
-      </c>
-      <c r="D274" t="n">
-        <v>706</v>
-      </c>
-      <c r="E274" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F274" t="n">
-        <v>1</v>
-      </c>
-      <c r="G274" t="n">
-        <v>0</v>
-      </c>
-      <c r="H274" t="n">
-        <v>273</v>
-      </c>
-      <c r="I274" t="n">
-        <v>12344</v>
-      </c>
-      <c r="J274" t="inlineStr">
-        <is>
-          <t>Construção do novo prédio do Fórum da Comarca de Camanducaia/MG</t>
-        </is>
-      </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L274" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M274" t="n">
-        <v>1</v>
-      </c>
-      <c r="N274" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O274" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Pouso Alegre</t>
-        </is>
-      </c>
-      <c r="P274" t="inlineStr">
-        <is>
-          <t>CAMANDUCAIA</t>
-        </is>
-      </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
-      <c r="R274" t="n">
-        <v>4627222</v>
-      </c>
-      <c r="S274" t="inlineStr"/>
-      <c r="T274" t="inlineStr"/>
-      <c r="U274" t="inlineStr"/>
-      <c r="V274" t="inlineStr"/>
-      <c r="W274" t="inlineStr"/>
-      <c r="X274" t="inlineStr"/>
-    </row>
-    <row r="275">
-      <c r="A275" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B275" t="n">
-        <v>2</v>
-      </c>
-      <c r="C275" t="n">
-        <v>61</v>
-      </c>
-      <c r="D275" t="n">
-        <v>706</v>
-      </c>
-      <c r="E275" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F275" t="n">
-        <v>1</v>
-      </c>
-      <c r="G275" t="n">
-        <v>0</v>
-      </c>
-      <c r="H275" t="n">
-        <v>274</v>
-      </c>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr">
-        <is>
-          <t>Obra de construção do novo Fórum da Comarca de São João do Paraíso</t>
-        </is>
-      </c>
-      <c r="K275" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L275" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M275" t="n">
-        <v>1</v>
-      </c>
-      <c r="N275" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O275" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Montes Claros</t>
-        </is>
-      </c>
-      <c r="P275" t="inlineStr">
-        <is>
-          <t>SÃO JOÃO DO PARAÍSO</t>
-        </is>
-      </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
-      <c r="R275" t="n">
-        <v>7290196</v>
-      </c>
-      <c r="S275" t="inlineStr"/>
-      <c r="T275" t="inlineStr"/>
-      <c r="U275" t="inlineStr"/>
-      <c r="V275" t="inlineStr"/>
-      <c r="W275" t="inlineStr"/>
-      <c r="X275" t="inlineStr"/>
-    </row>
-    <row r="276">
-      <c r="A276" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B276" t="n">
-        <v>2</v>
-      </c>
-      <c r="C276" t="n">
-        <v>61</v>
-      </c>
-      <c r="D276" t="n">
-        <v>706</v>
-      </c>
-      <c r="E276" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F276" t="n">
-        <v>1</v>
-      </c>
-      <c r="G276" t="n">
-        <v>0</v>
-      </c>
-      <c r="H276" t="n">
-        <v>275</v>
-      </c>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr">
-        <is>
-          <t>Implantação do Fórum Digital no município de Brasilândia de Minas</t>
-        </is>
-      </c>
-      <c r="K276" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L276" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M276" t="n">
-        <v>1</v>
-      </c>
-      <c r="N276" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O276" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Patos de Minas</t>
-        </is>
-      </c>
-      <c r="P276" t="inlineStr">
-        <is>
-          <t>BRASILÂNDIA DE MINAS</t>
-        </is>
-      </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
-      <c r="R276" t="n">
-        <v>1373680</v>
-      </c>
-      <c r="S276" t="inlineStr"/>
-      <c r="T276" t="inlineStr"/>
-      <c r="U276" t="inlineStr"/>
-      <c r="V276" t="inlineStr"/>
-      <c r="W276" t="inlineStr"/>
-      <c r="X276" t="inlineStr"/>
-    </row>
-    <row r="277">
-      <c r="A277" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B277" t="n">
-        <v>2</v>
-      </c>
-      <c r="C277" t="n">
-        <v>61</v>
-      </c>
-      <c r="D277" t="n">
-        <v>706</v>
-      </c>
-      <c r="E277" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F277" t="n">
-        <v>1</v>
-      </c>
-      <c r="G277" t="n">
-        <v>0</v>
-      </c>
-      <c r="H277" t="n">
-        <v>276</v>
-      </c>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr">
-        <is>
-          <t>Implantação do Fórum Digital no município de São Gonçalo do Abaeté</t>
-        </is>
-      </c>
-      <c r="K277" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L277" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M277" t="n">
-        <v>1</v>
-      </c>
-      <c r="N277" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O277" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Patos de Minas</t>
-        </is>
-      </c>
-      <c r="P277" t="inlineStr">
-        <is>
-          <t>SÃO GONÇALO DO ABAETÉ</t>
-        </is>
-      </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
-      <c r="R277" t="n">
-        <v>1373680</v>
-      </c>
-      <c r="S277" t="inlineStr"/>
-      <c r="T277" t="inlineStr"/>
-      <c r="U277" t="inlineStr"/>
-      <c r="V277" t="inlineStr"/>
-      <c r="W277" t="inlineStr"/>
-      <c r="X277" t="inlineStr"/>
-    </row>
-    <row r="278">
-      <c r="A278" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B278" t="n">
-        <v>2</v>
-      </c>
-      <c r="C278" t="n">
-        <v>61</v>
-      </c>
-      <c r="D278" t="n">
-        <v>706</v>
-      </c>
-      <c r="E278" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F278" t="n">
-        <v>1</v>
-      </c>
-      <c r="G278" t="n">
-        <v>0</v>
-      </c>
-      <c r="H278" t="n">
-        <v>277</v>
-      </c>
-      <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr">
-        <is>
-          <t>Implantação do Fórum Digital no município de Ponto Chique</t>
-        </is>
-      </c>
-      <c r="K278" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L278" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M278" t="n">
-        <v>1</v>
-      </c>
-      <c r="N278" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O278" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Montes Claros</t>
-        </is>
-      </c>
-      <c r="P278" t="inlineStr">
-        <is>
-          <t>PONTO CHIQUE</t>
-        </is>
-      </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
-      <c r="R278" t="n">
-        <v>1760000</v>
-      </c>
-      <c r="S278" t="inlineStr"/>
-      <c r="T278" t="inlineStr"/>
-      <c r="U278" t="inlineStr"/>
-      <c r="V278" t="inlineStr"/>
-      <c r="W278" t="inlineStr"/>
-      <c r="X278" t="inlineStr"/>
-    </row>
-    <row r="279">
-      <c r="A279" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B279" t="n">
-        <v>2</v>
-      </c>
-      <c r="C279" t="n">
-        <v>61</v>
-      </c>
-      <c r="D279" t="n">
-        <v>706</v>
-      </c>
-      <c r="E279" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F279" t="n">
-        <v>1</v>
-      </c>
-      <c r="G279" t="n">
-        <v>0</v>
-      </c>
-      <c r="H279" t="n">
-        <v>278</v>
-      </c>
-      <c r="I279" t="n">
-        <v>12627</v>
-      </c>
-      <c r="J279" t="inlineStr">
-        <is>
-          <t>Execução da 4ª (quarta) parcela da reforma parcial do Edifício-Sede do TRIBUNAL.</t>
-        </is>
-      </c>
-      <c r="K279" t="inlineStr">
-        <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L279" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M279" t="n">
-        <v>1</v>
-      </c>
-      <c r="N279" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O279" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Belo Horizonte</t>
-        </is>
-      </c>
-      <c r="P279" t="inlineStr">
-        <is>
-          <t>BELO HORIZONTE</t>
-        </is>
-      </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
-      <c r="R279" t="n">
-        <v>38084213</v>
-      </c>
-      <c r="S279" t="inlineStr"/>
-      <c r="T279" t="inlineStr"/>
-      <c r="U279" t="inlineStr"/>
-      <c r="V279" t="inlineStr"/>
-      <c r="W279" t="inlineStr"/>
-      <c r="X279" t="inlineStr"/>
-    </row>
-    <row r="280">
-      <c r="A280" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B280" t="n">
-        <v>2</v>
-      </c>
-      <c r="C280" t="n">
-        <v>61</v>
-      </c>
-      <c r="D280" t="n">
-        <v>706</v>
-      </c>
-      <c r="E280" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F280" t="n">
-        <v>1</v>
-      </c>
-      <c r="G280" t="n">
-        <v>0</v>
-      </c>
-      <c r="H280" t="n">
-        <v>279</v>
-      </c>
-      <c r="I280" t="n">
-        <v>12146</v>
-      </c>
-      <c r="J280" t="inlineStr">
-        <is>
-          <t>Reforma geral do Fórum Lafayette, em Belo Horizonte/MG</t>
-        </is>
-      </c>
-      <c r="K280" t="inlineStr">
-        <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L280" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M280" t="n">
-        <v>1</v>
-      </c>
-      <c r="N280" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O280" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Belo Horizonte</t>
-        </is>
-      </c>
-      <c r="P280" t="inlineStr">
-        <is>
-          <t>BELO HORIZONTE</t>
-        </is>
-      </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
-      <c r="R280" t="n">
-        <v>135013067</v>
-      </c>
-      <c r="S280" t="inlineStr"/>
-      <c r="T280" t="inlineStr"/>
-      <c r="U280" t="inlineStr"/>
-      <c r="V280" t="inlineStr"/>
-      <c r="W280" t="inlineStr"/>
-      <c r="X280" t="inlineStr"/>
-    </row>
-    <row r="281">
-      <c r="A281" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B281" t="n">
-        <v>2</v>
-      </c>
-      <c r="C281" t="n">
-        <v>61</v>
-      </c>
-      <c r="D281" t="n">
-        <v>706</v>
-      </c>
-      <c r="E281" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F281" t="n">
-        <v>1</v>
-      </c>
-      <c r="G281" t="n">
-        <v>0</v>
-      </c>
-      <c r="H281" t="n">
-        <v>280</v>
-      </c>
-      <c r="I281" t="n">
-        <v>12703</v>
-      </c>
-      <c r="J281" t="inlineStr">
-        <is>
-          <t>Cincão - Reforma parcial para adequações da estrutura física dos Armazéns 6, 7 e 8, Galpão 2, Arquivo Central e Permanente</t>
-        </is>
-      </c>
-      <c r="K281" t="inlineStr">
-        <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L281" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M281" t="n">
-        <v>1</v>
-      </c>
-      <c r="N281" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O281" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Belo Horizonte</t>
-        </is>
-      </c>
-      <c r="P281" t="inlineStr">
-        <is>
-          <t>BELO HORIZONTE</t>
-        </is>
-      </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
-      <c r="R281" t="n">
-        <v>1052449</v>
-      </c>
-      <c r="S281" t="inlineStr"/>
-      <c r="T281" t="inlineStr"/>
-      <c r="U281" t="inlineStr"/>
-      <c r="V281" t="inlineStr"/>
-      <c r="W281" t="inlineStr"/>
-      <c r="X281" t="inlineStr"/>
-    </row>
-    <row r="282">
-      <c r="A282" t="n">
-        <v>4031</v>
-      </c>
-      <c r="B282" t="n">
-        <v>2</v>
-      </c>
-      <c r="C282" t="n">
-        <v>61</v>
-      </c>
-      <c r="D282" t="n">
-        <v>706</v>
-      </c>
-      <c r="E282" t="n">
-        <v>2091</v>
-      </c>
-      <c r="F282" t="n">
-        <v>1</v>
-      </c>
-      <c r="G282" t="n">
-        <v>0</v>
-      </c>
-      <c r="H282" t="n">
-        <v>281</v>
-      </c>
-      <c r="I282" t="inlineStr"/>
-      <c r="J282" t="inlineStr">
-        <is>
-          <t>Obra de construção do novo Fórum da Comarca de Monte Alegre de Minas</t>
-        </is>
-      </c>
-      <c r="K282" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L282" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M282" t="n">
-        <v>1</v>
-      </c>
-      <c r="N282" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O282" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Uberlândia</t>
-        </is>
-      </c>
-      <c r="P282" t="inlineStr">
-        <is>
-          <t>MONTE ALEGRE DE MINAS</t>
-        </is>
-      </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
-      <c r="R282" t="n">
-        <v>6139672</v>
-      </c>
-      <c r="S282" t="inlineStr"/>
-      <c r="T282" t="inlineStr"/>
-      <c r="U282" t="inlineStr"/>
-      <c r="V282" t="inlineStr"/>
-      <c r="W282" t="inlineStr"/>
-      <c r="X282" t="inlineStr"/>
-    </row>
-    <row r="283">
-      <c r="A283" t="n">
-        <v>5011</v>
-      </c>
-      <c r="B283" t="n">
-        <v>4</v>
-      </c>
-      <c r="C283" t="n">
-        <v>122</v>
-      </c>
-      <c r="D283" t="n">
-        <v>133</v>
-      </c>
-      <c r="E283" t="n">
-        <v>3017</v>
-      </c>
-      <c r="F283" t="n">
-        <v>1</v>
-      </c>
-      <c r="G283" t="n">
-        <v>0</v>
-      </c>
-      <c r="H283" t="n">
-        <v>282</v>
-      </c>
-      <c r="I283" t="inlineStr"/>
-      <c r="J283" t="inlineStr">
-        <is>
-          <t>CENTRO DE CULTURA PRESIDENTE ITAMAR FRANCO</t>
-        </is>
-      </c>
-      <c r="K283" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L283" t="inlineStr"/>
-      <c r="M283" t="inlineStr"/>
-      <c r="N283" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O283" t="inlineStr">
-        <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="P283" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
-      <c r="R283" t="n">
-        <v>800000</v>
-      </c>
-      <c r="S283" t="inlineStr"/>
-      <c r="T283" t="inlineStr"/>
-      <c r="U283" t="inlineStr"/>
-      <c r="V283" t="inlineStr"/>
-      <c r="W283" t="inlineStr"/>
-      <c r="X283" t="inlineStr"/>
-    </row>
-    <row r="284">
-      <c r="A284" t="n">
-        <v>5031</v>
-      </c>
-      <c r="B284" t="n">
-        <v>19</v>
-      </c>
-      <c r="C284" t="n">
-        <v>572</v>
-      </c>
-      <c r="D284" t="n">
-        <v>133</v>
-      </c>
-      <c r="E284" t="n">
-        <v>3015</v>
-      </c>
-      <c r="F284" t="n">
-        <v>1</v>
-      </c>
-      <c r="G284" t="n">
-        <v>0</v>
-      </c>
-      <c r="H284" t="n">
-        <v>283</v>
-      </c>
-      <c r="I284" t="inlineStr"/>
-      <c r="J284" t="inlineStr">
-        <is>
-          <t>BALNEÁRIO ÁGUAS SANTAS - TIRADENTES/MG | BARREIO DE ARAXÁ</t>
-        </is>
-      </c>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L284" t="inlineStr"/>
-      <c r="M284" t="inlineStr"/>
-      <c r="N284" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O284" t="inlineStr">
-        <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="P284" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
-      <c r="R284" t="n">
-        <v>4782988</v>
-      </c>
-      <c r="S284" t="inlineStr"/>
-      <c r="T284" t="inlineStr"/>
-      <c r="U284" t="inlineStr"/>
-      <c r="V284" t="inlineStr"/>
-      <c r="W284" t="inlineStr"/>
-      <c r="X284" t="inlineStr"/>
-    </row>
-    <row r="285">
-      <c r="A285" t="n">
-        <v>5141</v>
-      </c>
-      <c r="B285" t="n">
-        <v>4</v>
-      </c>
-      <c r="C285" t="n">
-        <v>126</v>
-      </c>
-      <c r="D285" t="n">
-        <v>30</v>
-      </c>
-      <c r="E285" t="n">
-        <v>6006</v>
-      </c>
-      <c r="F285" t="n">
-        <v>1</v>
-      </c>
-      <c r="G285" t="n">
-        <v>0</v>
-      </c>
-      <c r="H285" t="n">
-        <v>284</v>
-      </c>
-      <c r="I285" t="inlineStr"/>
-      <c r="J285" t="inlineStr">
-        <is>
-          <t>ELABORAÇÃO E EXECUÇÃO DE PROJETOS RELACIONADOS À REFORMA, MODERNIZAÇÃO E ADEQUAÇÃO DAS INSTALAÇÕES PREDIAIS DA COMPANHIA.</t>
-        </is>
-      </c>
-      <c r="K285" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L285" t="inlineStr"/>
-      <c r="M285" t="inlineStr"/>
-      <c r="N285" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O285" t="inlineStr">
-        <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="P285" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
-      <c r="R285" t="n">
-        <v>16317109</v>
-      </c>
-      <c r="S285" t="inlineStr"/>
-      <c r="T285" t="inlineStr"/>
-      <c r="U285" t="inlineStr"/>
-      <c r="V285" t="inlineStr"/>
-      <c r="W285" t="inlineStr"/>
-      <c r="X285" t="inlineStr"/>
-    </row>
-    <row r="286">
-      <c r="A286" t="n">
-        <v>5251</v>
-      </c>
-      <c r="B286" t="n">
-        <v>25</v>
-      </c>
-      <c r="C286" t="n">
-        <v>121</v>
-      </c>
-      <c r="D286" t="n">
-        <v>133</v>
-      </c>
-      <c r="E286" t="n">
-        <v>3018</v>
-      </c>
-      <c r="F286" t="n">
-        <v>1</v>
-      </c>
-      <c r="G286" t="n">
-        <v>0</v>
-      </c>
-      <c r="H286" t="n">
-        <v>285</v>
-      </c>
-      <c r="I286" t="inlineStr"/>
-      <c r="J286" t="inlineStr">
-        <is>
-          <t>Projeto de Expansão</t>
-        </is>
-      </c>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L286" t="inlineStr"/>
-      <c r="M286" t="inlineStr"/>
-      <c r="N286" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O286" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Belo Horizonte</t>
-        </is>
-      </c>
-      <c r="P286" t="inlineStr">
-        <is>
-          <t>BELO HORIZONTE</t>
-        </is>
-      </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
-      <c r="R286" t="n">
-        <v>457766318</v>
-      </c>
-      <c r="S286" t="inlineStr"/>
-      <c r="T286" t="inlineStr"/>
-      <c r="U286" t="inlineStr"/>
-      <c r="V286" t="inlineStr"/>
-      <c r="W286" t="inlineStr"/>
-      <c r="X286" t="inlineStr"/>
-    </row>
-    <row r="287">
-      <c r="A287" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B287" t="n">
-        <v>25</v>
-      </c>
-      <c r="C287" t="n">
-        <v>752</v>
-      </c>
-      <c r="D287" t="n">
-        <v>92</v>
-      </c>
-      <c r="E287" t="n">
-        <v>3004</v>
-      </c>
-      <c r="F287" t="n">
-        <v>1</v>
-      </c>
-      <c r="G287" t="n">
-        <v>0</v>
-      </c>
-      <c r="H287" t="n">
-        <v>286</v>
-      </c>
-      <c r="I287" t="inlineStr"/>
-      <c r="J287" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
-        </is>
-      </c>
-      <c r="K287" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L287" t="inlineStr"/>
-      <c r="M287" t="inlineStr"/>
-      <c r="N287" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O287" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Belo Horizonte</t>
-        </is>
-      </c>
-      <c r="P287" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
-        </is>
-      </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
-      <c r="R287" t="n">
-        <v>92004926</v>
-      </c>
-      <c r="S287" t="inlineStr"/>
-      <c r="T287" t="inlineStr"/>
-      <c r="U287" t="inlineStr"/>
-      <c r="V287" t="inlineStr"/>
-      <c r="W287" t="inlineStr"/>
-      <c r="X287" t="inlineStr"/>
-    </row>
-    <row r="288">
-      <c r="A288" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B288" t="n">
-        <v>25</v>
-      </c>
-      <c r="C288" t="n">
-        <v>752</v>
-      </c>
-      <c r="D288" t="n">
-        <v>92</v>
-      </c>
-      <c r="E288" t="n">
-        <v>3004</v>
-      </c>
-      <c r="F288" t="n">
-        <v>1</v>
-      </c>
-      <c r="G288" t="n">
-        <v>0</v>
-      </c>
-      <c r="H288" t="n">
-        <v>287</v>
-      </c>
-      <c r="I288" t="inlineStr"/>
-      <c r="J288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
-        </is>
-      </c>
-      <c r="K288" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L288" t="inlineStr"/>
-      <c r="M288" t="inlineStr"/>
-      <c r="N288" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O288" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Montes Claros</t>
-        </is>
-      </c>
-      <c r="P288" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
-        </is>
-      </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
-      <c r="R288" t="n">
-        <v>10705994</v>
-      </c>
-      <c r="S288" t="inlineStr"/>
-      <c r="T288" t="inlineStr"/>
-      <c r="U288" t="inlineStr"/>
-      <c r="V288" t="inlineStr"/>
-      <c r="W288" t="inlineStr"/>
-      <c r="X288" t="inlineStr"/>
-    </row>
-    <row r="289">
-      <c r="A289" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B289" t="n">
-        <v>25</v>
-      </c>
-      <c r="C289" t="n">
-        <v>752</v>
-      </c>
-      <c r="D289" t="n">
-        <v>92</v>
-      </c>
-      <c r="E289" t="n">
-        <v>3004</v>
-      </c>
-      <c r="F289" t="n">
-        <v>1</v>
-      </c>
-      <c r="G289" t="n">
-        <v>0</v>
-      </c>
-      <c r="H289" t="n">
-        <v>288</v>
-      </c>
-      <c r="I289" t="inlineStr"/>
-      <c r="J289" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
-        </is>
-      </c>
-      <c r="K289" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L289" t="inlineStr"/>
-      <c r="M289" t="inlineStr"/>
-      <c r="N289" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O289" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Juíz de Fora</t>
-        </is>
-      </c>
-      <c r="P289" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
-        </is>
-      </c>
-      <c r="Q289" t="n">
-        <v>0</v>
-      </c>
-      <c r="R289" t="n">
-        <v>10464844</v>
-      </c>
-      <c r="S289" t="inlineStr"/>
-      <c r="T289" t="inlineStr"/>
-      <c r="U289" t="inlineStr"/>
-      <c r="V289" t="inlineStr"/>
-      <c r="W289" t="inlineStr"/>
-      <c r="X289" t="inlineStr"/>
-    </row>
-    <row r="290">
-      <c r="A290" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B290" t="n">
-        <v>25</v>
-      </c>
-      <c r="C290" t="n">
-        <v>752</v>
-      </c>
-      <c r="D290" t="n">
-        <v>92</v>
-      </c>
-      <c r="E290" t="n">
-        <v>3004</v>
-      </c>
-      <c r="F290" t="n">
-        <v>1</v>
-      </c>
-      <c r="G290" t="n">
-        <v>0</v>
-      </c>
-      <c r="H290" t="n">
-        <v>289</v>
-      </c>
-      <c r="I290" t="inlineStr"/>
-      <c r="J290" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
-        </is>
-      </c>
-      <c r="K290" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L290" t="inlineStr"/>
-      <c r="M290" t="inlineStr"/>
-      <c r="N290" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O290" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Uberlândia</t>
-        </is>
-      </c>
-      <c r="P290" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
-        </is>
-      </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
-      <c r="R290" t="n">
-        <v>2098278</v>
-      </c>
-      <c r="S290" t="inlineStr"/>
-      <c r="T290" t="inlineStr"/>
-      <c r="U290" t="inlineStr"/>
-      <c r="V290" t="inlineStr"/>
-      <c r="W290" t="inlineStr"/>
-      <c r="X290" t="inlineStr"/>
-    </row>
-    <row r="291">
-      <c r="A291" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B291" t="n">
-        <v>25</v>
-      </c>
-      <c r="C291" t="n">
-        <v>752</v>
-      </c>
-      <c r="D291" t="n">
-        <v>92</v>
-      </c>
-      <c r="E291" t="n">
-        <v>3004</v>
-      </c>
-      <c r="F291" t="n">
-        <v>1</v>
-      </c>
-      <c r="G291" t="n">
-        <v>0</v>
-      </c>
-      <c r="H291" t="n">
-        <v>290</v>
-      </c>
-      <c r="I291" t="inlineStr"/>
-      <c r="J291" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
-        </is>
-      </c>
-      <c r="K291" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L291" t="inlineStr"/>
-      <c r="M291" t="inlineStr"/>
-      <c r="N291" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O291" t="inlineStr">
-        <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="P291" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q291" t="n">
-        <v>0</v>
-      </c>
-      <c r="R291" t="n">
-        <v>96721858</v>
-      </c>
-      <c r="S291" t="inlineStr"/>
-      <c r="T291" t="inlineStr"/>
-      <c r="U291" t="inlineStr"/>
-      <c r="V291" t="inlineStr"/>
-      <c r="W291" t="inlineStr"/>
-      <c r="X291" t="inlineStr"/>
-    </row>
-    <row r="292">
-      <c r="A292" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B292" t="n">
-        <v>25</v>
-      </c>
-      <c r="C292" t="n">
-        <v>752</v>
-      </c>
-      <c r="D292" t="n">
-        <v>92</v>
-      </c>
-      <c r="E292" t="n">
-        <v>3004</v>
-      </c>
-      <c r="F292" t="n">
-        <v>1</v>
-      </c>
-      <c r="G292" t="n">
-        <v>0</v>
-      </c>
-      <c r="H292" t="n">
-        <v>291</v>
-      </c>
-      <c r="I292" t="inlineStr"/>
-      <c r="J292" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
-        </is>
-      </c>
-      <c r="K292" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L292" t="inlineStr"/>
-      <c r="M292" t="inlineStr"/>
-      <c r="N292" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O292" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Uberaba</t>
-        </is>
-      </c>
-      <c r="P292" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
-        </is>
-      </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
-      <c r="R292" t="n">
-        <v>16415074</v>
-      </c>
-      <c r="S292" t="inlineStr"/>
-      <c r="T292" t="inlineStr"/>
-      <c r="U292" t="inlineStr"/>
-      <c r="V292" t="inlineStr"/>
-      <c r="W292" t="inlineStr"/>
-      <c r="X292" t="inlineStr"/>
-    </row>
-    <row r="293">
-      <c r="A293" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B293" t="n">
-        <v>25</v>
-      </c>
-      <c r="C293" t="n">
-        <v>752</v>
-      </c>
-      <c r="D293" t="n">
-        <v>92</v>
-      </c>
-      <c r="E293" t="n">
-        <v>3004</v>
-      </c>
-      <c r="F293" t="n">
-        <v>1</v>
-      </c>
-      <c r="G293" t="n">
-        <v>0</v>
-      </c>
-      <c r="H293" t="n">
-        <v>292</v>
-      </c>
-      <c r="I293" t="inlineStr"/>
-      <c r="J293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
-        </is>
-      </c>
-      <c r="K293" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L293" t="inlineStr"/>
-      <c r="M293" t="inlineStr"/>
-      <c r="N293" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O293" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Ipatinga</t>
-        </is>
-      </c>
-      <c r="P293" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
-        </is>
-      </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
-      <c r="R293" t="n">
-        <v>1</v>
-      </c>
-      <c r="S293" t="inlineStr"/>
-      <c r="T293" t="inlineStr"/>
-      <c r="U293" t="inlineStr"/>
-      <c r="V293" t="inlineStr"/>
-      <c r="W293" t="inlineStr"/>
-      <c r="X293" t="inlineStr"/>
-    </row>
-    <row r="294">
-      <c r="A294" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B294" t="n">
-        <v>25</v>
-      </c>
-      <c r="C294" t="n">
-        <v>752</v>
-      </c>
-      <c r="D294" t="n">
-        <v>92</v>
-      </c>
-      <c r="E294" t="n">
-        <v>3005</v>
-      </c>
-      <c r="F294" t="n">
-        <v>1</v>
-      </c>
-      <c r="G294" t="n">
-        <v>0</v>
-      </c>
-      <c r="H294" t="n">
-        <v>293</v>
-      </c>
-      <c r="I294" t="inlineStr"/>
-      <c r="J294" t="inlineStr">
-        <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
-        </is>
-      </c>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L294" t="inlineStr"/>
-      <c r="M294" t="inlineStr"/>
-      <c r="N294" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O294" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Belo Horizonte</t>
-        </is>
-      </c>
-      <c r="P294" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
-        </is>
-      </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
-      <c r="R294" t="n">
-        <v>126817302</v>
-      </c>
-      <c r="S294" t="inlineStr"/>
-      <c r="T294" t="inlineStr"/>
-      <c r="U294" t="inlineStr"/>
-      <c r="V294" t="inlineStr"/>
-      <c r="W294" t="inlineStr"/>
-      <c r="X294" t="inlineStr"/>
-    </row>
-    <row r="295">
-      <c r="A295" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B295" t="n">
-        <v>25</v>
-      </c>
-      <c r="C295" t="n">
-        <v>752</v>
-      </c>
-      <c r="D295" t="n">
-        <v>92</v>
-      </c>
-      <c r="E295" t="n">
-        <v>3005</v>
-      </c>
-      <c r="F295" t="n">
-        <v>1</v>
-      </c>
-      <c r="G295" t="n">
-        <v>0</v>
-      </c>
-      <c r="H295" t="n">
-        <v>294</v>
-      </c>
-      <c r="I295" t="inlineStr"/>
-      <c r="J295" t="inlineStr">
-        <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
-        </is>
-      </c>
-      <c r="K295" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L295" t="inlineStr"/>
-      <c r="M295" t="inlineStr"/>
-      <c r="N295" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O295" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Montes Claros</t>
-        </is>
-      </c>
-      <c r="P295" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
-        </is>
-      </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
-      <c r="R295" t="n">
-        <v>16058991</v>
-      </c>
-      <c r="S295" t="inlineStr"/>
-      <c r="T295" t="inlineStr"/>
-      <c r="U295" t="inlineStr"/>
-      <c r="V295" t="inlineStr"/>
-      <c r="W295" t="inlineStr"/>
-      <c r="X295" t="inlineStr"/>
-    </row>
-    <row r="296">
-      <c r="A296" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B296" t="n">
-        <v>25</v>
-      </c>
-      <c r="C296" t="n">
-        <v>752</v>
-      </c>
-      <c r="D296" t="n">
-        <v>92</v>
-      </c>
-      <c r="E296" t="n">
-        <v>3005</v>
-      </c>
-      <c r="F296" t="n">
-        <v>1</v>
-      </c>
-      <c r="G296" t="n">
-        <v>0</v>
-      </c>
-      <c r="H296" t="n">
-        <v>295</v>
-      </c>
-      <c r="I296" t="inlineStr"/>
-      <c r="J296" t="inlineStr">
-        <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
-        </is>
-      </c>
-      <c r="K296" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L296" t="inlineStr"/>
-      <c r="M296" t="inlineStr"/>
-      <c r="N296" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O296" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Juíz de Fora</t>
-        </is>
-      </c>
-      <c r="P296" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
-        </is>
-      </c>
-      <c r="Q296" t="n">
-        <v>0</v>
-      </c>
-      <c r="R296" t="n">
-        <v>65795530</v>
-      </c>
-      <c r="S296" t="inlineStr"/>
-      <c r="T296" t="inlineStr"/>
-      <c r="U296" t="inlineStr"/>
-      <c r="V296" t="inlineStr"/>
-      <c r="W296" t="inlineStr"/>
-      <c r="X296" t="inlineStr"/>
-    </row>
-    <row r="297">
-      <c r="A297" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B297" t="n">
-        <v>25</v>
-      </c>
-      <c r="C297" t="n">
-        <v>752</v>
-      </c>
-      <c r="D297" t="n">
-        <v>92</v>
-      </c>
-      <c r="E297" t="n">
-        <v>3005</v>
-      </c>
-      <c r="F297" t="n">
-        <v>1</v>
-      </c>
-      <c r="G297" t="n">
-        <v>0</v>
-      </c>
-      <c r="H297" t="n">
-        <v>296</v>
-      </c>
-      <c r="I297" t="inlineStr"/>
-      <c r="J297" t="inlineStr">
-        <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
-        </is>
-      </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L297" t="inlineStr"/>
-      <c r="M297" t="inlineStr"/>
-      <c r="N297" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O297" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Uberlândia</t>
-        </is>
-      </c>
-      <c r="P297" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
-        </is>
-      </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
-      <c r="R297" t="n">
-        <v>44156794</v>
-      </c>
-      <c r="S297" t="inlineStr"/>
-      <c r="T297" t="inlineStr"/>
-      <c r="U297" t="inlineStr"/>
-      <c r="V297" t="inlineStr"/>
-      <c r="W297" t="inlineStr"/>
-      <c r="X297" t="inlineStr"/>
-    </row>
-    <row r="298">
-      <c r="A298" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B298" t="n">
-        <v>25</v>
-      </c>
-      <c r="C298" t="n">
-        <v>752</v>
-      </c>
-      <c r="D298" t="n">
-        <v>92</v>
-      </c>
-      <c r="E298" t="n">
-        <v>3005</v>
-      </c>
-      <c r="F298" t="n">
-        <v>1</v>
-      </c>
-      <c r="G298" t="n">
-        <v>0</v>
-      </c>
-      <c r="H298" t="n">
-        <v>297</v>
-      </c>
-      <c r="I298" t="inlineStr"/>
-      <c r="J298" t="inlineStr">
-        <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
-        </is>
-      </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L298" t="inlineStr"/>
-      <c r="M298" t="inlineStr"/>
-      <c r="N298" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O298" t="inlineStr">
-        <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="P298" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q298" t="n">
-        <v>0</v>
-      </c>
-      <c r="R298" t="n">
-        <v>140716908</v>
-      </c>
-      <c r="S298" t="inlineStr"/>
-      <c r="T298" t="inlineStr"/>
-      <c r="U298" t="inlineStr"/>
-      <c r="V298" t="inlineStr"/>
-      <c r="W298" t="inlineStr"/>
-      <c r="X298" t="inlineStr"/>
-    </row>
-    <row r="299">
-      <c r="A299" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B299" t="n">
-        <v>25</v>
-      </c>
-      <c r="C299" t="n">
-        <v>752</v>
-      </c>
-      <c r="D299" t="n">
-        <v>92</v>
-      </c>
-      <c r="E299" t="n">
-        <v>3005</v>
-      </c>
-      <c r="F299" t="n">
-        <v>1</v>
-      </c>
-      <c r="G299" t="n">
-        <v>0</v>
-      </c>
-      <c r="H299" t="n">
-        <v>298</v>
-      </c>
-      <c r="I299" t="inlineStr"/>
-      <c r="J299" t="inlineStr">
-        <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
-        </is>
-      </c>
-      <c r="K299" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L299" t="inlineStr"/>
-      <c r="M299" t="inlineStr"/>
-      <c r="N299" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O299" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Ipatinga</t>
-        </is>
-      </c>
-      <c r="P299" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
-        </is>
-      </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
-      <c r="R299" t="n">
-        <v>8715687</v>
-      </c>
-      <c r="S299" t="inlineStr"/>
-      <c r="T299" t="inlineStr"/>
-      <c r="U299" t="inlineStr"/>
-      <c r="V299" t="inlineStr"/>
-      <c r="W299" t="inlineStr"/>
-      <c r="X299" t="inlineStr"/>
-    </row>
-    <row r="300">
-      <c r="A300" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B300" t="n">
-        <v>25</v>
-      </c>
-      <c r="C300" t="n">
-        <v>752</v>
-      </c>
-      <c r="D300" t="n">
-        <v>92</v>
-      </c>
-      <c r="E300" t="n">
-        <v>3005</v>
-      </c>
-      <c r="F300" t="n">
-        <v>1</v>
-      </c>
-      <c r="G300" t="n">
-        <v>0</v>
-      </c>
-      <c r="H300" t="n">
-        <v>299</v>
-      </c>
-      <c r="I300" t="inlineStr"/>
-      <c r="J300" t="inlineStr">
-        <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
-        </is>
-      </c>
-      <c r="K300" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L300" t="inlineStr"/>
-      <c r="M300" t="inlineStr"/>
-      <c r="N300" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O300" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Uberaba</t>
-        </is>
-      </c>
-      <c r="P300" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
-        </is>
-      </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
-      <c r="R300" t="n">
-        <v>24622611</v>
-      </c>
-      <c r="S300" t="inlineStr"/>
-      <c r="T300" t="inlineStr"/>
-      <c r="U300" t="inlineStr"/>
-      <c r="V300" t="inlineStr"/>
-      <c r="W300" t="inlineStr"/>
-      <c r="X300" t="inlineStr"/>
-    </row>
-    <row r="301">
-      <c r="A301" t="n">
-        <v>5391</v>
-      </c>
-      <c r="B301" t="n">
-        <v>25</v>
-      </c>
-      <c r="C301" t="n">
-        <v>752</v>
-      </c>
-      <c r="D301" t="n">
-        <v>94</v>
-      </c>
-      <c r="E301" t="n">
-        <v>3001</v>
-      </c>
-      <c r="F301" t="n">
-        <v>1</v>
-      </c>
-      <c r="G301" t="n">
-        <v>0</v>
-      </c>
-      <c r="H301" t="n">
-        <v>300</v>
-      </c>
-      <c r="I301" t="inlineStr"/>
-      <c r="J301" t="inlineStr">
-        <is>
-          <t>Expansão do Sistema de Geração</t>
-        </is>
-      </c>
-      <c r="K301" t="inlineStr">
-        <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L301" t="inlineStr"/>
-      <c r="M301" t="inlineStr"/>
-      <c r="N301" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O301" t="inlineStr">
-        <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="P301" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
-      <c r="R301" t="n">
-        <v>1</v>
-      </c>
-      <c r="S301" t="inlineStr"/>
-      <c r="T301" t="inlineStr"/>
-      <c r="U301" t="inlineStr"/>
-      <c r="V301" t="inlineStr"/>
-      <c r="W301" t="inlineStr"/>
-      <c r="X301" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/data/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -18579,7 +18579,7 @@
         <v>0</v>
       </c>
       <c r="R268" t="n">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="S268" t="inlineStr"/>
       <c r="T268" t="inlineStr"/>

--- a/data/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/data/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
         <v>60000</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
         <v>197857</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
         <v>1929103</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
         <v>1929103</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
         <v>41022</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
         <v>100000</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
       </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>280106</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>519640</v>
+        <v>799746</v>
       </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
@@ -5448,10 +5448,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>894720</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>4087644</v>
+        <v>4982364</v>
       </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
@@ -5516,10 +5516,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>8264640</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>19153735</v>
+        <v>27418375</v>
       </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
@@ -5584,10 +5584,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>3155040</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>23943007</v>
+        <v>27098047</v>
       </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
@@ -5652,10 +5652,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>4840800</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>26593690</v>
+        <v>31434490</v>
       </c>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>613500</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>2870210</v>
+        <v>3483710</v>
       </c>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
@@ -5788,10 +5788,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>5963400</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>23280000</v>
+        <v>29243400</v>
       </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>3620820</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>19100000</v>
+        <v>22720820</v>
       </c>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>1839798</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>3269655</v>
+        <v>5109453</v>
       </c>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr"/>
@@ -6058,10 +6058,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
         <v>222899</v>
-      </c>
-      <c r="R82" t="n">
-        <v>0</v>
       </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
@@ -7206,10 +7206,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
         <v>299895</v>
-      </c>
-      <c r="R99" t="n">
-        <v>0</v>
       </c>
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr"/>
@@ -7274,10 +7274,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
         <v>4565604</v>
-      </c>
-      <c r="R100" t="n">
-        <v>0</v>
       </c>
       <c r="S100" t="inlineStr"/>
       <c r="T100" t="inlineStr"/>
@@ -7342,10 +7342,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>6286532</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>2728583</v>
+        <v>9015115</v>
       </c>
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="inlineStr"/>
@@ -7410,10 +7410,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
         <v>193263</v>
-      </c>
-      <c r="R102" t="n">
-        <v>0</v>
       </c>
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="inlineStr"/>
@@ -7608,10 +7608,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>904245</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>44308050</v>
+        <v>45212295</v>
       </c>
       <c r="S105" t="inlineStr"/>
       <c r="T105" t="inlineStr"/>
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
         <v>6999284</v>
-      </c>
-      <c r="R106" t="n">
-        <v>0</v>
       </c>
       <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr"/>
@@ -7740,10 +7740,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
         <v>651694</v>
-      </c>
-      <c r="R107" t="n">
-        <v>0</v>
       </c>
       <c r="S107" t="inlineStr"/>
       <c r="T107" t="inlineStr"/>
@@ -7806,10 +7806,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
         <v>651694</v>
-      </c>
-      <c r="R108" t="n">
-        <v>0</v>
       </c>
       <c r="S108" t="inlineStr"/>
       <c r="T108" t="inlineStr"/>
@@ -7872,10 +7872,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
         <v>1472757</v>
-      </c>
-      <c r="R109" t="n">
-        <v>0</v>
       </c>
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr"/>
@@ -7938,10 +7938,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" t="n">
         <v>651694</v>
-      </c>
-      <c r="R110" t="n">
-        <v>0</v>
       </c>
       <c r="S110" t="inlineStr"/>
       <c r="T110" t="inlineStr"/>
@@ -8004,10 +8004,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="n">
         <v>18572878</v>
-      </c>
-      <c r="R111" t="n">
-        <v>0</v>
       </c>
       <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr"/>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>19850000</v>
+        <v>20000000</v>
       </c>
       <c r="S120" t="inlineStr"/>
       <c r="T120" t="inlineStr"/>
@@ -8946,10 +8946,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
         <v>350000</v>
-      </c>
-      <c r="R125" t="n">
-        <v>0</v>
       </c>
       <c r="S125" t="inlineStr"/>
       <c r="T125" t="inlineStr"/>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R126" t="n">
-        <v>0</v>
       </c>
       <c r="S126" t="inlineStr"/>
       <c r="T126" t="inlineStr"/>
@@ -9814,10 +9814,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R138" t="n">
-        <v>0</v>
       </c>
       <c r="S138" t="inlineStr"/>
       <c r="T138" t="inlineStr"/>
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
         <v>143000</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0</v>
       </c>
       <c r="S139" t="inlineStr"/>
       <c r="T139" t="inlineStr"/>
@@ -9946,10 +9946,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="n">
         <v>5876140</v>
-      </c>
-      <c r="R140" t="n">
-        <v>0</v>
       </c>
       <c r="S140" t="inlineStr"/>
       <c r="T140" t="inlineStr"/>
@@ -10012,10 +10012,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="n">
         <v>1132500</v>
-      </c>
-      <c r="R141" t="n">
-        <v>0</v>
       </c>
       <c r="S141" t="inlineStr"/>
       <c r="T141" t="inlineStr"/>
@@ -10078,10 +10078,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" t="n">
         <v>34710000</v>
-      </c>
-      <c r="R142" t="n">
-        <v>0</v>
       </c>
       <c r="S142" t="inlineStr"/>
       <c r="T142" t="inlineStr"/>
@@ -10144,10 +10144,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" t="n">
         <v>59000000</v>
-      </c>
-      <c r="R143" t="n">
-        <v>0</v>
       </c>
       <c r="S143" t="inlineStr"/>
       <c r="T143" t="inlineStr"/>
@@ -10210,10 +10210,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R144" t="n">
-        <v>0</v>
       </c>
       <c r="S144" t="inlineStr"/>
       <c r="T144" t="inlineStr"/>
@@ -10276,10 +10276,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" t="n">
         <v>200000</v>
-      </c>
-      <c r="R145" t="n">
-        <v>0</v>
       </c>
       <c r="S145" t="inlineStr"/>
       <c r="T145" t="inlineStr"/>
@@ -10342,10 +10342,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
+        <v>0</v>
+      </c>
+      <c r="R146" t="n">
         <v>30980000</v>
-      </c>
-      <c r="R146" t="n">
-        <v>0</v>
       </c>
       <c r="S146" t="inlineStr"/>
       <c r="T146" t="inlineStr"/>
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
+        <v>0</v>
+      </c>
+      <c r="R147" t="n">
         <v>25655000</v>
-      </c>
-      <c r="R147" t="n">
-        <v>0</v>
       </c>
       <c r="S147" t="inlineStr"/>
       <c r="T147" t="inlineStr"/>
@@ -10474,10 +10474,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
+        <v>0</v>
+      </c>
+      <c r="R148" t="n">
         <v>66560000</v>
-      </c>
-      <c r="R148" t="n">
-        <v>0</v>
       </c>
       <c r="S148" t="inlineStr"/>
       <c r="T148" t="inlineStr"/>
@@ -10540,10 +10540,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
+        <v>0</v>
+      </c>
+      <c r="R149" t="n">
         <v>25464500</v>
-      </c>
-      <c r="R149" t="n">
-        <v>0</v>
       </c>
       <c r="S149" t="inlineStr"/>
       <c r="T149" t="inlineStr"/>
@@ -10606,10 +10606,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
+        <v>0</v>
+      </c>
+      <c r="R150" t="n">
         <v>1202905</v>
-      </c>
-      <c r="R150" t="n">
-        <v>0</v>
       </c>
       <c r="S150" t="inlineStr"/>
       <c r="T150" t="inlineStr"/>
@@ -10672,10 +10672,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
+        <v>0</v>
+      </c>
+      <c r="R151" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R151" t="n">
-        <v>0</v>
       </c>
       <c r="S151" t="inlineStr"/>
       <c r="T151" t="inlineStr"/>
@@ -10738,10 +10738,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
+        <v>0</v>
+      </c>
+      <c r="R152" t="n">
         <v>14920000</v>
-      </c>
-      <c r="R152" t="n">
-        <v>0</v>
       </c>
       <c r="S152" t="inlineStr"/>
       <c r="T152" t="inlineStr"/>
@@ -10804,10 +10804,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
+        <v>0</v>
+      </c>
+      <c r="R153" t="n">
         <v>8798400</v>
-      </c>
-      <c r="R153" t="n">
-        <v>0</v>
       </c>
       <c r="S153" t="inlineStr"/>
       <c r="T153" t="inlineStr"/>
@@ -10870,10 +10870,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
+        <v>0</v>
+      </c>
+      <c r="R154" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R154" t="n">
-        <v>0</v>
       </c>
       <c r="S154" t="inlineStr"/>
       <c r="T154" t="inlineStr"/>
@@ -10936,10 +10936,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
+        <v>0</v>
+      </c>
+      <c r="R155" t="n">
         <v>1203643</v>
-      </c>
-      <c r="R155" t="n">
-        <v>0</v>
       </c>
       <c r="S155" t="inlineStr"/>
       <c r="T155" t="inlineStr"/>
@@ -11002,10 +11002,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
+        <v>0</v>
+      </c>
+      <c r="R156" t="n">
         <v>66620</v>
-      </c>
-      <c r="R156" t="n">
-        <v>0</v>
       </c>
       <c r="S156" t="inlineStr"/>
       <c r="T156" t="inlineStr"/>
@@ -11068,10 +11068,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
+        <v>0</v>
+      </c>
+      <c r="R157" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R157" t="n">
-        <v>0</v>
       </c>
       <c r="S157" t="inlineStr"/>
       <c r="T157" t="inlineStr"/>
@@ -11134,10 +11134,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
+        <v>0</v>
+      </c>
+      <c r="R158" t="n">
         <v>2940000</v>
-      </c>
-      <c r="R158" t="n">
-        <v>0</v>
       </c>
       <c r="S158" t="inlineStr"/>
       <c r="T158" t="inlineStr"/>
@@ -11200,10 +11200,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
+        <v>0</v>
+      </c>
+      <c r="R159" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R159" t="n">
-        <v>0</v>
       </c>
       <c r="S159" t="inlineStr"/>
       <c r="T159" t="inlineStr"/>
@@ -11266,10 +11266,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
+        <v>0</v>
+      </c>
+      <c r="R160" t="n">
         <v>542000</v>
-      </c>
-      <c r="R160" t="n">
-        <v>0</v>
       </c>
       <c r="S160" t="inlineStr"/>
       <c r="T160" t="inlineStr"/>
@@ -11332,10 +11332,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" t="n">
         <v>2163814</v>
-      </c>
-      <c r="R161" t="n">
-        <v>0</v>
       </c>
       <c r="S161" t="inlineStr"/>
       <c r="T161" t="inlineStr"/>
@@ -11398,10 +11398,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
+        <v>0</v>
+      </c>
+      <c r="R162" t="n">
         <v>11974837</v>
-      </c>
-      <c r="R162" t="n">
-        <v>0</v>
       </c>
       <c r="S162" t="inlineStr"/>
       <c r="T162" t="inlineStr"/>
@@ -11464,10 +11464,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
+        <v>0</v>
+      </c>
+      <c r="R163" t="n">
         <v>1382535</v>
-      </c>
-      <c r="R163" t="n">
-        <v>0</v>
       </c>
       <c r="S163" t="inlineStr"/>
       <c r="T163" t="inlineStr"/>
@@ -11530,10 +11530,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R164" t="n">
-        <v>0</v>
       </c>
       <c r="S164" t="inlineStr"/>
       <c r="T164" t="inlineStr"/>
@@ -11596,10 +11596,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
+        <v>0</v>
+      </c>
+      <c r="R165" t="n">
         <v>35359853</v>
-      </c>
-      <c r="R165" t="n">
-        <v>0</v>
       </c>
       <c r="S165" t="inlineStr"/>
       <c r="T165" t="inlineStr"/>
@@ -11662,10 +11662,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
+        <v>0</v>
+      </c>
+      <c r="R166" t="n">
         <v>13982612</v>
-      </c>
-      <c r="R166" t="n">
-        <v>0</v>
       </c>
       <c r="S166" t="inlineStr"/>
       <c r="T166" t="inlineStr"/>
@@ -11728,10 +11728,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R167" t="n">
-        <v>0</v>
       </c>
       <c r="S167" t="inlineStr"/>
       <c r="T167" t="inlineStr"/>
@@ -11794,10 +11794,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
+        <v>0</v>
+      </c>
+      <c r="R168" t="n">
         <v>10459632</v>
-      </c>
-      <c r="R168" t="n">
-        <v>0</v>
       </c>
       <c r="S168" t="inlineStr"/>
       <c r="T168" t="inlineStr"/>
@@ -11860,10 +11860,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
+        <v>0</v>
+      </c>
+      <c r="R169" t="n">
         <v>17000000</v>
-      </c>
-      <c r="R169" t="n">
-        <v>0</v>
       </c>
       <c r="S169" t="inlineStr"/>
       <c r="T169" t="inlineStr"/>
@@ -11926,10 +11926,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
+        <v>0</v>
+      </c>
+      <c r="R170" t="n">
         <v>74941121</v>
-      </c>
-      <c r="R170" t="n">
-        <v>0</v>
       </c>
       <c r="S170" t="inlineStr"/>
       <c r="T170" t="inlineStr"/>
@@ -11992,10 +11992,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
+        <v>0</v>
+      </c>
+      <c r="R171" t="n">
         <v>38460000</v>
-      </c>
-      <c r="R171" t="n">
-        <v>0</v>
       </c>
       <c r="S171" t="inlineStr"/>
       <c r="T171" t="inlineStr"/>
@@ -12058,10 +12058,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
+        <v>0</v>
+      </c>
+      <c r="R172" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R172" t="n">
-        <v>0</v>
       </c>
       <c r="S172" t="inlineStr"/>
       <c r="T172" t="inlineStr"/>
@@ -12124,10 +12124,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
+        <v>0</v>
+      </c>
+      <c r="R173" t="n">
         <v>7000000</v>
-      </c>
-      <c r="R173" t="n">
-        <v>0</v>
       </c>
       <c r="S173" t="inlineStr"/>
       <c r="T173" t="inlineStr"/>
@@ -12190,10 +12190,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
+        <v>0</v>
+      </c>
+      <c r="R174" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R174" t="n">
-        <v>0</v>
       </c>
       <c r="S174" t="inlineStr"/>
       <c r="T174" t="inlineStr"/>
@@ -12784,10 +12784,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
+        <v>0</v>
+      </c>
+      <c r="R183" t="n">
         <v>100000</v>
-      </c>
-      <c r="R183" t="n">
-        <v>0</v>
       </c>
       <c r="S183" t="inlineStr"/>
       <c r="T183" t="inlineStr"/>
@@ -12850,10 +12850,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
+        <v>0</v>
+      </c>
+      <c r="R184" t="n">
         <v>6121132</v>
-      </c>
-      <c r="R184" t="n">
-        <v>0</v>
       </c>
       <c r="S184" t="inlineStr"/>
       <c r="T184" t="inlineStr"/>
@@ -12916,10 +12916,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
+        <v>0</v>
+      </c>
+      <c r="R185" t="n">
         <v>3541728</v>
-      </c>
-      <c r="R185" t="n">
-        <v>0</v>
       </c>
       <c r="S185" t="inlineStr"/>
       <c r="T185" t="inlineStr"/>
@@ -12982,10 +12982,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
+        <v>0</v>
+      </c>
+      <c r="R186" t="n">
         <v>22254062</v>
-      </c>
-      <c r="R186" t="n">
-        <v>0</v>
       </c>
       <c r="S186" t="inlineStr"/>
       <c r="T186" t="inlineStr"/>
@@ -13048,10 +13048,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
+        <v>0</v>
+      </c>
+      <c r="R187" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R187" t="n">
-        <v>0</v>
       </c>
       <c r="S187" t="inlineStr"/>
       <c r="T187" t="inlineStr"/>
@@ -13114,10 +13114,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
+        <v>0</v>
+      </c>
+      <c r="R188" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R188" t="n">
-        <v>0</v>
       </c>
       <c r="S188" t="inlineStr"/>
       <c r="T188" t="inlineStr"/>
@@ -13180,10 +13180,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
+        <v>0</v>
+      </c>
+      <c r="R189" t="n">
         <v>431809</v>
-      </c>
-      <c r="R189" t="n">
-        <v>0</v>
       </c>
       <c r="S189" t="inlineStr"/>
       <c r="T189" t="inlineStr"/>
@@ -13246,10 +13246,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
+        <v>0</v>
+      </c>
+      <c r="R190" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R190" t="n">
-        <v>0</v>
       </c>
       <c r="S190" t="inlineStr"/>
       <c r="T190" t="inlineStr"/>
@@ -13312,10 +13312,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
+        <v>0</v>
+      </c>
+      <c r="R191" t="n">
         <v>14356790</v>
-      </c>
-      <c r="R191" t="n">
-        <v>0</v>
       </c>
       <c r="S191" t="inlineStr"/>
       <c r="T191" t="inlineStr"/>
@@ -13378,10 +13378,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
+        <v>0</v>
+      </c>
+      <c r="R192" t="n">
         <v>1000</v>
-      </c>
-      <c r="R192" t="n">
-        <v>0</v>
       </c>
       <c r="S192" t="inlineStr"/>
       <c r="T192" t="inlineStr"/>
@@ -13444,10 +13444,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
+        <v>0</v>
+      </c>
+      <c r="R193" t="n">
         <v>1000</v>
-      </c>
-      <c r="R193" t="n">
-        <v>0</v>
       </c>
       <c r="S193" t="inlineStr"/>
       <c r="T193" t="inlineStr"/>
@@ -13972,10 +13972,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
+        <v>0</v>
+      </c>
+      <c r="R201" t="n">
         <v>50000000</v>
-      </c>
-      <c r="R201" t="n">
-        <v>0</v>
       </c>
       <c r="S201" t="inlineStr"/>
       <c r="T201" t="inlineStr"/>
@@ -14038,10 +14038,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
+        <v>0</v>
+      </c>
+      <c r="R202" t="n">
         <v>8151612</v>
-      </c>
-      <c r="R202" t="n">
-        <v>0</v>
       </c>
       <c r="S202" t="inlineStr"/>
       <c r="T202" t="inlineStr"/>
@@ -14104,10 +14104,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
+        <v>0</v>
+      </c>
+      <c r="R203" t="n">
         <v>7488179</v>
-      </c>
-      <c r="R203" t="n">
-        <v>0</v>
       </c>
       <c r="S203" t="inlineStr"/>
       <c r="T203" t="inlineStr"/>
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
+        <v>0</v>
+      </c>
+      <c r="R204" t="n">
         <v>9608804</v>
-      </c>
-      <c r="R204" t="n">
-        <v>0</v>
       </c>
       <c r="S204" t="inlineStr"/>
       <c r="T204" t="inlineStr"/>
@@ -14236,10 +14236,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
+        <v>0</v>
+      </c>
+      <c r="R205" t="n">
         <v>8168067</v>
-      </c>
-      <c r="R205" t="n">
-        <v>0</v>
       </c>
       <c r="S205" t="inlineStr"/>
       <c r="T205" t="inlineStr"/>
@@ -14302,10 +14302,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
+        <v>0</v>
+      </c>
+      <c r="R206" t="n">
         <v>571386707</v>
-      </c>
-      <c r="R206" t="n">
-        <v>0</v>
       </c>
       <c r="S206" t="inlineStr"/>
       <c r="T206" t="inlineStr"/>
@@ -14368,10 +14368,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
+        <v>0</v>
+      </c>
+      <c r="R207" t="n">
         <v>15000000</v>
-      </c>
-      <c r="R207" t="n">
-        <v>0</v>
       </c>
       <c r="S207" t="inlineStr"/>
       <c r="T207" t="inlineStr"/>
@@ -14434,10 +14434,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
+        <v>0</v>
+      </c>
+      <c r="R208" t="n">
         <v>1406178</v>
-      </c>
-      <c r="R208" t="n">
-        <v>0</v>
       </c>
       <c r="S208" t="inlineStr"/>
       <c r="T208" t="inlineStr"/>
@@ -14500,10 +14500,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
+        <v>0</v>
+      </c>
+      <c r="R209" t="n">
         <v>19448656</v>
-      </c>
-      <c r="R209" t="n">
-        <v>0</v>
       </c>
       <c r="S209" t="inlineStr"/>
       <c r="T209" t="inlineStr"/>
@@ -14566,10 +14566,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
+        <v>0</v>
+      </c>
+      <c r="R210" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R210" t="n">
-        <v>0</v>
       </c>
       <c r="S210" t="inlineStr"/>
       <c r="T210" t="inlineStr"/>
@@ -14632,10 +14632,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
+        <v>0</v>
+      </c>
+      <c r="R211" t="n">
         <v>30000000</v>
-      </c>
-      <c r="R211" t="n">
-        <v>0</v>
       </c>
       <c r="S211" t="inlineStr"/>
       <c r="T211" t="inlineStr"/>
@@ -14698,10 +14698,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
+        <v>0</v>
+      </c>
+      <c r="R212" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R212" t="n">
-        <v>0</v>
       </c>
       <c r="S212" t="inlineStr"/>
       <c r="T212" t="inlineStr"/>
@@ -14764,10 +14764,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
+        <v>0</v>
+      </c>
+      <c r="R213" t="n">
         <v>4000000</v>
-      </c>
-      <c r="R213" t="n">
-        <v>0</v>
       </c>
       <c r="S213" t="inlineStr"/>
       <c r="T213" t="inlineStr"/>
@@ -14830,10 +14830,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
+        <v>0</v>
+      </c>
+      <c r="R214" t="n">
         <v>4000000</v>
-      </c>
-      <c r="R214" t="n">
-        <v>0</v>
       </c>
       <c r="S214" t="inlineStr"/>
       <c r="T214" t="inlineStr"/>
@@ -14896,10 +14896,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
+        <v>0</v>
+      </c>
+      <c r="R215" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R215" t="n">
-        <v>0</v>
       </c>
       <c r="S215" t="inlineStr"/>
       <c r="T215" t="inlineStr"/>
@@ -15300,10 +15300,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
+        <v>0</v>
+      </c>
+      <c r="R221" t="n">
         <v>8311374</v>
-      </c>
-      <c r="R221" t="n">
-        <v>0</v>
       </c>
       <c r="S221" t="inlineStr"/>
       <c r="T221" t="inlineStr"/>
@@ -15366,10 +15366,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
+        <v>0</v>
+      </c>
+      <c r="R222" t="n">
         <v>477508</v>
-      </c>
-      <c r="R222" t="n">
-        <v>0</v>
       </c>
       <c r="S222" t="inlineStr"/>
       <c r="T222" t="inlineStr"/>
